--- a/Codex/artifacts_test/ACC-Ltd/output_unstructured.xlsx
+++ b/Codex/artifacts_test/ACC-Ltd/output_unstructured.xlsx
@@ -1196,37 +1196,29 @@
           <t>Cement Sales - Value in cr</t>
         </is>
       </c>
-      <c r="B2" s="96">
-        <f>'DuPoint Analysis'!E9-1443</f>
-        <v/>
-      </c>
-      <c r="C2" s="96">
-        <f>'DuPoint Analysis'!F9-1534</f>
-        <v/>
-      </c>
-      <c r="D2" s="96">
-        <f>'DuPoint Analysis'!G9-916</f>
-        <v/>
-      </c>
-      <c r="E2" s="96">
-        <f>E4*E11</f>
-        <v/>
-      </c>
-      <c r="F2" s="96">
-        <f>F4*F11</f>
-        <v/>
-      </c>
-      <c r="G2" s="96">
-        <f>G4*G11</f>
-        <v/>
-      </c>
-      <c r="H2" s="96">
-        <f>H4*H11</f>
-        <v/>
-      </c>
-      <c r="I2" s="96">
-        <f>I4*I11</f>
-        <v/>
+      <c r="B2" s="96" t="n">
+        <v>11917</v>
+      </c>
+      <c r="C2" s="96" t="n">
+        <v>11112.2</v>
+      </c>
+      <c r="D2" s="96" t="n">
+        <v>13413.58</v>
+      </c>
+      <c r="E2" s="96" t="n">
+        <v>14440.82251898734</v>
+      </c>
+      <c r="F2" s="96" t="n">
+        <v>15537.25533987342</v>
+      </c>
+      <c r="G2" s="96" t="n">
+        <v>16707.22938655064</v>
+      </c>
+      <c r="H2" s="96" t="n">
+        <v>17955.35769954589</v>
+      </c>
+      <c r="I2" s="96" t="n">
+        <v>19286.5307703743</v>
       </c>
     </row>
     <row r="3">
@@ -1255,25 +1247,20 @@
       <c r="D4" s="19" t="n">
         <v>26.21</v>
       </c>
-      <c r="E4" s="14">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F4" s="14">
-        <f>F5*F6</f>
-        <v/>
-      </c>
-      <c r="G4" s="14">
-        <f>G5*G6</f>
-        <v/>
-      </c>
-      <c r="H4" s="14">
-        <f>H5*H6</f>
-        <v/>
-      </c>
-      <c r="I4" s="14">
-        <f>I5*I6</f>
-        <v/>
+      <c r="E4" s="14" t="n">
+        <v>26.87354430379747</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>27.53708860759494</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>28.20063291139241</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>28.86417721518987</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>29.52772151898735</v>
       </c>
     </row>
     <row r="5">
@@ -1291,25 +1278,20 @@
       <c r="D5" s="19" t="n">
         <v>26.56</v>
       </c>
-      <c r="E5" s="14">
-        <f>E9*E8</f>
-        <v/>
-      </c>
-      <c r="F5" s="14">
-        <f>F9*F8</f>
-        <v/>
-      </c>
-      <c r="G5" s="14">
-        <f>G9*G8</f>
-        <v/>
-      </c>
-      <c r="H5" s="14">
-        <f>H9*H8</f>
-        <v/>
-      </c>
-      <c r="I5" s="14">
-        <f>I9*I8</f>
-        <v/>
+      <c r="E5" s="14" t="n">
+        <v>27.23240506329114</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>27.90481012658228</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>28.57721518987342</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>29.24962025316455</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>29.9220253164557</v>
       </c>
     </row>
     <row r="6">
@@ -1318,37 +1300,29 @@
           <t>Sales as % of prodn</t>
         </is>
       </c>
-      <c r="B6" s="15">
-        <f>B4/B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="15">
-        <f>C4/C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>D4/D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>$D$6</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>$D$6</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>$D$6</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
-        <f>$D$6</f>
-        <v/>
-      </c>
-      <c r="I6" s="16">
-        <f>$D$6</f>
-        <v/>
+      <c r="B6" s="15" t="n">
+        <v>0.990771812080537</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0.9918032786885246</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0.9868222891566266</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.9868222891566266</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.9868222891566266</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.9868222891566266</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.9868222891566266</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>0.9868222891566266</v>
       </c>
       <c r="J6" s="44" t="inlineStr">
         <is>
@@ -1382,25 +1356,20 @@
       <c r="D8" s="15" t="n">
         <v>0.79</v>
       </c>
-      <c r="E8" s="16">
-        <f>D8+2%</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>E8+2%</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>F8+2%</f>
-        <v/>
-      </c>
-      <c r="H8" s="16">
-        <f>G8+2%</f>
-        <v/>
-      </c>
-      <c r="I8" s="16">
-        <f>H8+2%</f>
-        <v/>
+      <c r="E8" s="16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0.8900000000000001</v>
       </c>
       <c r="J8" s="44" t="inlineStr">
         <is>
@@ -1414,37 +1383,29 @@
           <t>Capacity Million Tonnes</t>
         </is>
       </c>
-      <c r="B9" s="14">
-        <f>B5*100%/B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="14">
-        <f>C5*100%/C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>D5*100%/D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
-        <f>$D$9</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f>$D$9</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>$D$9</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>$D$9</f>
-        <v/>
-      </c>
-      <c r="I9" s="17">
-        <f>$D$9</f>
-        <v/>
+      <c r="B9" s="14" t="n">
+        <v>30.96103896103896</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>31.75342465753425</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>33.62025316455696</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>33.62025316455696</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>33.62025316455696</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>33.62025316455696</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>33.62025316455696</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>33.62025316455696</v>
       </c>
       <c r="J9" s="44" t="inlineStr">
         <is>
@@ -1469,69 +1430,54 @@
           <t>Average price in crores per Million Tonnes</t>
         </is>
       </c>
-      <c r="B11" s="18">
-        <f>B2/B4</f>
-        <v/>
-      </c>
-      <c r="C11" s="18">
-        <f>C2/C4</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
-        <f>D2/D4</f>
-        <v/>
-      </c>
-      <c r="E11" s="18">
-        <f>D11*(1+E12)</f>
-        <v/>
-      </c>
-      <c r="F11" s="18">
-        <f>E11*(1+F12)</f>
-        <v/>
-      </c>
-      <c r="G11" s="18">
-        <f>F11*(1+G12)</f>
-        <v/>
-      </c>
-      <c r="H11" s="18">
-        <f>G11*(1+H12)</f>
-        <v/>
-      </c>
-      <c r="I11" s="18">
-        <f>H11*(1+I12)</f>
-        <v/>
+      <c r="B11" s="18" t="n">
+        <v>504.5300592718035</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>483.3492822966508</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>511.7733689431515</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>537.3620373903091</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>564.2301392598246</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>592.4416462228158</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>622.0637285339567</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>653.1669149606546</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="19" t="n"/>
-      <c r="C12" s="15">
-        <f>C11/B11-1</f>
-        <v/>
-      </c>
-      <c r="D12" s="15">
-        <f>D11/C11-1</f>
-        <v/>
-      </c>
-      <c r="E12" s="16">
-        <f>DCF!$B$33</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
-        <f>DCF!$B$33</f>
-        <v/>
-      </c>
-      <c r="G12" s="16">
-        <f>DCF!$B$33</f>
-        <v/>
-      </c>
-      <c r="H12" s="16">
-        <f>DCF!$B$33</f>
-        <v/>
-      </c>
-      <c r="I12" s="16">
-        <f>DCF!$B$33</f>
-        <v/>
+      <c r="C12" s="15" t="n">
+        <v>-0.04198119930797251</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0.05880651464183972</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>0.05</v>
       </c>
       <c r="J12" s="44" t="inlineStr">
         <is>
@@ -1567,37 +1513,29 @@
           <t>Average price per tonne</t>
         </is>
       </c>
-      <c r="B15" s="96">
-        <f>B11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="C15" s="96">
-        <f>C11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="D15" s="96">
-        <f>D11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="E15" s="96">
-        <f>E11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="F15" s="96">
-        <f>F11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="G15" s="96">
-        <f>G11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="H15" s="96">
-        <f>H11*10000000/1000000</f>
-        <v/>
-      </c>
-      <c r="I15" s="96">
-        <f>I11*10000000/1000000</f>
-        <v/>
+      <c r="B15" s="96" t="n">
+        <v>5045.300592718035</v>
+      </c>
+      <c r="C15" s="96" t="n">
+        <v>4833.492822966508</v>
+      </c>
+      <c r="D15" s="96" t="n">
+        <v>5117.733689431515</v>
+      </c>
+      <c r="E15" s="96" t="n">
+        <v>5373.620373903091</v>
+      </c>
+      <c r="F15" s="96" t="n">
+        <v>5642.301392598246</v>
+      </c>
+      <c r="G15" s="96" t="n">
+        <v>5924.416462228159</v>
+      </c>
+      <c r="H15" s="96" t="n">
+        <v>6220.637285339567</v>
+      </c>
+      <c r="I15" s="96" t="n">
+        <v>6531.669149606547</v>
       </c>
     </row>
     <row r="16">
@@ -1606,37 +1544,29 @@
           <t>Average price per kg</t>
         </is>
       </c>
-      <c r="B16" s="97">
-        <f>B15/1000</f>
-        <v/>
-      </c>
-      <c r="C16" s="97">
-        <f>C15/1000</f>
-        <v/>
-      </c>
-      <c r="D16" s="97">
-        <f>D15/1000</f>
-        <v/>
-      </c>
-      <c r="E16" s="97">
-        <f>E15/1000</f>
-        <v/>
-      </c>
-      <c r="F16" s="97">
-        <f>F15/1000</f>
-        <v/>
-      </c>
-      <c r="G16" s="97">
-        <f>G15/1000</f>
-        <v/>
-      </c>
-      <c r="H16" s="97">
-        <f>H15/1000</f>
-        <v/>
-      </c>
-      <c r="I16" s="97">
-        <f>I15/1000</f>
-        <v/>
+      <c r="B16" s="97" t="n">
+        <v>5.045300592718035</v>
+      </c>
+      <c r="C16" s="97" t="n">
+        <v>4.833492822966508</v>
+      </c>
+      <c r="D16" s="97" t="n">
+        <v>5.117733689431515</v>
+      </c>
+      <c r="E16" s="97" t="n">
+        <v>5.373620373903091</v>
+      </c>
+      <c r="F16" s="97" t="n">
+        <v>5.642301392598246</v>
+      </c>
+      <c r="G16" s="97" t="n">
+        <v>5.924416462228159</v>
+      </c>
+      <c r="H16" s="97" t="n">
+        <v>6.220637285339567</v>
+      </c>
+      <c r="I16" s="97" t="n">
+        <v>6.531669149606547</v>
       </c>
     </row>
     <row r="17">
@@ -1668,25 +1598,20 @@
       <c r="D19" s="26" t="n">
         <v>1965.98</v>
       </c>
-      <c r="E19" s="98">
-        <f>E$2*E29</f>
-        <v/>
-      </c>
-      <c r="F19" s="98">
-        <f>F$2*F29</f>
-        <v/>
-      </c>
-      <c r="G19" s="98">
-        <f>G$2*G29</f>
-        <v/>
-      </c>
-      <c r="H19" s="98">
-        <f>H$2*H29</f>
-        <v/>
-      </c>
-      <c r="I19" s="98">
-        <f>I$2*I29</f>
-        <v/>
+      <c r="E19" s="98" t="n">
+        <v>2116.539227848101</v>
+      </c>
+      <c r="F19" s="98" t="n">
+        <v>2277.239428481013</v>
+      </c>
+      <c r="G19" s="98" t="n">
+        <v>2448.718301107595</v>
+      </c>
+      <c r="H19" s="98" t="n">
+        <v>2631.651962425633</v>
+      </c>
+      <c r="I19" s="98" t="n">
+        <v>2826.757194122707</v>
       </c>
     </row>
     <row r="20">
@@ -1704,25 +1629,20 @@
       <c r="D20" s="26" t="n">
         <v>2716.94</v>
       </c>
-      <c r="E20" s="98">
-        <f>E$2*E30</f>
-        <v/>
-      </c>
-      <c r="F20" s="98">
-        <f>F$2*F30</f>
-        <v/>
-      </c>
-      <c r="G20" s="98">
-        <f>G$2*G30</f>
-        <v/>
-      </c>
-      <c r="H20" s="98">
-        <f>H$2*H30</f>
-        <v/>
-      </c>
-      <c r="I20" s="98">
-        <f>I$2*I30</f>
-        <v/>
+      <c r="E20" s="98" t="n">
+        <v>2925.009455696203</v>
+      </c>
+      <c r="F20" s="98" t="n">
+        <v>3147.093506962026</v>
+      </c>
+      <c r="G20" s="98" t="n">
+        <v>3384.07343971519</v>
+      </c>
+      <c r="H20" s="98" t="n">
+        <v>3636.883631976267</v>
+      </c>
+      <c r="I20" s="98" t="n">
+        <v>3906.514659864164</v>
       </c>
     </row>
     <row r="21">
@@ -1740,25 +1660,20 @@
       <c r="D21" s="26" t="n">
         <v>3433.75</v>
       </c>
-      <c r="E21" s="98">
-        <f>E$2*E31</f>
-        <v/>
-      </c>
-      <c r="F21" s="98">
-        <f>F$2*F31</f>
-        <v/>
-      </c>
-      <c r="G21" s="98">
-        <f>G$2*G31</f>
-        <v/>
-      </c>
-      <c r="H21" s="98">
-        <f>H$2*H31</f>
-        <v/>
-      </c>
-      <c r="I21" s="98">
-        <f>I$2*I31</f>
-        <v/>
+      <c r="E21" s="98" t="n">
+        <v>3913.326736518988</v>
+      </c>
+      <c r="F21" s="98" t="n">
+        <v>4288.135969139242</v>
+      </c>
+      <c r="G21" s="98" t="n">
+        <v>4694.573920977058</v>
+      </c>
+      <c r="H21" s="98" t="n">
+        <v>5135.062996512485</v>
+      </c>
+      <c r="I21" s="98" t="n">
+        <v>5612.198596657526</v>
       </c>
     </row>
     <row r="22">
@@ -1776,25 +1691,20 @@
       <c r="D22" s="26" t="n">
         <v>821.36</v>
       </c>
-      <c r="E22" s="98">
-        <f>E$2*E32</f>
-        <v/>
-      </c>
-      <c r="F22" s="98">
-        <f>F$2*F32</f>
-        <v/>
-      </c>
-      <c r="G22" s="98">
-        <f>G$2*G32</f>
-        <v/>
-      </c>
-      <c r="H22" s="98">
-        <f>H$2*H32</f>
-        <v/>
-      </c>
-      <c r="I22" s="98">
-        <f>I$2*I32</f>
-        <v/>
+      <c r="E22" s="98" t="n">
+        <v>884.2616202531647</v>
+      </c>
+      <c r="F22" s="98" t="n">
+        <v>951.4000025316458</v>
+      </c>
+      <c r="G22" s="98" t="n">
+        <v>1023.041568987342</v>
+      </c>
+      <c r="H22" s="98" t="n">
+        <v>1099.468792082279</v>
+      </c>
+      <c r="I22" s="98" t="n">
+        <v>1180.981133564241</v>
       </c>
     </row>
     <row r="23">
@@ -1812,25 +1722,20 @@
       <c r="D23" s="39" t="n">
         <v>2440.8</v>
       </c>
-      <c r="E23" s="99">
-        <f>E$2*E33</f>
-        <v/>
-      </c>
-      <c r="F23" s="99">
-        <f>F$2*F33</f>
-        <v/>
-      </c>
-      <c r="G23" s="99">
-        <f>G$2*G33</f>
-        <v/>
-      </c>
-      <c r="H23" s="99">
-        <f>H$2*H33</f>
-        <v/>
-      </c>
-      <c r="I23" s="99">
-        <f>I$2*I33</f>
-        <v/>
+      <c r="E23" s="99" t="n">
+        <v>2627.722025316456</v>
+      </c>
+      <c r="F23" s="99" t="n">
+        <v>2827.234253164558</v>
+      </c>
+      <c r="G23" s="99" t="n">
+        <v>3040.128398734178</v>
+      </c>
+      <c r="H23" s="99" t="n">
+        <v>3267.243873227849</v>
+      </c>
+      <c r="I23" s="99" t="n">
+        <v>3509.470574174053</v>
       </c>
     </row>
     <row r="24">
@@ -1839,37 +1744,29 @@
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B24" s="37">
-        <f>SUM(B19:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="37">
-        <f>SUM(C19:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="37">
-        <f>SUM(D19:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="37">
-        <f>SUM(E19:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="37">
-        <f>SUM(F19:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="37">
-        <f>SUM(G19:G23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="37">
-        <f>SUM(H19:H23)</f>
-        <v/>
-      </c>
-      <c r="I24" s="37">
-        <f>SUM(I19:I23)</f>
-        <v/>
+      <c r="B24" s="37" t="n">
+        <v>10269.05</v>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>9517.190000000001</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>11378.83</v>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>12466.85906563291</v>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>13491.10316027848</v>
+      </c>
+      <c r="G24" s="37" t="n">
+        <v>14590.53562952136</v>
+      </c>
+      <c r="H24" s="37" t="n">
+        <v>15770.31125622451</v>
+      </c>
+      <c r="I24" s="37" t="n">
+        <v>17035.92215838269</v>
       </c>
       <c r="M24" s="28" t="n"/>
     </row>
@@ -1885,37 +1782,29 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B26" s="26">
-        <f>B2-B24</f>
-        <v/>
-      </c>
-      <c r="C26" s="26">
-        <f>C2-C24</f>
-        <v/>
-      </c>
-      <c r="D26" s="26">
-        <f>D2-D24</f>
-        <v/>
-      </c>
-      <c r="E26" s="26">
-        <f>E2-E24</f>
-        <v/>
-      </c>
-      <c r="F26" s="26">
-        <f>F2-F24</f>
-        <v/>
-      </c>
-      <c r="G26" s="26">
-        <f>G2-G24</f>
-        <v/>
-      </c>
-      <c r="H26" s="26">
-        <f>H2-H24</f>
-        <v/>
-      </c>
-      <c r="I26" s="26">
-        <f>I2-I24</f>
-        <v/>
+      <c r="B26" s="26" t="n">
+        <v>1647.950000000001</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>1595.01</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>2034.749999999998</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>1973.96345335443</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>2046.152179594937</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>2116.693757029272</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>2185.046443321378</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>2250.608611991611</v>
       </c>
       <c r="M26" s="28" t="n"/>
     </row>
@@ -1925,37 +1814,29 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="B27" s="28">
-        <f>B26/B2</f>
-        <v/>
-      </c>
-      <c r="C27" s="28">
-        <f>C26/C2</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>D26/D2</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>E26/E2</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
-        <f>F26/F2</f>
-        <v/>
-      </c>
-      <c r="G27" s="28">
-        <f>G26/G2</f>
-        <v/>
-      </c>
-      <c r="H27" s="28">
-        <f>H26/H2</f>
-        <v/>
-      </c>
-      <c r="I27" s="28">
-        <f>I26/I2</f>
-        <v/>
+      <c r="B27" s="28" t="n">
+        <v>0.1382856423596543</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>0.1435368333903277</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>0.1516932839704239</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>0.136693283970424</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>0.131693283970424</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>0.126693283970424</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>0.1216932839704241</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>0.1166932839704241</v>
       </c>
       <c r="M27" s="28" t="n"/>
     </row>
@@ -1969,37 +1850,29 @@
           <t>Raw Materials as % of sales</t>
         </is>
       </c>
-      <c r="B29" s="28">
-        <f>B19/B$2</f>
-        <v/>
-      </c>
-      <c r="C29" s="28">
-        <f>C19/C$2</f>
-        <v/>
-      </c>
-      <c r="D29" s="28">
-        <f>D19/D$2</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>D29</f>
-        <v/>
-      </c>
-      <c r="F29" s="28">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="28">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="H29" s="28">
-        <f>G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="28">
-        <f>H29</f>
-        <v/>
+      <c r="B29" s="28" t="n">
+        <v>0.1550826550306285</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>0.1445951296772916</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>0.1465663901806974</v>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>0.1465663901806974</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>0.1465663901806974</v>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>0.1465663901806974</v>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>0.1465663901806974</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>0.1465663901806974</v>
       </c>
     </row>
     <row r="30">
@@ -2008,37 +1881,29 @@
           <t>Power as % of sales</t>
         </is>
       </c>
-      <c r="B30" s="28">
-        <f>B20/B$2</f>
-        <v/>
-      </c>
-      <c r="C30" s="28">
-        <f>C20/C$2</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>D20/D$2</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>D30</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
-        <f>E30</f>
-        <v/>
-      </c>
-      <c r="G30" s="28">
-        <f>F30</f>
-        <v/>
-      </c>
-      <c r="H30" s="28">
-        <f>G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="28">
-        <f>H30</f>
-        <v/>
+      <c r="B30" s="28" t="n">
+        <v>0.2011135352857263</v>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>0.1943728514605568</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>0.2025514441334826</v>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>0.2025514441334826</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>0.2025514441334826</v>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>0.2025514441334826</v>
+      </c>
+      <c r="H30" s="28" t="n">
+        <v>0.2025514441334826</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>0.2025514441334826</v>
       </c>
     </row>
     <row r="31">
@@ -2047,37 +1912,29 @@
           <t>Transport as % of sales</t>
         </is>
       </c>
-      <c r="B31" s="43">
-        <f>B21/B$2</f>
-        <v/>
-      </c>
-      <c r="C31" s="43">
-        <f>C21/C$2</f>
-        <v/>
-      </c>
-      <c r="D31" s="43">
-        <f>D21/D$2</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>D31+1.5%</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>E31+0.5%</f>
-        <v/>
-      </c>
-      <c r="G31" s="28">
-        <f>F31+0.5%</f>
-        <v/>
-      </c>
-      <c r="H31" s="28">
-        <f>G31+0.5%</f>
-        <v/>
-      </c>
-      <c r="I31" s="28">
-        <f>H31+0.5%</f>
-        <v/>
+      <c r="B31" s="43" t="n">
+        <v>0.2269203658638919</v>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>0.2372266517881248</v>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>0.2559905707499415</v>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>0.2709905707499415</v>
+      </c>
+      <c r="F31" s="28" t="n">
+        <v>0.2759905707499415</v>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>0.2809905707499415</v>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>0.2859905707499415</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>0.2909905707499415</v>
       </c>
     </row>
     <row r="32">
@@ -2086,37 +1943,29 @@
           <t>Salaries as % of sales</t>
         </is>
       </c>
-      <c r="B32" s="28">
-        <f>B22/B$2</f>
-        <v/>
-      </c>
-      <c r="C32" s="28">
-        <f>C22/C$2</f>
-        <v/>
-      </c>
-      <c r="D32" s="28">
-        <f>D22/D$2</f>
-        <v/>
-      </c>
-      <c r="E32" s="28">
-        <f>D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="28">
-        <f>E32</f>
-        <v/>
-      </c>
-      <c r="G32" s="28">
-        <f>F32</f>
-        <v/>
-      </c>
-      <c r="H32" s="28">
-        <f>G32</f>
-        <v/>
-      </c>
-      <c r="I32" s="28">
-        <f>H32</f>
-        <v/>
+      <c r="B32" s="28" t="n">
+        <v>0.06479483091382059</v>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>0.0680981263836144</v>
+      </c>
+      <c r="D32" s="28" t="n">
+        <v>0.06123346638257646</v>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>0.06123346638257646</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>0.06123346638257646</v>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>0.06123346638257646</v>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>0.06123346638257646</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>0.06123346638257646</v>
       </c>
     </row>
     <row r="33">
@@ -2125,37 +1974,29 @@
           <t>Other exps as % of sales</t>
         </is>
       </c>
-      <c r="B33" s="28">
-        <f>B23/B$2</f>
-        <v/>
-      </c>
-      <c r="C33" s="28">
-        <f>C23/C$2</f>
-        <v/>
-      </c>
-      <c r="D33" s="28">
-        <f>D23/D$2</f>
-        <v/>
-      </c>
-      <c r="E33" s="28">
-        <f>D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="28">
-        <f>E33</f>
-        <v/>
-      </c>
-      <c r="G33" s="28">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H33" s="28">
-        <f>G33</f>
-        <v/>
-      </c>
-      <c r="I33" s="28">
-        <f>H33</f>
-        <v/>
+      <c r="B33" s="28" t="n">
+        <v>0.2138029705462784</v>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>0.2121704073000846</v>
+      </c>
+      <c r="D33" s="28" t="n">
+        <v>0.181964844582878</v>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>0.181964844582878</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <v>0.181964844582878</v>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>0.181964844582878</v>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>0.181964844582878</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>0.181964844582878</v>
       </c>
     </row>
     <row r="34">
@@ -2185,13 +2026,11 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="C36" s="28">
-        <f>C35/B35-1</f>
-        <v/>
-      </c>
-      <c r="D36" s="28">
-        <f>D35/C35-1</f>
-        <v/>
+      <c r="C36" s="28" t="n">
+        <v>-0.1055008210180625</v>
+      </c>
+      <c r="D36" s="28" t="n">
+        <v>0.1663607159247362</v>
       </c>
     </row>
     <row r="37">
@@ -2214,17 +2053,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="28">
-        <f>C37/B37-1</f>
-        <v/>
-      </c>
-      <c r="D38" s="28">
-        <f>D37/C37-1</f>
-        <v/>
-      </c>
-      <c r="E38" s="28">
-        <f>E37/D37-1</f>
-        <v/>
+      <c r="C38" s="28" t="n">
+        <v>-0.1489722798415991</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>0.2003102149346332</v>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>0.3442865054458186</v>
       </c>
     </row>
     <row r="39">
@@ -2244,24 +2080,20 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="28">
-        <f>C39/B39-1</f>
-        <v/>
-      </c>
-      <c r="D40" s="28">
-        <f>D39/C39-1</f>
-        <v/>
+      <c r="C40" s="28" t="n">
+        <v>0.04235561945842314</v>
+      </c>
+      <c r="D40" s="28" t="n">
+        <v>-0.02567676303235822</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="44" t="n"/>
-      <c r="C41" s="28">
-        <f>C21/B21-1</f>
-        <v/>
-      </c>
-      <c r="D41" s="28">
-        <f>D21/C21-1</f>
-        <v/>
+      <c r="C41" s="28" t="n">
+        <v>-0.02518295546573668</v>
+      </c>
+      <c r="D41" s="28" t="n">
+        <v>0.3025822139440311</v>
       </c>
       <c r="E41" s="28" t="n"/>
       <c r="F41" s="28" t="n"/>
@@ -2819,37 +2651,29 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B2" s="100">
-        <f>'Revenue Model'!B2</f>
-        <v/>
-      </c>
-      <c r="C2" s="100">
-        <f>'Revenue Model'!C2</f>
-        <v/>
-      </c>
-      <c r="D2" s="100">
-        <f>'Revenue Model'!D2</f>
-        <v/>
-      </c>
-      <c r="E2" s="100">
-        <f>'Revenue Model'!E2</f>
-        <v/>
-      </c>
-      <c r="F2" s="100">
-        <f>'Revenue Model'!F2</f>
-        <v/>
-      </c>
-      <c r="G2" s="100">
-        <f>'Revenue Model'!G2</f>
-        <v/>
-      </c>
-      <c r="H2" s="100">
-        <f>'Revenue Model'!H2</f>
-        <v/>
-      </c>
-      <c r="I2" s="100">
-        <f>'Revenue Model'!I2</f>
-        <v/>
+      <c r="B2" s="100" t="n">
+        <v>11917</v>
+      </c>
+      <c r="C2" s="100" t="n">
+        <v>11112.2</v>
+      </c>
+      <c r="D2" s="100" t="n">
+        <v>13413.58</v>
+      </c>
+      <c r="E2" s="100" t="n">
+        <v>14440.82251898734</v>
+      </c>
+      <c r="F2" s="100" t="n">
+        <v>15537.25533987342</v>
+      </c>
+      <c r="G2" s="100" t="n">
+        <v>16707.22938655064</v>
+      </c>
+      <c r="H2" s="100" t="n">
+        <v>17955.35769954589</v>
+      </c>
+      <c r="I2" s="100" t="n">
+        <v>19286.5307703743</v>
       </c>
       <c r="K2" s="44" t="inlineStr">
         <is>
@@ -2897,41 +2721,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>'Revenue Model'!A19</f>
-        <v/>
-      </c>
-      <c r="B4" s="26">
-        <f>'Revenue Model'!B19</f>
-        <v/>
-      </c>
-      <c r="C4" s="26">
-        <f>'Revenue Model'!C19</f>
-        <v/>
-      </c>
-      <c r="D4" s="26">
-        <f>'Revenue Model'!D19</f>
-        <v/>
-      </c>
-      <c r="E4" s="26">
-        <f>'Revenue Model'!E19</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>'Revenue Model'!F19</f>
-        <v/>
-      </c>
-      <c r="G4" s="26">
-        <f>'Revenue Model'!G19</f>
-        <v/>
-      </c>
-      <c r="H4" s="26">
-        <f>'Revenue Model'!H19</f>
-        <v/>
-      </c>
-      <c r="I4" s="26">
-        <f>'Revenue Model'!I19</f>
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n">
+        <v>1848.12</v>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>1606.77</v>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>1965.98</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>2116.539227848101</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>2277.239428481013</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>2448.718301107595</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>2631.651962425633</v>
+      </c>
+      <c r="I4" s="26" t="n">
+        <v>2826.757194122707</v>
       </c>
       <c r="K4" s="44" t="inlineStr">
         <is>
@@ -2943,63 +2760,51 @@
       <c r="N4" s="26" t="n">
         <v>9167.860000000001</v>
       </c>
-      <c r="O4" s="98">
-        <f>N4+E20</f>
-        <v/>
-      </c>
-      <c r="P4" s="98">
-        <f>O4+F20</f>
-        <v/>
-      </c>
-      <c r="Q4" s="98">
-        <f>P4+G20</f>
-        <v/>
-      </c>
-      <c r="R4" s="98">
-        <f>Q4+H20</f>
-        <v/>
-      </c>
-      <c r="S4" s="98">
-        <f>R4+I20</f>
-        <v/>
+      <c r="O4" s="98" t="n">
+        <v>9775.935080537865</v>
+      </c>
+      <c r="P4" s="98" t="n">
+        <v>10425.74684436236</v>
+      </c>
+      <c r="Q4" s="98" t="n">
+        <v>11114.37960676032</v>
+      </c>
+      <c r="R4" s="98" t="n">
+        <v>11838.81970358575</v>
+      </c>
+      <c r="S4" s="98" t="n">
+        <v>12595.89211658078</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <f>'Revenue Model'!A20</f>
-        <v/>
-      </c>
-      <c r="B5" s="26">
-        <f>'Revenue Model'!B20</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
-        <f>'Revenue Model'!C20</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
-        <f>'Revenue Model'!D20</f>
-        <v/>
-      </c>
-      <c r="E5" s="26">
-        <f>'Revenue Model'!E20</f>
-        <v/>
-      </c>
-      <c r="F5" s="26">
-        <f>'Revenue Model'!F20</f>
-        <v/>
-      </c>
-      <c r="G5" s="26">
-        <f>'Revenue Model'!G20</f>
-        <v/>
-      </c>
-      <c r="H5" s="26">
-        <f>'Revenue Model'!H20</f>
-        <v/>
-      </c>
-      <c r="I5" s="26">
-        <f>'Revenue Model'!I20</f>
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>2396.67</v>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>2159.91</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>2716.94</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>2925.009455696203</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>3147.093506962026</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>3384.07343971519</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>3636.883631976267</v>
+      </c>
+      <c r="I5" s="26" t="n">
+        <v>3906.514659864164</v>
       </c>
       <c r="K5" s="44" t="inlineStr">
         <is>
@@ -3026,103 +2831,83 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>'Revenue Model'!A21</f>
-        <v/>
-      </c>
-      <c r="B6" s="26">
-        <f>'Revenue Model'!B21</f>
-        <v/>
-      </c>
-      <c r="C6" s="26">
-        <f>'Revenue Model'!C21</f>
-        <v/>
-      </c>
-      <c r="D6" s="26">
-        <f>'Revenue Model'!D21</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>'Revenue Model'!E21</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>'Revenue Model'!F21</f>
-        <v/>
-      </c>
-      <c r="G6" s="26">
-        <f>'Revenue Model'!G21</f>
-        <v/>
-      </c>
-      <c r="H6" s="26">
-        <f>'Revenue Model'!H21</f>
-        <v/>
-      </c>
-      <c r="I6" s="26">
-        <f>'Revenue Model'!I21</f>
-        <v/>
-      </c>
-      <c r="N6" s="98">
-        <f>SUM(N3:N5)</f>
-        <v/>
-      </c>
-      <c r="O6" s="98">
-        <f>SUM(O3:O5)</f>
-        <v/>
-      </c>
-      <c r="P6" s="98">
-        <f>SUM(P3:P5)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="98">
-        <f>SUM(Q3:Q5)</f>
-        <v/>
-      </c>
-      <c r="R6" s="98">
-        <f>SUM(R3:R5)</f>
-        <v/>
-      </c>
-      <c r="S6" s="98">
-        <f>SUM(S3:S5)</f>
-        <v/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>2704.21</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>2636.11</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>3433.75</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>3913.326736518988</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>4288.135969139242</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>4694.573920977058</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>5135.062996512485</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>5612.198596657526</v>
+      </c>
+      <c r="N6" s="98" t="n">
+        <v>9355.860000000001</v>
+      </c>
+      <c r="O6" s="98" t="n">
+        <v>9963.925080537865</v>
+      </c>
+      <c r="P6" s="98" t="n">
+        <v>10613.73684436236</v>
+      </c>
+      <c r="Q6" s="98" t="n">
+        <v>11302.36960676032</v>
+      </c>
+      <c r="R6" s="98" t="n">
+        <v>12026.80970358575</v>
+      </c>
+      <c r="S6" s="98" t="n">
+        <v>12783.88211658078</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>'Revenue Model'!A22</f>
-        <v/>
-      </c>
-      <c r="B7" s="26">
-        <f>'Revenue Model'!B22</f>
-        <v/>
-      </c>
-      <c r="C7" s="26">
-        <f>'Revenue Model'!C22</f>
-        <v/>
-      </c>
-      <c r="D7" s="26">
-        <f>'Revenue Model'!D22</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>'Revenue Model'!E22</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>'Revenue Model'!F22</f>
-        <v/>
-      </c>
-      <c r="G7" s="26">
-        <f>'Revenue Model'!G22</f>
-        <v/>
-      </c>
-      <c r="H7" s="26">
-        <f>'Revenue Model'!H22</f>
-        <v/>
-      </c>
-      <c r="I7" s="26">
-        <f>'Revenue Model'!I22</f>
-        <v/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>772.16</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>756.72</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>821.36</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>884.2616202531647</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>951.4000025316458</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>1023.041568987342</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>1099.468792082279</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>1180.981133564241</v>
       </c>
       <c r="K7" s="44" t="inlineStr">
         <is>
@@ -3132,41 +2917,34 @@
       <c r="N7" s="98" t="n"/>
     </row>
     <row r="8">
-      <c r="A8">
-        <f>'Revenue Model'!A23</f>
-        <v/>
-      </c>
-      <c r="B8" s="26">
-        <f>'Revenue Model'!B23</f>
-        <v/>
-      </c>
-      <c r="C8" s="26">
-        <f>'Revenue Model'!C23</f>
-        <v/>
-      </c>
-      <c r="D8" s="26">
-        <f>'Revenue Model'!D23</f>
-        <v/>
-      </c>
-      <c r="E8" s="26">
-        <f>'Revenue Model'!E23</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>'Revenue Model'!F23</f>
-        <v/>
-      </c>
-      <c r="G8" s="26">
-        <f>'Revenue Model'!G23</f>
-        <v/>
-      </c>
-      <c r="H8" s="26">
-        <f>'Revenue Model'!H23</f>
-        <v/>
-      </c>
-      <c r="I8" s="26">
-        <f>'Revenue Model'!I23</f>
-        <v/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Other exps</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>2547.89</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>2357.68</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>2440.8</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>2627.722025316456</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>2827.234253164558</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>3040.128398734178</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>3267.243873227849</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>3509.470574174053</v>
       </c>
       <c r="K8" s="44" t="inlineStr">
         <is>
@@ -3175,96 +2953,77 @@
       </c>
       <c r="L8" s="100" t="n"/>
       <c r="M8" s="100" t="n"/>
-      <c r="N8" s="100">
-        <f>'Asset schedule'!D6+'Asset schedule'!D14+'Asset schedule'!D22+'Asset schedule'!D30+'Asset schedule'!D38+'Asset schedule'!D46+'Asset schedule'!D54+'Asset schedule'!D62+'Asset schedule'!D70+'Asset schedule'!D78+'Asset schedule'!D86</f>
-        <v/>
-      </c>
-      <c r="O8" s="100">
-        <f>'Asset schedule'!E6+'Asset schedule'!E14+'Asset schedule'!E22+'Asset schedule'!E30+'Asset schedule'!E38+'Asset schedule'!E46+'Asset schedule'!E54+'Asset schedule'!E62+'Asset schedule'!E70+'Asset schedule'!E78+'Asset schedule'!E86</f>
-        <v/>
-      </c>
-      <c r="P8" s="100">
-        <f>'Asset schedule'!F6+'Asset schedule'!F14+'Asset schedule'!F22+'Asset schedule'!F30+'Asset schedule'!F38+'Asset schedule'!F46+'Asset schedule'!F54+'Asset schedule'!F62+'Asset schedule'!F70+'Asset schedule'!F78+'Asset schedule'!F86</f>
-        <v/>
-      </c>
-      <c r="Q8" s="100">
-        <f>'Asset schedule'!G6+'Asset schedule'!G14+'Asset schedule'!G22+'Asset schedule'!G30+'Asset schedule'!G38+'Asset schedule'!G46+'Asset schedule'!G54+'Asset schedule'!G62+'Asset schedule'!G70+'Asset schedule'!G78+'Asset schedule'!G86</f>
-        <v/>
-      </c>
-      <c r="R8" s="100">
-        <f>'Asset schedule'!H6+'Asset schedule'!H14+'Asset schedule'!H22+'Asset schedule'!H30+'Asset schedule'!H38+'Asset schedule'!H46+'Asset schedule'!H54+'Asset schedule'!H62+'Asset schedule'!H70+'Asset schedule'!H78+'Asset schedule'!H86</f>
-        <v/>
-      </c>
-      <c r="S8" s="100">
-        <f>'Asset schedule'!I6+'Asset schedule'!I14+'Asset schedule'!I22+'Asset schedule'!I30+'Asset schedule'!I38+'Asset schedule'!I46+'Asset schedule'!I54+'Asset schedule'!I62+'Asset schedule'!I70+'Asset schedule'!I78+'Asset schedule'!I86</f>
-        <v/>
+      <c r="N8" s="100" t="n">
+        <v>7264.49</v>
+      </c>
+      <c r="O8" s="100" t="n">
+        <v>7088.693052020696</v>
+      </c>
+      <c r="P8" s="100" t="n">
+        <v>6960.331255933688</v>
+      </c>
+      <c r="Q8" s="100" t="n">
+        <v>6876.924751098072</v>
+      </c>
+      <c r="R8" s="100" t="n">
+        <v>6836.457073271327</v>
+      </c>
+      <c r="S8" s="100" t="n">
+        <v>6837.308117831549</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36">
-        <f>'Revenue Model'!A24</f>
-        <v/>
-      </c>
-      <c r="B9" s="37">
-        <f>SUM(B4:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="37">
-        <f>SUM(C4:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="37">
-        <f>SUM(D4:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="37">
-        <f>SUM(E4:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="37">
-        <f>SUM(F4:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="37">
-        <f>SUM(G4:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="37">
-        <f>SUM(H4:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="37">
-        <f>SUM(I4:I8)</f>
-        <v/>
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="n">
+        <v>10269.05</v>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>9517.190000000001</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>11378.83</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>12466.85906563291</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>13491.10316027848</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <v>14590.53562952136</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>15770.31125622451</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>17035.92215838269</v>
       </c>
       <c r="K9" s="44" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="N9" s="100">
-        <f>N34</f>
-        <v/>
-      </c>
-      <c r="O9" s="100">
-        <f>O34</f>
-        <v/>
-      </c>
-      <c r="P9" s="100">
-        <f>P34</f>
-        <v/>
-      </c>
-      <c r="Q9" s="100">
-        <f>Q34</f>
-        <v/>
-      </c>
-      <c r="R9" s="100">
-        <f>R34</f>
-        <v/>
-      </c>
-      <c r="S9" s="100">
-        <f>S34</f>
-        <v/>
+      <c r="N9" s="100" t="n">
+        <v>2559.11</v>
+      </c>
+      <c r="O9" s="100" t="n">
+        <v>3143.421708963787</v>
+      </c>
+      <c r="P9" s="100" t="n">
+        <v>3888.890718034904</v>
+      </c>
+      <c r="Q9" s="100" t="n">
+        <v>4626.195635123337</v>
+      </c>
+      <c r="R9" s="100" t="n">
+        <v>5354.223003271239</v>
+      </c>
+      <c r="S9" s="100" t="n">
+        <v>6071.295348656084</v>
       </c>
     </row>
     <row r="10">
@@ -3273,61 +3032,47 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="26">
-        <f>B2-B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="26">
-        <f>C2-C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="26">
-        <f>D2-D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="26">
-        <f>E2-E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="26">
-        <f>F2-F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="26">
-        <f>G2-G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="26">
-        <f>H2-H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="26">
-        <f>I2-I9</f>
-        <v/>
-      </c>
-      <c r="N10" s="98">
-        <f>SUM(N8:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="98">
-        <f>SUM(O8:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="98">
-        <f>SUM(P8:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="98">
-        <f>SUM(Q8:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="98">
-        <f>SUM(R8:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="98">
-        <f>SUM(S8:S9)</f>
-        <v/>
+      <c r="B10" s="26" t="n">
+        <v>1647.950000000001</v>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>1595.01</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>2034.749999999998</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>1973.96345335443</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>2046.152179594937</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>2116.693757029272</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>2185.046443321378</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>2250.608611991611</v>
+      </c>
+      <c r="N10" s="98" t="n">
+        <v>9823.6</v>
+      </c>
+      <c r="O10" s="98" t="n">
+        <v>10232.11476098448</v>
+      </c>
+      <c r="P10" s="98" t="n">
+        <v>10849.22197396859</v>
+      </c>
+      <c r="Q10" s="98" t="n">
+        <v>11503.12038622141</v>
+      </c>
+      <c r="R10" s="98" t="n">
+        <v>12190.68007654257</v>
+      </c>
+      <c r="S10" s="98" t="n">
+        <v>12908.60346648763</v>
       </c>
     </row>
     <row r="11">
@@ -3342,53 +3087,41 @@
       <c r="C11" s="41" t="n">
         <v>609.1799999999999</v>
       </c>
-      <c r="D11" s="41">
-        <f>'Asset schedule'!D5+'Asset schedule'!D13+'Asset schedule'!D21+'Asset schedule'!D29+'Asset schedule'!D37+'Asset schedule'!D45+'Asset schedule'!D53+'Asset schedule'!D61+'Asset schedule'!D69+'Asset schedule'!D77+'Asset schedule'!D85</f>
-        <v/>
-      </c>
-      <c r="E11" s="41">
-        <f>'Asset schedule'!E5+'Asset schedule'!E13+'Asset schedule'!E21+'Asset schedule'!E29+'Asset schedule'!E37+'Asset schedule'!E45+'Asset schedule'!E53+'Asset schedule'!E61+'Asset schedule'!E69+'Asset schedule'!E77+'Asset schedule'!E85</f>
-        <v/>
-      </c>
-      <c r="F11" s="41">
-        <f>'Asset schedule'!F5+'Asset schedule'!F13+'Asset schedule'!F21+'Asset schedule'!F29+'Asset schedule'!F37+'Asset schedule'!F45+'Asset schedule'!F53+'Asset schedule'!F61+'Asset schedule'!F69+'Asset schedule'!F77+'Asset schedule'!F85</f>
-        <v/>
-      </c>
-      <c r="G11" s="41">
-        <f>'Asset schedule'!G5+'Asset schedule'!G13+'Asset schedule'!G21+'Asset schedule'!G29+'Asset schedule'!G37+'Asset schedule'!G45+'Asset schedule'!G53+'Asset schedule'!G61+'Asset schedule'!G69+'Asset schedule'!G77+'Asset schedule'!G85</f>
-        <v/>
-      </c>
-      <c r="H11" s="41">
-        <f>'Asset schedule'!H5+'Asset schedule'!H13+'Asset schedule'!H21+'Asset schedule'!H29+'Asset schedule'!H37+'Asset schedule'!H45+'Asset schedule'!H53+'Asset schedule'!H61+'Asset schedule'!H69+'Asset schedule'!H77+'Asset schedule'!H85</f>
-        <v/>
-      </c>
-      <c r="I11" s="41">
-        <f>'Asset schedule'!I5+'Asset schedule'!I13+'Asset schedule'!I21+'Asset schedule'!I29+'Asset schedule'!I37+'Asset schedule'!I45+'Asset schedule'!I53+'Asset schedule'!I61+'Asset schedule'!I69+'Asset schedule'!I77+'Asset schedule'!I85</f>
-        <v/>
-      </c>
-      <c r="N11" s="101">
-        <f>N6-N10</f>
-        <v/>
-      </c>
-      <c r="O11" s="101">
-        <f>O6-O10</f>
-        <v/>
-      </c>
-      <c r="P11" s="101">
-        <f>P6-P10</f>
-        <v/>
-      </c>
-      <c r="Q11" s="101">
-        <f>Q6-Q10</f>
-        <v/>
-      </c>
-      <c r="R11" s="101">
-        <f>R6-R10</f>
-        <v/>
-      </c>
-      <c r="S11" s="101">
-        <f>S6-S10</f>
-        <v/>
+      <c r="D11" s="41" t="n">
+        <v>643.6199999999999</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>582.6373910172789</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>566.0919764667541</v>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>554.0982951837184</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>546.3229136890859</v>
+      </c>
+      <c r="I11" s="41" t="n">
+        <v>542.5072518919166</v>
+      </c>
+      <c r="N11" s="101" t="n">
+        <v>-467.7399999999998</v>
+      </c>
+      <c r="O11" s="101" t="n">
+        <v>-268.1896804466178</v>
+      </c>
+      <c r="P11" s="101" t="n">
+        <v>-235.4851296062334</v>
+      </c>
+      <c r="Q11" s="101" t="n">
+        <v>-200.7507794610883</v>
+      </c>
+      <c r="R11" s="101" t="n">
+        <v>-163.8703729568169</v>
+      </c>
+      <c r="S11" s="101" t="n">
+        <v>-124.7213499068512</v>
       </c>
     </row>
     <row r="12">
@@ -3397,37 +3130,29 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B12" s="26">
-        <f>B10-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="26">
-        <f>C10-C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>D10-D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
-        <f>E10-E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>F10-F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>G10-G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="26">
-        <f>H10-H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
-        <f>I10-I11</f>
-        <v/>
+      <c r="B12" s="26" t="n">
+        <v>984.9500000000007</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>985.8300000000003</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>1391.129999999998</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>1391.326062337152</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>1480.060203128183</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>1562.595461845554</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>1638.723529632292</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>1708.101360099694</v>
       </c>
     </row>
     <row r="13">
@@ -3445,25 +3170,20 @@
       <c r="D13" s="41" t="n">
         <v>98.53</v>
       </c>
-      <c r="E13" s="41">
-        <f>D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="41">
-        <f>E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="41">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="41">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="41">
-        <f>H13</f>
-        <v/>
+      <c r="E13" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="I13" s="41" t="n">
+        <v>98.53</v>
       </c>
       <c r="L13" s="24" t="n">
         <v>2015</v>
@@ -3506,37 +3226,29 @@
           <t>PBT</t>
         </is>
       </c>
-      <c r="B14" s="100">
-        <f>B12-B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="100">
-        <f>C12-C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="100">
-        <f>D12-D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="100">
-        <f>E12-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="100">
-        <f>F12-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="100">
-        <f>G12-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="100">
-        <f>H12-H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="100">
-        <f>I12-I13</f>
-        <v/>
+      <c r="B14" s="100" t="n">
+        <v>920.3100000000007</v>
+      </c>
+      <c r="C14" s="100" t="n">
+        <v>907.1600000000003</v>
+      </c>
+      <c r="D14" s="100" t="n">
+        <v>1292.599999999998</v>
+      </c>
+      <c r="E14" s="100" t="n">
+        <v>1292.796062337152</v>
+      </c>
+      <c r="F14" s="100" t="n">
+        <v>1381.530203128183</v>
+      </c>
+      <c r="G14" s="100" t="n">
+        <v>1464.065461845554</v>
+      </c>
+      <c r="H14" s="100" t="n">
+        <v>1540.193529632292</v>
+      </c>
+      <c r="I14" s="100" t="n">
+        <v>1609.571360099694</v>
       </c>
       <c r="K14" s="44" t="inlineStr">
         <is>
@@ -3559,25 +3271,20 @@
       <c r="D15" s="41" t="n">
         <v>385.55</v>
       </c>
-      <c r="E15" s="41">
-        <f>E14*E16</f>
-        <v/>
-      </c>
-      <c r="F15" s="41">
-        <f>F14*F16</f>
-        <v/>
-      </c>
-      <c r="G15" s="41">
-        <f>G14*G16</f>
-        <v/>
-      </c>
-      <c r="H15" s="41">
-        <f>H14*H16</f>
-        <v/>
-      </c>
-      <c r="I15" s="41">
-        <f>I14*I16</f>
-        <v/>
+      <c r="E15" s="41" t="n">
+        <v>354.4750031481766</v>
+      </c>
+      <c r="F15" s="41" t="n">
+        <v>378.805240339175</v>
+      </c>
+      <c r="G15" s="41" t="n">
+        <v>401.4357904669225</v>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>422.3095368021208</v>
+      </c>
+      <c r="I15" s="41" t="n">
+        <v>441.3324185928392</v>
       </c>
       <c r="K15" s="44" t="inlineStr">
         <is>
@@ -3587,25 +3294,20 @@
       <c r="L15" s="98" t="n"/>
       <c r="M15" s="98" t="n"/>
       <c r="N15" s="98" t="n"/>
-      <c r="O15" s="98">
-        <f>E17</f>
-        <v/>
-      </c>
-      <c r="P15" s="98">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="Q15" s="98">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="R15" s="98">
-        <f>H17</f>
-        <v/>
-      </c>
-      <c r="S15" s="98">
-        <f>I17</f>
-        <v/>
+      <c r="O15" s="98" t="n">
+        <v>938.321059188975</v>
+      </c>
+      <c r="P15" s="98" t="n">
+        <v>1002.724962789008</v>
+      </c>
+      <c r="Q15" s="98" t="n">
+        <v>1062.629671378631</v>
+      </c>
+      <c r="R15" s="98" t="n">
+        <v>1117.883992830172</v>
+      </c>
+      <c r="S15" s="98" t="n">
+        <v>1168.238941506855</v>
       </c>
     </row>
     <row r="16">
@@ -3614,37 +3316,29 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B16" s="57">
-        <f>B15/B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="57">
-        <f>C15/C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="57">
-        <f>D15/D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="57">
-        <f>AVERAGE($C$16:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="57">
-        <f>AVERAGE($C$16:$D$16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="57">
-        <f>AVERAGE($C$16:$D$16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="57">
-        <f>AVERAGE($C$16:$D$16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="57">
-        <f>AVERAGE($C$16:$D$16)</f>
-        <v/>
+      <c r="B16" s="57" t="n">
+        <v>0.2064304419163107</v>
+      </c>
+      <c r="C16" s="57" t="n">
+        <v>0.2501102341373075</v>
+      </c>
+      <c r="D16" s="57" t="n">
+        <v>0.2982747949868486</v>
+      </c>
+      <c r="E16" s="57" t="n">
+        <v>0.274192514562078</v>
+      </c>
+      <c r="F16" s="57" t="n">
+        <v>0.274192514562078</v>
+      </c>
+      <c r="G16" s="57" t="n">
+        <v>0.274192514562078</v>
+      </c>
+      <c r="H16" s="57" t="n">
+        <v>0.274192514562078</v>
+      </c>
+      <c r="I16" s="57" t="n">
+        <v>0.274192514562078</v>
       </c>
       <c r="K16" s="44" t="inlineStr">
         <is>
@@ -3653,25 +3347,20 @@
       </c>
       <c r="M16" s="41" t="n"/>
       <c r="N16" s="41" t="n"/>
-      <c r="O16" s="41">
-        <f>E11</f>
-        <v/>
-      </c>
-      <c r="P16" s="41">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="Q16" s="41">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="R16" s="41">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="S16" s="41">
-        <f>I11</f>
-        <v/>
+      <c r="O16" s="41" t="n">
+        <v>582.6373910172789</v>
+      </c>
+      <c r="P16" s="41" t="n">
+        <v>566.0919764667541</v>
+      </c>
+      <c r="Q16" s="41" t="n">
+        <v>554.0982951837184</v>
+      </c>
+      <c r="R16" s="41" t="n">
+        <v>546.3229136890859</v>
+      </c>
+      <c r="S16" s="41" t="n">
+        <v>542.5072518919166</v>
       </c>
     </row>
     <row r="17">
@@ -3680,37 +3369,29 @@
           <t>PAT</t>
         </is>
       </c>
-      <c r="B17" s="98">
-        <f>B14-B15</f>
-        <v/>
-      </c>
-      <c r="C17" s="98">
-        <f>C14-C15</f>
-        <v/>
-      </c>
-      <c r="D17" s="98">
-        <f>D14-D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="98">
-        <f>E14-E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="98">
-        <f>F14-F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="98">
-        <f>G14-G15</f>
-        <v/>
-      </c>
-      <c r="H17" s="98">
-        <f>H14-H15</f>
-        <v/>
-      </c>
-      <c r="I17" s="98">
-        <f>I14-I15</f>
-        <v/>
+      <c r="B17" s="98" t="n">
+        <v>730.3300000000007</v>
+      </c>
+      <c r="C17" s="98" t="n">
+        <v>680.2700000000003</v>
+      </c>
+      <c r="D17" s="98" t="n">
+        <v>907.0499999999984</v>
+      </c>
+      <c r="E17" s="98" t="n">
+        <v>938.321059188975</v>
+      </c>
+      <c r="F17" s="98" t="n">
+        <v>1002.724962789008</v>
+      </c>
+      <c r="G17" s="98" t="n">
+        <v>1062.629671378631</v>
+      </c>
+      <c r="H17" s="98" t="n">
+        <v>1117.883992830172</v>
+      </c>
+      <c r="I17" s="98" t="n">
+        <v>1168.238941506855</v>
       </c>
       <c r="K17" s="44" t="inlineStr">
         <is>
@@ -3720,25 +3401,20 @@
       <c r="L17" s="41" t="n"/>
       <c r="M17" s="41" t="n"/>
       <c r="N17" s="41" t="n"/>
-      <c r="O17" s="41">
-        <f>E13</f>
-        <v/>
-      </c>
-      <c r="P17" s="41">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="Q17" s="41">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="R17" s="41">
-        <f>H13</f>
-        <v/>
-      </c>
-      <c r="S17" s="41">
-        <f>I13</f>
-        <v/>
+      <c r="O17" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="P17" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="Q17" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="R17" s="41" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="S17" s="41" t="n">
+        <v>98.53</v>
       </c>
     </row>
     <row r="18">
@@ -3755,25 +3431,20 @@
           <t>Change in inventory</t>
         </is>
       </c>
-      <c r="O18" s="41">
-        <f>'Balance Sheet'!D18-'Balance Sheet'!E18</f>
-        <v/>
-      </c>
-      <c r="P18" s="41">
-        <f>'Balance Sheet'!E18-'Balance Sheet'!F18</f>
-        <v/>
-      </c>
-      <c r="Q18" s="41">
-        <f>'Balance Sheet'!F18-'Balance Sheet'!G18</f>
-        <v/>
-      </c>
-      <c r="R18" s="41">
-        <f>'Balance Sheet'!G18-'Balance Sheet'!H18</f>
-        <v/>
-      </c>
-      <c r="S18" s="41">
-        <f>'Balance Sheet'!H18-'Balance Sheet'!I18</f>
-        <v/>
+      <c r="O18" s="41" t="n">
+        <v>-209.9123032094292</v>
+      </c>
+      <c r="P18" s="41" t="n">
+        <v>-135.3460361485713</v>
+      </c>
+      <c r="Q18" s="41" t="n">
+        <v>-145.4890405398157</v>
+      </c>
+      <c r="R18" s="41" t="n">
+        <v>-156.3402368565332</v>
+      </c>
+      <c r="S18" s="41" t="n">
+        <v>-167.946699609131</v>
       </c>
     </row>
     <row r="19">
@@ -3791,50 +3462,40 @@
       <c r="D19" s="41" t="n">
         <v>319.24</v>
       </c>
-      <c r="E19" s="98">
-        <f>E17*E21</f>
-        <v/>
-      </c>
-      <c r="F19" s="98">
-        <f>F17*F21</f>
-        <v/>
-      </c>
-      <c r="G19" s="98">
-        <f>G17*G21</f>
-        <v/>
-      </c>
-      <c r="H19" s="98">
-        <f>H17*H21</f>
-        <v/>
-      </c>
-      <c r="I19" s="98">
-        <f>I17*I21</f>
-        <v/>
+      <c r="E19" s="98" t="n">
+        <v>330.2459786511096</v>
+      </c>
+      <c r="F19" s="98" t="n">
+        <v>352.9131989645153</v>
+      </c>
+      <c r="G19" s="98" t="n">
+        <v>373.9969089806679</v>
+      </c>
+      <c r="H19" s="98" t="n">
+        <v>393.4438960047458</v>
+      </c>
+      <c r="I19" s="98" t="n">
+        <v>411.1665285118231</v>
       </c>
       <c r="K19" s="44" t="inlineStr">
         <is>
           <t>Change in receivables</t>
         </is>
       </c>
-      <c r="O19" s="41">
-        <f>'Balance Sheet'!D21-'Balance Sheet'!E21</f>
-        <v/>
-      </c>
-      <c r="P19" s="41">
-        <f>'Balance Sheet'!E21-'Balance Sheet'!F21</f>
-        <v/>
-      </c>
-      <c r="Q19" s="41">
-        <f>'Balance Sheet'!F21-'Balance Sheet'!G21</f>
-        <v/>
-      </c>
-      <c r="R19" s="41">
-        <f>'Balance Sheet'!G21-'Balance Sheet'!H21</f>
-        <v/>
-      </c>
-      <c r="S19" s="41">
-        <f>'Balance Sheet'!H21-'Balance Sheet'!I21</f>
-        <v/>
+      <c r="O19" s="41" t="n">
+        <v>-38.96189705790357</v>
+      </c>
+      <c r="P19" s="41" t="n">
+        <v>-53.52260699884096</v>
+      </c>
+      <c r="Q19" s="41" t="n">
+        <v>-57.11253795608002</v>
+      </c>
+      <c r="R19" s="41" t="n">
+        <v>-60.92765549154637</v>
+      </c>
+      <c r="S19" s="41" t="n">
+        <v>-64.9815034356692</v>
       </c>
     </row>
     <row r="20">
@@ -3843,62 +3504,49 @@
           <t>PAT transferred to BS</t>
         </is>
       </c>
-      <c r="B20" s="98">
-        <f>B17-B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="98">
-        <f>C17-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="98">
-        <f>D17-D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="98">
-        <f>E17-E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="98">
-        <f>F17-F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="98">
-        <f>G17-G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="98">
-        <f>H17-H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="98">
-        <f>I17-I19</f>
-        <v/>
+      <c r="B20" s="98" t="n">
+        <v>168.6600000000008</v>
+      </c>
+      <c r="C20" s="98" t="n">
+        <v>361.0600000000003</v>
+      </c>
+      <c r="D20" s="98" t="n">
+        <v>587.8099999999984</v>
+      </c>
+      <c r="E20" s="98" t="n">
+        <v>608.0750805378655</v>
+      </c>
+      <c r="F20" s="98" t="n">
+        <v>649.811763824493</v>
+      </c>
+      <c r="G20" s="98" t="n">
+        <v>688.6327623979632</v>
+      </c>
+      <c r="H20" s="98" t="n">
+        <v>724.4400968254261</v>
+      </c>
+      <c r="I20" s="98" t="n">
+        <v>757.072412995032</v>
       </c>
       <c r="K20" s="44" t="inlineStr">
         <is>
           <t>Change in payables</t>
         </is>
       </c>
-      <c r="O20" s="41">
-        <f>'Balance Sheet'!E44-'Balance Sheet'!D44</f>
-        <v/>
-      </c>
-      <c r="P20" s="41">
-        <f>'Balance Sheet'!F44-'Balance Sheet'!E44</f>
-        <v/>
-      </c>
-      <c r="Q20" s="41">
-        <f>'Balance Sheet'!G44-'Balance Sheet'!F44</f>
-        <v/>
-      </c>
-      <c r="R20" s="41">
-        <f>'Balance Sheet'!H44-'Balance Sheet'!G44</f>
-        <v/>
-      </c>
-      <c r="S20" s="41">
-        <f>'Balance Sheet'!I44-'Balance Sheet'!H44</f>
-        <v/>
+      <c r="O20" s="41" t="n">
+        <v>49.31388071395008</v>
+      </c>
+      <c r="P20" s="41" t="n">
+        <v>156.164092307029</v>
+      </c>
+      <c r="Q20" s="41" t="n">
+        <v>167.8672283507481</v>
+      </c>
+      <c r="R20" s="41" t="n">
+        <v>180.3874858438116</v>
+      </c>
+      <c r="S20" s="41" t="n">
+        <v>193.7791799948332</v>
       </c>
     </row>
     <row r="21">
@@ -3907,61 +3555,48 @@
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="B21" s="28">
-        <f>B19/B17</f>
-        <v/>
-      </c>
-      <c r="C21" s="28">
-        <f>C19/C17</f>
-        <v/>
-      </c>
-      <c r="D21" s="28">
-        <f>D19/D17</f>
-        <v/>
-      </c>
-      <c r="E21" s="28">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="F21" s="28">
-        <f>E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="28">
-        <f>F21</f>
-        <v/>
-      </c>
-      <c r="H21" s="28">
-        <f>G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="28">
-        <f>H21</f>
-        <v/>
+      <c r="B21" s="28" t="n">
+        <v>0.7690633001519853</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>0.4692401546444792</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>0.3519541370376502</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>0.3519541370376502</v>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>0.3519541370376502</v>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>0.3519541370376502</v>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>0.3519541370376502</v>
+      </c>
+      <c r="I21" s="28" t="n">
+        <v>0.3519541370376502</v>
       </c>
       <c r="K21" s="44" t="n"/>
       <c r="L21" s="98" t="n"/>
       <c r="M21" s="98" t="n"/>
       <c r="N21" s="98" t="n"/>
-      <c r="O21" s="98">
-        <f>SUM(O15:O20)</f>
-        <v/>
-      </c>
-      <c r="P21" s="98">
-        <f>SUM(P15:P20)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="98">
-        <f>SUM(Q15:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="98">
-        <f>SUM(R15:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="98">
-        <f>SUM(S15:S20)</f>
-        <v/>
+      <c r="O21" s="98" t="n">
+        <v>1419.928130652871</v>
+      </c>
+      <c r="P21" s="98" t="n">
+        <v>1634.642388415379</v>
+      </c>
+      <c r="Q21" s="98" t="n">
+        <v>1680.523616417202</v>
+      </c>
+      <c r="R21" s="98" t="n">
+        <v>1725.85650001499</v>
+      </c>
+      <c r="S21" s="98" t="n">
+        <v>1770.127170348805</v>
       </c>
     </row>
     <row r="22">
@@ -3978,48 +3613,38 @@
         </is>
       </c>
       <c r="N23" s="41" t="n"/>
-      <c r="O23" s="41">
-        <f>-'Asset schedule'!P2</f>
-        <v/>
-      </c>
-      <c r="P23" s="41">
-        <f>-'Asset schedule'!Q2</f>
-        <v/>
-      </c>
-      <c r="Q23" s="41">
-        <f>-'Asset schedule'!R2</f>
-        <v/>
-      </c>
-      <c r="R23" s="41">
-        <f>-'Asset schedule'!S2</f>
-        <v/>
-      </c>
-      <c r="S23" s="41">
-        <f>-'Asset schedule'!T2</f>
-        <v/>
+      <c r="O23" s="41" t="n">
+        <v>-406.8404430379748</v>
+      </c>
+      <c r="P23" s="41" t="n">
+        <v>-437.730180379747</v>
+      </c>
+      <c r="Q23" s="41" t="n">
+        <v>-470.6917903481014</v>
+      </c>
+      <c r="R23" s="41" t="n">
+        <v>-505.8552358623419</v>
+      </c>
+      <c r="S23" s="41" t="n">
+        <v>-543.3582964521364</v>
       </c>
     </row>
     <row r="24">
       <c r="N24" s="41" t="n"/>
-      <c r="O24" s="41">
-        <f>SUM(O23)</f>
-        <v/>
-      </c>
-      <c r="P24" s="41">
-        <f>SUM(P23)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="41">
-        <f>SUM(Q23)</f>
-        <v/>
-      </c>
-      <c r="R24" s="41">
-        <f>SUM(R23)</f>
-        <v/>
-      </c>
-      <c r="S24" s="41">
-        <f>SUM(S23)</f>
-        <v/>
+      <c r="O24" s="41" t="n">
+        <v>-406.8404430379748</v>
+      </c>
+      <c r="P24" s="41" t="n">
+        <v>-437.730180379747</v>
+      </c>
+      <c r="Q24" s="41" t="n">
+        <v>-470.6917903481014</v>
+      </c>
+      <c r="R24" s="41" t="n">
+        <v>-505.8552358623419</v>
+      </c>
+      <c r="S24" s="41" t="n">
+        <v>-543.3582964521364</v>
       </c>
     </row>
     <row r="25">
@@ -4082,25 +3707,20 @@
       <c r="L28" s="41" t="n"/>
       <c r="M28" s="41" t="n"/>
       <c r="N28" s="41" t="n"/>
-      <c r="O28" s="41">
-        <f>-E19</f>
-        <v/>
-      </c>
-      <c r="P28" s="41">
-        <f>-F19</f>
-        <v/>
-      </c>
-      <c r="Q28" s="41">
-        <f>-G19</f>
-        <v/>
-      </c>
-      <c r="R28" s="41">
-        <f>-H19</f>
-        <v/>
-      </c>
-      <c r="S28" s="41">
-        <f>-I19</f>
-        <v/>
+      <c r="O28" s="41" t="n">
+        <v>-330.2459786511096</v>
+      </c>
+      <c r="P28" s="41" t="n">
+        <v>-352.9131989645153</v>
+      </c>
+      <c r="Q28" s="41" t="n">
+        <v>-373.9969089806679</v>
+      </c>
+      <c r="R28" s="41" t="n">
+        <v>-393.4438960047458</v>
+      </c>
+      <c r="S28" s="41" t="n">
+        <v>-411.1665285118231</v>
       </c>
     </row>
     <row r="29">
@@ -4112,50 +3732,40 @@
       <c r="L29" s="41" t="n"/>
       <c r="M29" s="41" t="n"/>
       <c r="N29" s="41" t="n"/>
-      <c r="O29" s="41">
-        <f>-E13</f>
-        <v/>
-      </c>
-      <c r="P29" s="41">
-        <f>-F13</f>
-        <v/>
-      </c>
-      <c r="Q29" s="41">
-        <f>-G13</f>
-        <v/>
-      </c>
-      <c r="R29" s="41">
-        <f>-H13</f>
-        <v/>
-      </c>
-      <c r="S29" s="41">
-        <f>-I13</f>
-        <v/>
+      <c r="O29" s="41" t="n">
+        <v>-98.53</v>
+      </c>
+      <c r="P29" s="41" t="n">
+        <v>-98.53</v>
+      </c>
+      <c r="Q29" s="41" t="n">
+        <v>-98.53</v>
+      </c>
+      <c r="R29" s="41" t="n">
+        <v>-98.53</v>
+      </c>
+      <c r="S29" s="41" t="n">
+        <v>-98.53</v>
       </c>
     </row>
     <row r="30">
       <c r="L30" s="41" t="n"/>
       <c r="M30" s="41" t="n"/>
       <c r="N30" s="41" t="n"/>
-      <c r="O30" s="41">
-        <f>SUM(O26:O29)</f>
-        <v/>
-      </c>
-      <c r="P30" s="41">
-        <f>SUM(P26:P29)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="41">
-        <f>SUM(Q26:Q29)</f>
-        <v/>
-      </c>
-      <c r="R30" s="41">
-        <f>SUM(R26:R29)</f>
-        <v/>
-      </c>
-      <c r="S30" s="41">
-        <f>SUM(S26:S29)</f>
-        <v/>
+      <c r="O30" s="41" t="n">
+        <v>-428.7759786511095</v>
+      </c>
+      <c r="P30" s="41" t="n">
+        <v>-451.4431989645153</v>
+      </c>
+      <c r="Q30" s="41" t="n">
+        <v>-472.5269089806679</v>
+      </c>
+      <c r="R30" s="41" t="n">
+        <v>-491.9738960047458</v>
+      </c>
+      <c r="S30" s="41" t="n">
+        <v>-509.6965285118231</v>
       </c>
     </row>
     <row r="32">
@@ -4167,25 +3777,20 @@
       <c r="N32" t="n">
         <v>1810</v>
       </c>
-      <c r="O32" s="41">
-        <f>N34</f>
-        <v/>
-      </c>
-      <c r="P32" s="41">
-        <f>O34</f>
-        <v/>
-      </c>
-      <c r="Q32" s="41">
-        <f>P34</f>
-        <v/>
-      </c>
-      <c r="R32" s="41">
-        <f>Q34</f>
-        <v/>
-      </c>
-      <c r="S32" s="41">
-        <f>R34</f>
-        <v/>
+      <c r="O32" s="41" t="n">
+        <v>2559.11</v>
+      </c>
+      <c r="P32" s="41" t="n">
+        <v>3143.421708963787</v>
+      </c>
+      <c r="Q32" s="41" t="n">
+        <v>3888.890718034904</v>
+      </c>
+      <c r="R32" s="41" t="n">
+        <v>4626.195635123337</v>
+      </c>
+      <c r="S32" s="41" t="n">
+        <v>5354.223003271239</v>
       </c>
     </row>
     <row r="33">
@@ -4197,25 +3802,20 @@
       <c r="N33" s="98" t="n">
         <v>749.11</v>
       </c>
-      <c r="O33" s="98">
-        <f>O21+O24+O30</f>
-        <v/>
-      </c>
-      <c r="P33" s="98">
-        <f>P21+P24+P30</f>
-        <v/>
-      </c>
-      <c r="Q33" s="98">
-        <f>Q21+Q24+Q30</f>
-        <v/>
-      </c>
-      <c r="R33" s="98">
-        <f>R21+R24+R30</f>
-        <v/>
-      </c>
-      <c r="S33" s="98">
-        <f>S21+S24+S30</f>
-        <v/>
+      <c r="O33" s="98" t="n">
+        <v>584.3117089637869</v>
+      </c>
+      <c r="P33" s="98" t="n">
+        <v>745.4690090711168</v>
+      </c>
+      <c r="Q33" s="98" t="n">
+        <v>737.3049170884326</v>
+      </c>
+      <c r="R33" s="98" t="n">
+        <v>728.0273681479019</v>
+      </c>
+      <c r="S33" s="98" t="n">
+        <v>717.072345384845</v>
       </c>
     </row>
     <row r="34">
@@ -4224,29 +3824,23 @@
           <t>Closing bal</t>
         </is>
       </c>
-      <c r="N34" s="41">
-        <f>N32+N33</f>
-        <v/>
-      </c>
-      <c r="O34" s="41">
-        <f>O32+O33</f>
-        <v/>
-      </c>
-      <c r="P34" s="41">
-        <f>P32+P33</f>
-        <v/>
-      </c>
-      <c r="Q34" s="41">
-        <f>Q32+Q33</f>
-        <v/>
-      </c>
-      <c r="R34" s="41">
-        <f>R32+R33</f>
-        <v/>
-      </c>
-      <c r="S34" s="41">
-        <f>S32+S33</f>
-        <v/>
+      <c r="N34" s="41" t="n">
+        <v>2559.11</v>
+      </c>
+      <c r="O34" s="41" t="n">
+        <v>3143.421708963787</v>
+      </c>
+      <c r="P34" s="41" t="n">
+        <v>3888.890718034904</v>
+      </c>
+      <c r="Q34" s="41" t="n">
+        <v>4626.195635123337</v>
+      </c>
+      <c r="R34" s="41" t="n">
+        <v>5354.223003271239</v>
+      </c>
+      <c r="S34" s="41" t="n">
+        <v>6071.295348656084</v>
       </c>
     </row>
   </sheetData>
@@ -4347,54 +3941,43 @@
       <c r="D2" t="n">
         <v>130.61</v>
       </c>
-      <c r="E2">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="I2">
-        <f>H6</f>
-        <v/>
+      <c r="E2" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="F2" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="G2" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="H2" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="I2" t="n">
+        <v>130.61</v>
       </c>
       <c r="L2" s="44" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="O2">
-        <f>SUM(O5:O15)</f>
-        <v/>
-      </c>
-      <c r="P2" s="102">
-        <f>'Financial Statements'!E2*'Asset schedule'!P3</f>
-        <v/>
-      </c>
-      <c r="Q2" s="102">
-        <f>'Financial Statements'!F2*'Asset schedule'!Q3</f>
-        <v/>
-      </c>
-      <c r="R2" s="102">
-        <f>'Financial Statements'!G2*'Asset schedule'!R3</f>
-        <v/>
-      </c>
-      <c r="S2" s="102">
-        <f>'Financial Statements'!H2*'Asset schedule'!S3</f>
-        <v/>
-      </c>
-      <c r="T2" s="102">
-        <f>'Financial Statements'!I2*'Asset schedule'!T3</f>
-        <v/>
+      <c r="O2" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="P2" s="102" t="n">
+        <v>406.8404430379748</v>
+      </c>
+      <c r="Q2" s="102" t="n">
+        <v>437.730180379747</v>
+      </c>
+      <c r="R2" s="102" t="n">
+        <v>470.6917903481014</v>
+      </c>
+      <c r="S2" s="102" t="n">
+        <v>505.8552358623419</v>
+      </c>
+      <c r="T2" s="102" t="n">
+        <v>543.3582964521364</v>
       </c>
     </row>
     <row r="3">
@@ -4406,54 +3989,43 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A1,$L$4:$L$15,0),MATCH(E1,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F3" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A1,$L$4:$L$15,0),MATCH(F1,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G3" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A1,$L$4:$L$15,0),MATCH(G1,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H3" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A1,$L$4:$L$15,0),MATCH(H1,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I3" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A1,$L$4:$L$15,0),MATCH(I1,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E3" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="102" t="n">
+        <v>0</v>
       </c>
       <c r="L3" s="44" t="inlineStr">
         <is>
           <t>Capex as % of revenue</t>
         </is>
       </c>
-      <c r="O3" s="103">
-        <f>O2/'Financial Statements'!D2</f>
-        <v/>
-      </c>
-      <c r="P3" s="103">
-        <f>O3</f>
-        <v/>
-      </c>
-      <c r="Q3" s="103">
-        <f>P3</f>
-        <v/>
-      </c>
-      <c r="R3" s="103">
-        <f>Q3</f>
-        <v/>
-      </c>
-      <c r="S3" s="103">
-        <f>R3</f>
-        <v/>
-      </c>
-      <c r="T3" s="103">
-        <f>S3</f>
-        <v/>
+      <c r="O3" s="103" t="n">
+        <v>0.02817294115366666</v>
+      </c>
+      <c r="P3" s="103" t="n">
+        <v>0.02817294115366666</v>
+      </c>
+      <c r="Q3" s="103" t="n">
+        <v>0.02817294115366666</v>
+      </c>
+      <c r="R3" s="103" t="n">
+        <v>0.02817294115366666</v>
+      </c>
+      <c r="S3" s="103" t="n">
+        <v>0.02817294115366666</v>
+      </c>
+      <c r="T3" s="103" t="n">
+        <v>0.02817294115366666</v>
       </c>
     </row>
     <row r="4">
@@ -4518,58 +4090,46 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="41">
-        <f>E2*$B7</f>
-        <v/>
-      </c>
-      <c r="F5" s="41">
-        <f>F2*$B$7</f>
-        <v/>
-      </c>
-      <c r="G5" s="41">
-        <f>G2*$B$7</f>
-        <v/>
-      </c>
-      <c r="H5" s="41">
-        <f>H2*$B$7</f>
-        <v/>
-      </c>
-      <c r="I5" s="41">
-        <f>I2*$B$7</f>
-        <v/>
+      <c r="E5" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="36" t="inlineStr">
         <is>
           <t>Freehold Non Mining Land</t>
         </is>
       </c>
-      <c r="N5" s="28">
-        <f>O5/$O$16</f>
-        <v/>
-      </c>
-      <c r="O5">
-        <f>D3</f>
-        <v/>
-      </c>
-      <c r="P5">
-        <f>P$2*$N5</f>
-        <v/>
-      </c>
-      <c r="Q5">
-        <f>Q$2*$N5</f>
-        <v/>
-      </c>
-      <c r="R5">
-        <f>R$2*$N5</f>
-        <v/>
-      </c>
-      <c r="S5">
-        <f>S$2*$N5</f>
-        <v/>
-      </c>
-      <c r="T5">
-        <f>T$2*$N5</f>
-        <v/>
+      <c r="N5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4581,58 +4141,46 @@
       <c r="D6" t="n">
         <v>130.61</v>
       </c>
-      <c r="E6" s="47">
-        <f>E2+E3-E4-E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="47">
-        <f>F2+F3-F4-F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="47">
-        <f>G2+G3-G4-G5</f>
-        <v/>
-      </c>
-      <c r="H6" s="47">
-        <f>H2+H3-H4-H5</f>
-        <v/>
-      </c>
-      <c r="I6" s="47">
-        <f>I2+I3-I4-I5</f>
-        <v/>
+      <c r="E6" s="47" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="G6" s="47" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="I6" s="47" t="n">
+        <v>130.61</v>
       </c>
       <c r="L6" s="36" t="inlineStr">
         <is>
           <t>Freehold Mining Land</t>
         </is>
       </c>
-      <c r="N6" s="28">
-        <f>O6/$O$16</f>
-        <v/>
-      </c>
-      <c r="O6">
-        <f>D11</f>
-        <v/>
-      </c>
-      <c r="P6" s="47">
-        <f>P$2*$N6</f>
-        <v/>
-      </c>
-      <c r="Q6" s="47">
-        <f>Q$2*$N6</f>
-        <v/>
-      </c>
-      <c r="R6" s="47">
-        <f>R$2*$N6</f>
-        <v/>
-      </c>
-      <c r="S6" s="47">
-        <f>S$2*$N6</f>
-        <v/>
-      </c>
-      <c r="T6" s="47">
-        <f>T$2*$N6</f>
-        <v/>
+      <c r="N6" s="28" t="n">
+        <v>0.006456734585869277</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P6" s="47" t="n">
+        <v>2.626860759493671</v>
+      </c>
+      <c r="Q6" s="47" t="n">
+        <v>2.82630759493671</v>
+      </c>
+      <c r="R6" s="47" t="n">
+        <v>3.039131962025317</v>
+      </c>
+      <c r="S6" s="47" t="n">
+        <v>3.266172996835444</v>
+      </c>
+      <c r="T6" s="47" t="n">
+        <v>3.508320305221521</v>
       </c>
     </row>
     <row r="7">
@@ -4641,42 +4189,34 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B7" s="28">
-        <f>D5/(D2+D3-D4)</f>
-        <v/>
+      <c r="B7" s="28" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Leasehold Land</t>
         </is>
       </c>
-      <c r="N7" s="28">
-        <f>O7/$O$16</f>
-        <v/>
-      </c>
-      <c r="O7">
-        <f>D19</f>
-        <v/>
-      </c>
-      <c r="P7" s="47">
-        <f>P$2*$N7</f>
-        <v/>
-      </c>
-      <c r="Q7" s="47">
-        <f>Q$2*$N7</f>
-        <v/>
-      </c>
-      <c r="R7" s="47">
-        <f>R$2*$N7</f>
-        <v/>
-      </c>
-      <c r="S7" s="47">
-        <f>S$2*$N7</f>
-        <v/>
-      </c>
-      <c r="T7" s="47">
-        <f>T$2*$N7</f>
-        <v/>
+      <c r="N7" s="28" t="n">
+        <v>0.007594601746493781</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P7" s="47" t="n">
+        <v>3.089791139240507</v>
+      </c>
+      <c r="Q7" s="47" t="n">
+        <v>3.324386392405064</v>
+      </c>
+      <c r="R7" s="47" t="n">
+        <v>3.574716693037975</v>
+      </c>
+      <c r="S7" s="47" t="n">
+        <v>3.841769057753165</v>
+      </c>
+      <c r="T7" s="47" t="n">
+        <v>4.126589867207281</v>
       </c>
     </row>
     <row r="8">
@@ -4685,33 +4225,26 @@
           <t>Buildings</t>
         </is>
       </c>
-      <c r="N8" s="28">
-        <f>O8/$O$16</f>
-        <v/>
-      </c>
-      <c r="O8">
-        <f>D27</f>
-        <v/>
-      </c>
-      <c r="P8" s="47">
-        <f>P$2*$N8</f>
-        <v/>
-      </c>
-      <c r="Q8" s="47">
-        <f>Q$2*$N8</f>
-        <v/>
-      </c>
-      <c r="R8" s="47">
-        <f>R$2*$N8</f>
-        <v/>
-      </c>
-      <c r="S8" s="47">
-        <f>S$2*$N8</f>
-        <v/>
-      </c>
-      <c r="T8" s="47">
-        <f>T$2*$N8</f>
-        <v/>
+      <c r="N8" s="28" t="n">
+        <v>0.09465467054776396</v>
+      </c>
+      <c r="O8" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="P8" s="47" t="n">
+        <v>38.50934810126583</v>
+      </c>
+      <c r="Q8" s="47" t="n">
+        <v>41.43320601265824</v>
+      </c>
+      <c r="R8" s="47" t="n">
+        <v>44.55317634493672</v>
+      </c>
+      <c r="S8" s="47" t="n">
+        <v>47.8815606954114</v>
+      </c>
+      <c r="T8" s="47" t="n">
+        <v>51.43140054007123</v>
       </c>
     </row>
     <row r="9">
@@ -4759,33 +4292,26 @@
           <t>Plants &amp; Eq</t>
         </is>
       </c>
-      <c r="N9" s="28">
-        <f>O9/$O$16</f>
-        <v/>
-      </c>
-      <c r="O9">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="P9" s="47">
-        <f>P$2*$N9</f>
-        <v/>
-      </c>
-      <c r="Q9" s="47">
-        <f>Q$2*$N9</f>
-        <v/>
-      </c>
-      <c r="R9" s="47">
-        <f>R$2*$N9</f>
-        <v/>
-      </c>
-      <c r="S9" s="47">
-        <f>S$2*$N9</f>
-        <v/>
-      </c>
-      <c r="T9" s="47">
-        <f>T$2*$N9</f>
-        <v/>
+      <c r="N9" s="28" t="n">
+        <v>0.66806033342154</v>
+      </c>
+      <c r="O9" t="n">
+        <v>252.46</v>
+      </c>
+      <c r="P9" s="47" t="n">
+        <v>271.7939620253165</v>
+      </c>
+      <c r="Q9" s="47" t="n">
+        <v>292.4301702531646</v>
+      </c>
+      <c r="R9" s="47" t="n">
+        <v>314.4505143987342</v>
+      </c>
+      <c r="S9" s="47" t="n">
+        <v>337.9418175332279</v>
+      </c>
+      <c r="T9" s="47" t="n">
+        <v>362.9961246951742</v>
       </c>
     </row>
     <row r="10">
@@ -4797,58 +4323,46 @@
       <c r="D10" s="102" t="n">
         <v>303.09</v>
       </c>
-      <c r="E10">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="I10">
-        <f>H14</f>
-        <v/>
+      <c r="E10" t="n">
+        <v>304.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>306.6571001133368</v>
+      </c>
+      <c r="G10" t="n">
+        <v>309.2115575029657</v>
+      </c>
+      <c r="H10" t="n">
+        <v>311.9765747441525</v>
+      </c>
+      <c r="I10" t="n">
+        <v>314.9661818442124</v>
       </c>
       <c r="L10" s="36" t="inlineStr">
         <is>
           <t>Railway sidings</t>
         </is>
       </c>
-      <c r="N10" s="28">
-        <f>O10/$O$16</f>
-        <v/>
-      </c>
-      <c r="O10">
-        <f>D43</f>
-        <v/>
-      </c>
-      <c r="P10" s="47">
-        <f>P$2*$N10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="47">
-        <f>Q$2*$N10</f>
-        <v/>
-      </c>
-      <c r="R10" s="47">
-        <f>R$2*$N10</f>
-        <v/>
-      </c>
-      <c r="S10" s="47">
-        <f>S$2*$N10</f>
-        <v/>
-      </c>
-      <c r="T10" s="47">
-        <f>T$2*$N10</f>
-        <v/>
+      <c r="N10" s="28" t="n">
+        <v>0.1332098438740408</v>
+      </c>
+      <c r="O10" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="P10" s="47" t="n">
+        <v>54.19515189873419</v>
+      </c>
+      <c r="Q10" s="47" t="n">
+        <v>58.30996898734179</v>
+      </c>
+      <c r="R10" s="47" t="n">
+        <v>62.70077990506331</v>
+      </c>
+      <c r="S10" s="47" t="n">
+        <v>67.38489699208863</v>
+      </c>
+      <c r="T10" s="47" t="n">
+        <v>72.38067383805384</v>
       </c>
     </row>
     <row r="11">
@@ -4860,58 +4374,46 @@
       <c r="D11" t="n">
         <v>2.44</v>
       </c>
-      <c r="E11" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A9,$L$4:$L$15,0),MATCH(E9,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A9,$L$4:$L$15,0),MATCH(F9,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A9,$L$4:$L$15,0),MATCH(G9,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A9,$L$4:$L$15,0),MATCH(H9,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A9,$L$4:$L$15,0),MATCH(I9,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E11" s="102" t="n">
+        <v>2.626860759493671</v>
+      </c>
+      <c r="F11" s="102" t="n">
+        <v>2.82630759493671</v>
+      </c>
+      <c r="G11" s="102" t="n">
+        <v>3.039131962025317</v>
+      </c>
+      <c r="H11" s="102" t="n">
+        <v>3.266172996835444</v>
+      </c>
+      <c r="I11" s="102" t="n">
+        <v>3.508320305221521</v>
       </c>
       <c r="L11" s="36" t="inlineStr">
         <is>
           <t>Office Eq</t>
         </is>
       </c>
-      <c r="N11" s="28">
-        <f>O11/$O$16</f>
-        <v/>
-      </c>
-      <c r="O11">
-        <f>D51</f>
-        <v/>
-      </c>
-      <c r="P11" s="47">
-        <f>P$2*$N11</f>
-        <v/>
-      </c>
-      <c r="Q11" s="47">
-        <f>Q$2*$N11</f>
-        <v/>
-      </c>
-      <c r="R11" s="47">
-        <f>R$2*$N11</f>
-        <v/>
-      </c>
-      <c r="S11" s="47">
-        <f>S$2*$N11</f>
-        <v/>
-      </c>
-      <c r="T11" s="47">
-        <f>T$2*$N11</f>
-        <v/>
+      <c r="N11" s="28" t="n">
+        <v>0.0193172797036253</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="P11" s="47" t="n">
+        <v>7.859050632911393</v>
+      </c>
+      <c r="Q11" s="47" t="n">
+        <v>8.455756329113926</v>
+      </c>
+      <c r="R11" s="47" t="n">
+        <v>9.092484968354432</v>
+      </c>
+      <c r="S11" s="47" t="n">
+        <v>9.771747080696205</v>
+      </c>
+      <c r="T11" s="47" t="n">
+        <v>10.49620419185127</v>
       </c>
     </row>
     <row r="12">
@@ -4943,33 +4445,26 @@
           <t>Software</t>
         </is>
       </c>
-      <c r="N12" s="28">
-        <f>O12/$O$16</f>
-        <v/>
-      </c>
-      <c r="O12">
-        <f>D59</f>
-        <v/>
-      </c>
-      <c r="P12" s="47">
-        <f>P$2*$N12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="47">
-        <f>Q$2*$N12</f>
-        <v/>
-      </c>
-      <c r="R12" s="47">
-        <f>R$2*$N12</f>
-        <v/>
-      </c>
-      <c r="S12" s="47">
-        <f>S$2*$N12</f>
-        <v/>
-      </c>
-      <c r="T12" s="47">
-        <f>T$2*$N12</f>
-        <v/>
+      <c r="N12" s="28" t="n">
+        <v>0.0009261709446943635</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P12" s="47" t="n">
+        <v>0.3768037974683545</v>
+      </c>
+      <c r="Q12" s="47" t="n">
+        <v>0.4054129746835444</v>
+      </c>
+      <c r="R12" s="47" t="n">
+        <v>0.4359410601265823</v>
+      </c>
+      <c r="S12" s="47" t="n">
+        <v>0.4685084216772152</v>
+      </c>
+      <c r="T12" s="47" t="n">
+        <v>0.5032426667325952</v>
       </c>
     </row>
     <row r="13">
@@ -4981,58 +4476,46 @@
       <c r="D13" t="n">
         <v>0.27</v>
       </c>
-      <c r="E13" s="41">
-        <f>E10*$B15</f>
-        <v/>
-      </c>
-      <c r="F13" s="41">
-        <f>F10*$B15</f>
-        <v/>
-      </c>
-      <c r="G13" s="41">
-        <f>G10*$B15</f>
-        <v/>
-      </c>
-      <c r="H13" s="41">
-        <f>H10*$B15</f>
-        <v/>
-      </c>
-      <c r="I13" s="41">
-        <f>I10*$B15</f>
-        <v/>
+      <c r="E13" s="41" t="n">
+        <v>0.2697606461568769</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>0.2718502053078141</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>0.2741147208385618</v>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>0.2765658967755234</v>
+      </c>
+      <c r="I13" s="41" t="n">
+        <v>0.2792161706600694</v>
       </c>
       <c r="L13" s="36" t="inlineStr">
         <is>
           <t>Mining rights</t>
         </is>
       </c>
-      <c r="N13" s="28">
-        <f>O13/$O$16</f>
-        <v/>
-      </c>
-      <c r="O13">
-        <f>D67</f>
-        <v/>
-      </c>
-      <c r="P13" s="47">
-        <f>P$2*$N13</f>
-        <v/>
-      </c>
-      <c r="Q13" s="47">
-        <f>Q$2*$N13</f>
-        <v/>
-      </c>
-      <c r="R13" s="47">
-        <f>R$2*$N13</f>
-        <v/>
-      </c>
-      <c r="S13" s="47">
-        <f>S$2*$N13</f>
-        <v/>
-      </c>
-      <c r="T13" s="47">
-        <f>T$2*$N13</f>
-        <v/>
+      <c r="N13" s="28" t="n">
+        <v>0.04440328129134691</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="P13" s="47" t="n">
+        <v>18.06505063291139</v>
+      </c>
+      <c r="Q13" s="47" t="n">
+        <v>19.43665632911393</v>
+      </c>
+      <c r="R13" s="47" t="n">
+        <v>20.90025996835443</v>
+      </c>
+      <c r="S13" s="47" t="n">
+        <v>22.46163233069621</v>
+      </c>
+      <c r="T13" s="47" t="n">
+        <v>24.12689127935128</v>
       </c>
     </row>
     <row r="14">
@@ -5044,58 +4527,46 @@
       <c r="D14" t="n">
         <v>304.3</v>
       </c>
-      <c r="E14" s="47">
-        <f>E10+E11-E12-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="47">
-        <f>F10+F11-F12-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="47">
-        <f>G10+G11-G12-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="47">
-        <f>H10+H11-H12-H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="47">
-        <f>I10+I11-I12-I13</f>
-        <v/>
+      <c r="E14" s="47" t="n">
+        <v>306.6571001133368</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <v>309.2115575029657</v>
+      </c>
+      <c r="G14" s="47" t="n">
+        <v>311.9765747441525</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>314.9661818442124</v>
+      </c>
+      <c r="I14" s="47" t="n">
+        <v>318.1952859787738</v>
       </c>
       <c r="L14" s="36" t="inlineStr">
         <is>
           <t>Vehicles</t>
         </is>
       </c>
-      <c r="N14" s="28">
-        <f>O14/$O$16</f>
-        <v/>
-      </c>
-      <c r="O14">
-        <f>D75</f>
-        <v/>
-      </c>
-      <c r="P14" s="47">
-        <f>P$2*$N14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="47">
-        <f>Q$2*$N14</f>
-        <v/>
-      </c>
-      <c r="R14" s="47">
-        <f>R$2*$N14</f>
-        <v/>
-      </c>
-      <c r="S14" s="47">
-        <f>S$2*$N14</f>
-        <v/>
-      </c>
-      <c r="T14" s="47">
-        <f>T$2*$N14</f>
-        <v/>
+      <c r="N14" s="28" t="n">
+        <v>0.01854988092087854</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P14" s="47" t="n">
+        <v>7.546841772151899</v>
+      </c>
+      <c r="Q14" s="47" t="n">
+        <v>8.119842721518989</v>
+      </c>
+      <c r="R14" s="47" t="n">
+        <v>8.731276661392407</v>
+      </c>
+      <c r="S14" s="47" t="n">
+        <v>9.383554388449369</v>
+      </c>
+      <c r="T14" s="47" t="n">
+        <v>10.07923169655855</v>
       </c>
     </row>
     <row r="15">
@@ -5104,68 +4575,54 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B15" s="28">
-        <f>D13/(D10+D11-D12)</f>
-        <v/>
+      <c r="B15" s="28" t="n">
+        <v>0.0008864957152707096</v>
       </c>
       <c r="L15" s="36" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="N15" s="28">
-        <f>O15/$O$16</f>
-        <v/>
-      </c>
-      <c r="O15">
-        <f>D83</f>
-        <v/>
-      </c>
-      <c r="P15" s="47">
-        <f>P$2*$N15</f>
-        <v/>
-      </c>
-      <c r="Q15" s="47">
-        <f>Q$2*$N15</f>
-        <v/>
-      </c>
-      <c r="R15" s="47">
-        <f>R$2*$N15</f>
-        <v/>
-      </c>
-      <c r="S15" s="47">
-        <f>S$2*$N15</f>
-        <v/>
-      </c>
-      <c r="T15" s="47">
-        <f>T$2*$N15</f>
-        <v/>
+      <c r="N15" s="28" t="n">
+        <v>0.006827202963747022</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P15" s="47" t="n">
+        <v>2.777582278481013</v>
+      </c>
+      <c r="Q15" s="47" t="n">
+        <v>2.988472784810127</v>
+      </c>
+      <c r="R15" s="47" t="n">
+        <v>3.21350838607595</v>
+      </c>
+      <c r="S15" s="47" t="n">
+        <v>3.45357636550633</v>
+      </c>
+      <c r="T15" s="47" t="n">
+        <v>3.709617371914559</v>
       </c>
     </row>
     <row r="16">
-      <c r="O16">
-        <f>SUM(O5:O15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="102">
-        <f>SUM(P5:P15)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="102">
-        <f>SUM(Q5:Q15)</f>
-        <v/>
-      </c>
-      <c r="R16" s="102">
-        <f>SUM(R5:R15)</f>
-        <v/>
-      </c>
-      <c r="S16" s="102">
-        <f>SUM(S5:S15)</f>
-        <v/>
-      </c>
-      <c r="T16" s="102">
-        <f>SUM(T5:T15)</f>
-        <v/>
+      <c r="O16" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="P16" s="102" t="n">
+        <v>406.8404430379748</v>
+      </c>
+      <c r="Q16" s="102" t="n">
+        <v>437.730180379747</v>
+      </c>
+      <c r="R16" s="102" t="n">
+        <v>470.6917903481014</v>
+      </c>
+      <c r="S16" s="102" t="n">
+        <v>505.8552358623419</v>
+      </c>
+      <c r="T16" s="102" t="n">
+        <v>543.3582964521363</v>
       </c>
     </row>
     <row r="17">
@@ -5218,25 +4675,20 @@
       <c r="D18" t="n">
         <v>36.1</v>
       </c>
-      <c r="E18">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>E22</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="I18">
-        <f>H22</f>
-        <v/>
+      <c r="E18" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41.04646550413658</v>
+      </c>
+      <c r="G18" t="n">
+        <v>43.83367721326965</v>
+      </c>
+      <c r="H18" t="n">
+        <v>46.83474301129178</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50.06358625596415</v>
       </c>
     </row>
     <row r="19">
@@ -5248,25 +4700,20 @@
       <c r="D19" t="n">
         <v>2.87</v>
       </c>
-      <c r="E19" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A17,$L$4:$L$15,0),MATCH(E17,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F19" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A17,$L$4:$L$15,0),MATCH(F17,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G19" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A17,$L$4:$L$15,0),MATCH(G17,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H19" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A17,$L$4:$L$15,0),MATCH(H17,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I19" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A17,$L$4:$L$15,0),MATCH(I17,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E19" s="102" t="n">
+        <v>3.089791139240507</v>
+      </c>
+      <c r="F19" s="102" t="n">
+        <v>3.324386392405064</v>
+      </c>
+      <c r="G19" s="102" t="n">
+        <v>3.574716693037975</v>
+      </c>
+      <c r="H19" s="102" t="n">
+        <v>3.841769057753165</v>
+      </c>
+      <c r="I19" s="102" t="n">
+        <v>4.126589867207281</v>
       </c>
     </row>
     <row r="20">
@@ -5303,25 +4750,20 @@
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
-      <c r="E21" s="102">
-        <f>E18*$B23</f>
-        <v/>
-      </c>
-      <c r="F21" s="102">
-        <f>F18*$B23</f>
-        <v/>
-      </c>
-      <c r="G21" s="102">
-        <f>G18*$B23</f>
-        <v/>
-      </c>
-      <c r="H21" s="102">
-        <f>H18*$B23</f>
-        <v/>
-      </c>
-      <c r="I21" s="102">
-        <f>I18*$B23</f>
-        <v/>
+      <c r="E21" s="102" t="n">
+        <v>0.5033256351039261</v>
+      </c>
+      <c r="F21" s="102" t="n">
+        <v>0.5371746832719952</v>
+      </c>
+      <c r="G21" s="102" t="n">
+        <v>0.5736508950158461</v>
+      </c>
+      <c r="H21" s="102" t="n">
+        <v>0.6129258130808009</v>
+      </c>
+      <c r="I21" s="102" t="n">
+        <v>0.6551816523105393</v>
       </c>
     </row>
     <row r="22">
@@ -5333,25 +4775,20 @@
       <c r="D22" t="n">
         <v>38.46</v>
       </c>
-      <c r="E22" s="47">
-        <f>E18+E19-E20-E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="47">
-        <f>F18+F19-F20-F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="47">
-        <f>G18+G19-G20-G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="47">
-        <f>H18+H19-H20-H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="47">
-        <f>I18+I19-I20-I21</f>
-        <v/>
+      <c r="E22" s="47" t="n">
+        <v>41.04646550413658</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>43.83367721326965</v>
+      </c>
+      <c r="G22" s="47" t="n">
+        <v>46.83474301129178</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>50.06358625596415</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>53.53499447086089</v>
       </c>
     </row>
     <row r="23">
@@ -5360,9 +4797,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B23" s="28">
-        <f>D21/(D18+D19-D20)</f>
-        <v/>
+      <c r="B23" s="28" t="n">
+        <v>0.01308698999230177</v>
       </c>
     </row>
     <row r="25">
@@ -5415,25 +4851,20 @@
       <c r="D26" t="n">
         <v>1515.39</v>
       </c>
-      <c r="E26">
-        <f>D30</f>
-        <v/>
-      </c>
-      <c r="F26">
-        <f>E30</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>F30</f>
-        <v/>
-      </c>
-      <c r="H26">
-        <f>G30</f>
-        <v/>
-      </c>
-      <c r="I26">
-        <f>H30</f>
-        <v/>
+      <c r="E26" t="n">
+        <v>1472.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1436.901306966578</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1406.11076193844</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1379.987829135409</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1358.506311846563</v>
       </c>
     </row>
     <row r="27">
@@ -5445,25 +4876,20 @@
       <c r="D27" t="n">
         <v>35.77</v>
       </c>
-      <c r="E27" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A25,$L$4:$L$15,0),MATCH(E25,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F27" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A25,$L$4:$L$15,0),MATCH(F25,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G27" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A25,$L$4:$L$15,0),MATCH(G25,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H27" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A25,$L$4:$L$15,0),MATCH(H25,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I27" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A25,$L$4:$L$15,0),MATCH(I25,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E27" s="102" t="n">
+        <v>38.50934810126583</v>
+      </c>
+      <c r="F27" s="102" t="n">
+        <v>41.43320601265824</v>
+      </c>
+      <c r="G27" s="102" t="n">
+        <v>44.55317634493672</v>
+      </c>
+      <c r="H27" s="102" t="n">
+        <v>47.8815606954114</v>
+      </c>
+      <c r="I27" s="102" t="n">
+        <v>51.43140054007123</v>
       </c>
     </row>
     <row r="28">
@@ -5500,25 +4926,20 @@
       <c r="D29" t="n">
         <v>77.91</v>
       </c>
-      <c r="E29" s="102">
-        <f>E26*$B31</f>
-        <v/>
-      </c>
-      <c r="F29" s="102">
-        <f>F26*$B31</f>
-        <v/>
-      </c>
-      <c r="G29" s="102">
-        <f>G26*$B31</f>
-        <v/>
-      </c>
-      <c r="H29" s="102">
-        <f>H26*$B31</f>
-        <v/>
-      </c>
-      <c r="I29" s="102">
-        <f>I26*$B31</f>
-        <v/>
+      <c r="E29" s="102" t="n">
+        <v>74.00804113468772</v>
+      </c>
+      <c r="F29" s="102" t="n">
+        <v>72.2237510407967</v>
+      </c>
+      <c r="G29" s="102" t="n">
+        <v>70.67610914796735</v>
+      </c>
+      <c r="H29" s="102" t="n">
+        <v>69.3630779842582</v>
+      </c>
+      <c r="I29" s="102" t="n">
+        <v>68.28334081015574</v>
       </c>
     </row>
     <row r="30">
@@ -5530,25 +4951,20 @@
       <c r="D30" t="n">
         <v>1472.4</v>
       </c>
-      <c r="E30" s="47">
-        <f>E26+E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F30" s="47">
-        <f>F26+F27-F28-F29</f>
-        <v/>
-      </c>
-      <c r="G30" s="47">
-        <f>G26+G27-G28-G29</f>
-        <v/>
-      </c>
-      <c r="H30" s="47">
-        <f>H26+H27-H28-H29</f>
-        <v/>
-      </c>
-      <c r="I30" s="47">
-        <f>I26+I27-I28-I29</f>
-        <v/>
+      <c r="E30" s="47" t="n">
+        <v>1436.901306966578</v>
+      </c>
+      <c r="F30" s="47" t="n">
+        <v>1406.11076193844</v>
+      </c>
+      <c r="G30" s="47" t="n">
+        <v>1379.987829135409</v>
+      </c>
+      <c r="H30" s="47" t="n">
+        <v>1358.506311846563</v>
+      </c>
+      <c r="I30" s="47" t="n">
+        <v>1341.654371576478</v>
       </c>
     </row>
     <row r="31">
@@ -5557,9 +4973,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B31" s="28">
-        <f>D29/(D26+D27-D28)</f>
-        <v/>
+      <c r="B31" s="28" t="n">
+        <v>0.05026354328625898</v>
       </c>
     </row>
     <row r="33">
@@ -5612,25 +5027,20 @@
       <c r="D34" t="n">
         <v>5264.32</v>
       </c>
-      <c r="E34">
-        <f>D38</f>
-        <v/>
-      </c>
-      <c r="F34">
-        <f>E38</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>F38</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>G38</f>
-        <v/>
-      </c>
-      <c r="I34">
-        <f>H38</f>
-        <v/>
+      <c r="E34" t="n">
+        <v>4984.63</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4789.876427870993</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4633.987457821441</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4514.709606875374</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4430.087134880485</v>
       </c>
     </row>
     <row r="35">
@@ -5642,25 +5052,20 @@
       <c r="D35" t="n">
         <v>252.46</v>
       </c>
-      <c r="E35" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A33,$L$4:$L$15,0),MATCH(E33,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F35" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A33,$L$4:$L$15,0),MATCH(F33,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G35" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A33,$L$4:$L$15,0),MATCH(G33,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H35" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A33,$L$4:$L$15,0),MATCH(H33,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I35" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A33,$L$4:$L$15,0),MATCH(I33,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E35" s="102" t="n">
+        <v>271.7939620253165</v>
+      </c>
+      <c r="F35" s="102" t="n">
+        <v>292.4301702531646</v>
+      </c>
+      <c r="G35" s="102" t="n">
+        <v>314.4505143987342</v>
+      </c>
+      <c r="H35" s="102" t="n">
+        <v>337.9418175332279</v>
+      </c>
+      <c r="I35" s="102" t="n">
+        <v>362.9961246951742</v>
       </c>
     </row>
     <row r="36">
@@ -5697,25 +5102,20 @@
       <c r="D37" t="n">
         <v>514.24</v>
       </c>
-      <c r="E37" s="102">
-        <f>E34*$B39</f>
-        <v/>
-      </c>
-      <c r="F37" s="102">
-        <f>F34*$B39</f>
-        <v/>
-      </c>
-      <c r="G37" s="102">
-        <f>G34*$B39</f>
-        <v/>
-      </c>
-      <c r="H37" s="102">
-        <f>H34*$B39</f>
-        <v/>
-      </c>
-      <c r="I37" s="102">
-        <f>I34*$B39</f>
-        <v/>
+      <c r="E37" s="102" t="n">
+        <v>466.5475341543233</v>
+      </c>
+      <c r="F37" s="102" t="n">
+        <v>448.3191403027166</v>
+      </c>
+      <c r="G37" s="102" t="n">
+        <v>433.7283653448009</v>
+      </c>
+      <c r="H37" s="102" t="n">
+        <v>422.5642895281175</v>
+      </c>
+      <c r="I37" s="102" t="n">
+        <v>414.643861002177</v>
       </c>
     </row>
     <row r="38">
@@ -5727,25 +5127,20 @@
       <c r="D38" t="n">
         <v>4984.63</v>
       </c>
-      <c r="E38" s="47">
-        <f>E34+E35-E36-E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="47">
-        <f>F34+F35-F36-F37</f>
-        <v/>
-      </c>
-      <c r="G38" s="47">
-        <f>G34+G35-G36-G37</f>
-        <v/>
-      </c>
-      <c r="H38" s="47">
-        <f>H34+H35-H36-H37</f>
-        <v/>
-      </c>
-      <c r="I38" s="47">
-        <f>I34+I35-I36-I37</f>
-        <v/>
+      <c r="E38" s="47" t="n">
+        <v>4789.876427870993</v>
+      </c>
+      <c r="F38" s="47" t="n">
+        <v>4633.987457821441</v>
+      </c>
+      <c r="G38" s="47" t="n">
+        <v>4514.709606875374</v>
+      </c>
+      <c r="H38" s="47" t="n">
+        <v>4430.087134880485</v>
+      </c>
+      <c r="I38" s="47" t="n">
+        <v>4378.439398573482</v>
       </c>
     </row>
     <row r="39">
@@ -5754,9 +5149,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B39" s="28">
-        <f>D37/(D34+D35-D36)</f>
-        <v/>
+      <c r="B39" s="28" t="n">
+        <v>0.09359722469959121</v>
       </c>
     </row>
     <row r="41">
@@ -5809,25 +5203,20 @@
       <c r="D42" t="n">
         <v>181.92</v>
       </c>
-      <c r="E42">
-        <f>D46</f>
-        <v/>
-      </c>
-      <c r="F42">
-        <f>E46</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>F46</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>G46</f>
-        <v/>
-      </c>
-      <c r="I42">
-        <f>H46</f>
-        <v/>
+      <c r="E42" t="n">
+        <v>212.14</v>
+      </c>
+      <c r="F42" t="n">
+        <v>248.0073668950734</v>
+      </c>
+      <c r="G42" t="n">
+        <v>284.8907982196598</v>
+      </c>
+      <c r="H42" t="n">
+        <v>322.9785051573844</v>
+      </c>
+      <c r="I42" t="n">
+        <v>362.459750771476</v>
       </c>
     </row>
     <row r="43">
@@ -5839,25 +5228,20 @@
       <c r="D43" t="n">
         <v>50.34</v>
       </c>
-      <c r="E43" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A41,$L$4:$L$15,0),MATCH(E41,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F43" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A41,$L$4:$L$15,0),MATCH(F41,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G43" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A41,$L$4:$L$15,0),MATCH(G41,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H43" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A41,$L$4:$L$15,0),MATCH(H41,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I43" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A41,$L$4:$L$15,0),MATCH(I41,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E43" s="102" t="n">
+        <v>54.19515189873419</v>
+      </c>
+      <c r="F43" s="102" t="n">
+        <v>58.30996898734179</v>
+      </c>
+      <c r="G43" s="102" t="n">
+        <v>62.70077990506331</v>
+      </c>
+      <c r="H43" s="102" t="n">
+        <v>67.38489699208863</v>
+      </c>
+      <c r="I43" s="102" t="n">
+        <v>72.38067383805384</v>
       </c>
     </row>
     <row r="44">
@@ -5894,25 +5278,20 @@
       <c r="D45" t="n">
         <v>20.06</v>
       </c>
-      <c r="E45" s="102">
-        <f>E42*$B47</f>
-        <v/>
-      </c>
-      <c r="F45" s="102">
-        <f>F42*$B47</f>
-        <v/>
-      </c>
-      <c r="G45" s="102">
-        <f>G42*$B47</f>
-        <v/>
-      </c>
-      <c r="H45" s="102">
-        <f>H42*$B47</f>
-        <v/>
-      </c>
-      <c r="I45" s="102">
-        <f>I42*$B47</f>
-        <v/>
+      <c r="E45" s="102" t="n">
+        <v>18.32778500366079</v>
+      </c>
+      <c r="F45" s="102" t="n">
+        <v>21.42653766275538</v>
+      </c>
+      <c r="G45" s="102" t="n">
+        <v>24.61307296733871</v>
+      </c>
+      <c r="H45" s="102" t="n">
+        <v>27.90365137799703</v>
+      </c>
+      <c r="I45" s="102" t="n">
+        <v>31.31462423220556</v>
       </c>
     </row>
     <row r="46">
@@ -5924,25 +5303,20 @@
       <c r="D46" t="n">
         <v>212.14</v>
       </c>
-      <c r="E46" s="47">
-        <f>E42+E43-E44-E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="47">
-        <f>F42+F43-F44-F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="47">
-        <f>G42+G43-G44-G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="47">
-        <f>H42+H43-H44-H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="47">
-        <f>I42+I43-I44-I45</f>
-        <v/>
+      <c r="E46" s="47" t="n">
+        <v>248.0073668950734</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>284.8907982196598</v>
+      </c>
+      <c r="G46" s="47" t="n">
+        <v>322.9785051573844</v>
+      </c>
+      <c r="H46" s="47" t="n">
+        <v>362.459750771476</v>
+      </c>
+      <c r="I46" s="47" t="n">
+        <v>403.5258003773242</v>
       </c>
     </row>
     <row r="47">
@@ -5951,9 +5325,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B47" s="28">
-        <f>D45/(D42+D43-D44)</f>
-        <v/>
+      <c r="B47" s="28" t="n">
+        <v>0.08639476290968603</v>
       </c>
     </row>
     <row r="49">
@@ -6006,25 +5379,20 @@
       <c r="D50" t="n">
         <v>32.42</v>
       </c>
-      <c r="E50">
-        <f>D54</f>
-        <v/>
-      </c>
-      <c r="F50">
-        <f>E54</f>
-        <v/>
-      </c>
-      <c r="G50">
-        <f>F54</f>
-        <v/>
-      </c>
-      <c r="H50">
-        <f>G54</f>
-        <v/>
-      </c>
-      <c r="I50">
-        <f>H54</f>
-        <v/>
+      <c r="E50" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F50" t="n">
+        <v>24.93358080861804</v>
+      </c>
+      <c r="G50" t="n">
+        <v>24.77972787455752</v>
+      </c>
+      <c r="H50" t="n">
+        <v>25.31572926819843</v>
+      </c>
+      <c r="I50" t="n">
+        <v>26.34591055116683</v>
       </c>
     </row>
     <row r="51">
@@ -6036,25 +5404,20 @@
       <c r="D51" t="n">
         <v>7.3</v>
       </c>
-      <c r="E51" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A49,$L$4:$L$15,0),MATCH(E49,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F51" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A49,$L$4:$L$15,0),MATCH(F49,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G51" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A49,$L$4:$L$15,0),MATCH(G49,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H51" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A49,$L$4:$L$15,0),MATCH(H49,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I51" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A49,$L$4:$L$15,0),MATCH(I49,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E51" s="102" t="n">
+        <v>7.859050632911393</v>
+      </c>
+      <c r="F51" s="102" t="n">
+        <v>8.455756329113926</v>
+      </c>
+      <c r="G51" s="102" t="n">
+        <v>9.092484968354432</v>
+      </c>
+      <c r="H51" s="102" t="n">
+        <v>9.771747080696205</v>
+      </c>
+      <c r="I51" s="102" t="n">
+        <v>10.49620419185127</v>
       </c>
     </row>
     <row r="52">
@@ -6091,25 +5454,20 @@
       <c r="D53" t="n">
         <v>13.56</v>
       </c>
-      <c r="E53" s="102">
-        <f>E50*$B55</f>
-        <v/>
-      </c>
-      <c r="F53" s="102">
-        <f>F50*$B55</f>
-        <v/>
-      </c>
-      <c r="G53" s="102">
-        <f>G50*$B55</f>
-        <v/>
-      </c>
-      <c r="H53" s="102">
-        <f>H50*$B55</f>
-        <v/>
-      </c>
-      <c r="I53" s="102">
-        <f>I50*$B55</f>
-        <v/>
+      <c r="E53" s="102" t="n">
+        <v>9.005469824293353</v>
+      </c>
+      <c r="F53" s="102" t="n">
+        <v>8.609609263174448</v>
+      </c>
+      <c r="G53" s="102" t="n">
+        <v>8.556483574713521</v>
+      </c>
+      <c r="H53" s="102" t="n">
+        <v>8.7415657977278</v>
+      </c>
+      <c r="I53" s="102" t="n">
+        <v>9.097289204833773</v>
       </c>
     </row>
     <row r="54">
@@ -6121,25 +5479,20 @@
       <c r="D54" t="n">
         <v>26.08</v>
       </c>
-      <c r="E54" s="47">
-        <f>E50+E51-E52-E53</f>
-        <v/>
-      </c>
-      <c r="F54" s="47">
-        <f>F50+F51-F52-F53</f>
-        <v/>
-      </c>
-      <c r="G54" s="47">
-        <f>G50+G51-G52-G53</f>
-        <v/>
-      </c>
-      <c r="H54" s="47">
-        <f>H50+H51-H52-H53</f>
-        <v/>
-      </c>
-      <c r="I54" s="47">
-        <f>I50+I51-I52-I53</f>
-        <v/>
+      <c r="E54" s="47" t="n">
+        <v>24.93358080861804</v>
+      </c>
+      <c r="F54" s="47" t="n">
+        <v>24.77972787455752</v>
+      </c>
+      <c r="G54" s="47" t="n">
+        <v>25.31572926819843</v>
+      </c>
+      <c r="H54" s="47" t="n">
+        <v>26.34591055116683</v>
+      </c>
+      <c r="I54" s="47" t="n">
+        <v>27.74482553818433</v>
       </c>
     </row>
     <row r="55">
@@ -6148,9 +5501,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B55" s="28">
-        <f>D53/(D50+D51-D52)</f>
-        <v/>
+      <c r="B55" s="28" t="n">
+        <v>0.345301757066463</v>
       </c>
     </row>
     <row r="57">
@@ -6203,25 +5555,20 @@
       <c r="D58" t="n">
         <v>3.63</v>
       </c>
-      <c r="E58">
-        <f>D62</f>
-        <v/>
-      </c>
-      <c r="F58">
-        <f>E62</f>
-        <v/>
-      </c>
-      <c r="G58">
-        <f>F62</f>
-        <v/>
-      </c>
-      <c r="H58">
-        <f>G62</f>
-        <v/>
-      </c>
-      <c r="I58">
-        <f>H62</f>
-        <v/>
+      <c r="E58" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.474696359451825</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.39870019200027</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.378040776225937</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.396692911449231</v>
       </c>
     </row>
     <row r="59">
@@ -6233,25 +5580,20 @@
       <c r="D59" t="n">
         <v>0.35</v>
       </c>
-      <c r="E59" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A57,$L$4:$L$15,0),MATCH(E57,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F59" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A57,$L$4:$L$15,0),MATCH(F57,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G59" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A57,$L$4:$L$15,0),MATCH(G57,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H59" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A57,$L$4:$L$15,0),MATCH(H57,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I59" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A57,$L$4:$L$15,0),MATCH(I57,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E59" s="102" t="n">
+        <v>0.3768037974683545</v>
+      </c>
+      <c r="F59" s="102" t="n">
+        <v>0.4054129746835444</v>
+      </c>
+      <c r="G59" s="102" t="n">
+        <v>0.4359410601265823</v>
+      </c>
+      <c r="H59" s="102" t="n">
+        <v>0.4685084216772152</v>
+      </c>
+      <c r="I59" s="102" t="n">
+        <v>0.5032426667325952</v>
       </c>
     </row>
     <row r="60">
@@ -6288,25 +5630,20 @@
       <c r="D61" t="n">
         <v>0.79</v>
       </c>
-      <c r="E61" s="102">
-        <f>E58*$B63</f>
-        <v/>
-      </c>
-      <c r="F61" s="102">
-        <f>F58*$B63</f>
-        <v/>
-      </c>
-      <c r="G61" s="102">
-        <f>G58*$B63</f>
-        <v/>
-      </c>
-      <c r="H61" s="102">
-        <f>H58*$B63</f>
-        <v/>
-      </c>
-      <c r="I61" s="102">
-        <f>I58*$B63</f>
-        <v/>
+      <c r="E61" s="102" t="n">
+        <v>0.5321074380165289</v>
+      </c>
+      <c r="F61" s="102" t="n">
+        <v>0.4814091421351</v>
+      </c>
+      <c r="G61" s="102" t="n">
+        <v>0.4566004759009145</v>
+      </c>
+      <c r="H61" s="102" t="n">
+        <v>0.4498562864539218</v>
+      </c>
+      <c r="I61" s="102" t="n">
+        <v>0.4559452066301209</v>
       </c>
     </row>
     <row r="62">
@@ -6318,25 +5655,20 @@
       <c r="D62" t="n">
         <v>1.63</v>
       </c>
-      <c r="E62" s="47">
-        <f>E58+E59-E60-E61</f>
-        <v/>
-      </c>
-      <c r="F62" s="47">
-        <f>F58+F59-F60-F61</f>
-        <v/>
-      </c>
-      <c r="G62" s="47">
-        <f>G58+G59-G60-G61</f>
-        <v/>
-      </c>
-      <c r="H62" s="47">
-        <f>H58+H59-H60-H61</f>
-        <v/>
-      </c>
-      <c r="I62" s="47">
-        <f>I58+I59-I60-I61</f>
-        <v/>
+      <c r="E62" s="47" t="n">
+        <v>1.474696359451825</v>
+      </c>
+      <c r="F62" s="47" t="n">
+        <v>1.39870019200027</v>
+      </c>
+      <c r="G62" s="47" t="n">
+        <v>1.378040776225937</v>
+      </c>
+      <c r="H62" s="47" t="n">
+        <v>1.396692911449231</v>
+      </c>
+      <c r="I62" s="47" t="n">
+        <v>1.443990371551705</v>
       </c>
     </row>
     <row r="63">
@@ -6345,9 +5677,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B63" s="28">
-        <f>D61/(D58+D59-D60)</f>
-        <v/>
+      <c r="B63" s="28" t="n">
+        <v>0.3264462809917356</v>
       </c>
     </row>
     <row r="65">
@@ -6400,25 +5731,20 @@
       <c r="D66" t="n">
         <v>24.09</v>
       </c>
-      <c r="E66">
-        <f>D70</f>
-        <v/>
-      </c>
-      <c r="F66">
-        <f>E70</f>
-        <v/>
-      </c>
-      <c r="G66">
-        <f>F70</f>
-        <v/>
-      </c>
-      <c r="H66">
-        <f>G70</f>
-        <v/>
-      </c>
-      <c r="I66">
-        <f>H70</f>
-        <v/>
+      <c r="E66" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>54.14432638529701</v>
+      </c>
+      <c r="G66" t="n">
+        <v>70.30874180000713</v>
+      </c>
+      <c r="H66" t="n">
+        <v>86.95985588517053</v>
+      </c>
+      <c r="I66" t="n">
+        <v>104.1660234731124</v>
       </c>
     </row>
     <row r="67">
@@ -6430,25 +5756,20 @@
       <c r="D67" t="n">
         <v>16.78</v>
       </c>
-      <c r="E67" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A65,$L$4:$L$15,0),MATCH(E65,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F67" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A65,$L$4:$L$15,0),MATCH(F65,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G67" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A65,$L$4:$L$15,0),MATCH(G65,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H67" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A65,$L$4:$L$15,0),MATCH(H65,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I67" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A65,$L$4:$L$15,0),MATCH(I65,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E67" s="102" t="n">
+        <v>18.06505063291139</v>
+      </c>
+      <c r="F67" s="102" t="n">
+        <v>19.43665632911393</v>
+      </c>
+      <c r="G67" s="102" t="n">
+        <v>20.90025996835443</v>
+      </c>
+      <c r="H67" s="102" t="n">
+        <v>22.46163233069621</v>
+      </c>
+      <c r="I67" s="102" t="n">
+        <v>24.12689127935128</v>
       </c>
     </row>
     <row r="68">
@@ -6485,25 +5806,20 @@
       <c r="D69" t="n">
         <v>2.47</v>
       </c>
-      <c r="E69" s="102">
-        <f>E66*$B71</f>
-        <v/>
-      </c>
-      <c r="F69" s="102">
-        <f>F66*$B71</f>
-        <v/>
-      </c>
-      <c r="G69" s="102">
-        <f>G66*$B71</f>
-        <v/>
-      </c>
-      <c r="H69" s="102">
-        <f>H66*$B71</f>
-        <v/>
-      </c>
-      <c r="I69" s="102">
-        <f>I66*$B71</f>
-        <v/>
+      <c r="E69" s="102" t="n">
+        <v>2.320724247614387</v>
+      </c>
+      <c r="F69" s="102" t="n">
+        <v>3.272240914403807</v>
+      </c>
+      <c r="G69" s="102" t="n">
+        <v>4.249145883191035</v>
+      </c>
+      <c r="H69" s="102" t="n">
+        <v>5.255464742754373</v>
+      </c>
+      <c r="I69" s="102" t="n">
+        <v>6.295328553427638</v>
       </c>
     </row>
     <row r="70">
@@ -6515,25 +5831,20 @@
       <c r="D70" t="n">
         <v>38.4</v>
       </c>
-      <c r="E70" s="47">
-        <f>E66+E67-E68-E69</f>
-        <v/>
-      </c>
-      <c r="F70" s="47">
-        <f>F66+F67-F68-F69</f>
-        <v/>
-      </c>
-      <c r="G70" s="47">
-        <f>G66+G67-G68-G69</f>
-        <v/>
-      </c>
-      <c r="H70" s="47">
-        <f>H66+H67-H68-H69</f>
-        <v/>
-      </c>
-      <c r="I70" s="47">
-        <f>I66+I67-I68-I69</f>
-        <v/>
+      <c r="E70" s="47" t="n">
+        <v>54.14432638529701</v>
+      </c>
+      <c r="F70" s="47" t="n">
+        <v>70.30874180000713</v>
+      </c>
+      <c r="G70" s="47" t="n">
+        <v>86.95985588517053</v>
+      </c>
+      <c r="H70" s="47" t="n">
+        <v>104.1660234731124</v>
+      </c>
+      <c r="I70" s="47" t="n">
+        <v>121.997586199036</v>
       </c>
     </row>
     <row r="71">
@@ -6542,9 +5853,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B71" s="28">
-        <f>D69/(D66+D67-D68)</f>
-        <v/>
+      <c r="B71" s="28" t="n">
+        <v>0.06043552728162466</v>
       </c>
     </row>
     <row r="73">
@@ -6597,25 +5907,20 @@
       <c r="D74" t="n">
         <v>41.91</v>
       </c>
-      <c r="E74">
-        <f>D78</f>
-        <v/>
-      </c>
-      <c r="F74">
-        <f>E78</f>
-        <v/>
-      </c>
-      <c r="G74">
-        <f>F78</f>
-        <v/>
-      </c>
-      <c r="H74">
-        <f>G78</f>
-        <v/>
-      </c>
-      <c r="I74">
-        <f>H78</f>
-        <v/>
+      <c r="E74" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="F74" t="n">
+        <v>39.32307497455008</v>
+      </c>
+      <c r="G74" t="n">
+        <v>39.89048092713026</v>
+      </c>
+      <c r="H74" t="n">
+        <v>40.96034415430642</v>
+      </c>
+      <c r="I74" t="n">
+        <v>42.47700589868908</v>
       </c>
     </row>
     <row r="75">
@@ -6627,25 +5932,20 @@
       <c r="D75" t="n">
         <v>7.01</v>
       </c>
-      <c r="E75" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A73,$L$4:$L$15,0),MATCH(E73,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F75" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A73,$L$4:$L$15,0),MATCH(F73,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G75" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A73,$L$4:$L$15,0),MATCH(G73,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H75" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A73,$L$4:$L$15,0),MATCH(H73,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I75" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A73,$L$4:$L$15,0),MATCH(I73,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E75" s="102" t="n">
+        <v>7.546841772151899</v>
+      </c>
+      <c r="F75" s="102" t="n">
+        <v>8.119842721518989</v>
+      </c>
+      <c r="G75" s="102" t="n">
+        <v>8.731276661392407</v>
+      </c>
+      <c r="H75" s="102" t="n">
+        <v>9.383554388449369</v>
+      </c>
+      <c r="I75" s="102" t="n">
+        <v>10.07923169655855</v>
       </c>
     </row>
     <row r="76">
@@ -6682,25 +5982,20 @@
       <c r="D77" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="E77" s="102">
-        <f>E74*$B79</f>
-        <v/>
-      </c>
-      <c r="F77" s="102">
-        <f>F74*$B79</f>
-        <v/>
-      </c>
-      <c r="G77" s="102">
-        <f>G74*$B79</f>
-        <v/>
-      </c>
-      <c r="H77" s="102">
-        <f>H74*$B79</f>
-        <v/>
-      </c>
-      <c r="I77" s="102">
-        <f>I74*$B79</f>
-        <v/>
+      <c r="E77" s="102" t="n">
+        <v>7.553766797601819</v>
+      </c>
+      <c r="F77" s="102" t="n">
+        <v>7.552436768938811</v>
+      </c>
+      <c r="G77" s="102" t="n">
+        <v>7.661413434216253</v>
+      </c>
+      <c r="H77" s="102" t="n">
+        <v>7.866892644066708</v>
+      </c>
+      <c r="I77" s="102" t="n">
+        <v>8.158184511036211</v>
       </c>
     </row>
     <row r="78">
@@ -6712,25 +6007,20 @@
       <c r="D78" t="n">
         <v>39.33</v>
       </c>
-      <c r="E78" s="47">
-        <f>E74+E75-E76-E77</f>
-        <v/>
-      </c>
-      <c r="F78" s="47">
-        <f>F74+F75-F76-F77</f>
-        <v/>
-      </c>
-      <c r="G78" s="47">
-        <f>G74+G75-G76-G77</f>
-        <v/>
-      </c>
-      <c r="H78" s="47">
-        <f>H74+H75-H76-H77</f>
-        <v/>
-      </c>
-      <c r="I78" s="47">
-        <f>I74+I75-I76-I77</f>
-        <v/>
+      <c r="E78" s="47" t="n">
+        <v>39.32307497455008</v>
+      </c>
+      <c r="F78" s="47" t="n">
+        <v>39.89048092713026</v>
+      </c>
+      <c r="G78" s="47" t="n">
+        <v>40.96034415430642</v>
+      </c>
+      <c r="H78" s="47" t="n">
+        <v>42.47700589868908</v>
+      </c>
+      <c r="I78" s="47" t="n">
+        <v>44.39805308421142</v>
       </c>
     </row>
     <row r="79">
@@ -6739,9 +6029,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B79" s="28">
-        <f>D77/(D74+D75-D76)</f>
-        <v/>
+      <c r="B79" s="28" t="n">
+        <v>0.192061194955551</v>
       </c>
     </row>
     <row r="81">
@@ -6794,25 +6083,20 @@
       <c r="D82" t="n">
         <v>18.72</v>
       </c>
-      <c r="E82">
-        <f>D86</f>
-        <v/>
-      </c>
-      <c r="F82">
-        <f>E86</f>
-        <v/>
-      </c>
-      <c r="G82">
-        <f>F86</f>
-        <v/>
-      </c>
-      <c r="H82">
-        <f>G86</f>
-        <v/>
-      </c>
-      <c r="I82">
-        <f>H86</f>
-        <v/>
+      <c r="E82" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="F82" t="n">
+        <v>15.71870614266083</v>
+      </c>
+      <c r="G82" t="n">
+        <v>15.30935244421764</v>
+      </c>
+      <c r="H82" t="n">
+        <v>15.21352209055835</v>
+      </c>
+      <c r="I82" t="n">
+        <v>15.37847483821085</v>
       </c>
     </row>
     <row r="83">
@@ -6824,25 +6108,20 @@
       <c r="D83" t="n">
         <v>2.58</v>
       </c>
-      <c r="E83" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A81,$L$4:$L$15,0),MATCH(E81,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="F83" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A81,$L$4:$L$15,0),MATCH(F81,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="G83" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A81,$L$4:$L$15,0),MATCH(G81,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="H83" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A81,$L$4:$L$15,0),MATCH(H81,$L$4:$T$4,0))</f>
-        <v/>
-      </c>
-      <c r="I83" s="102">
-        <f>INDEX($L$4:$T$15,MATCH($A81,$L$4:$L$15,0),MATCH(I81,$L$4:$T$4,0))</f>
-        <v/>
+      <c r="E83" s="102" t="n">
+        <v>2.777582278481013</v>
+      </c>
+      <c r="F83" s="102" t="n">
+        <v>2.988472784810127</v>
+      </c>
+      <c r="G83" s="102" t="n">
+        <v>3.21350838607595</v>
+      </c>
+      <c r="H83" s="102" t="n">
+        <v>3.45357636550633</v>
+      </c>
+      <c r="I83" s="102" t="n">
+        <v>3.709617371914559</v>
       </c>
     </row>
     <row r="84">
@@ -6879,25 +6158,20 @@
       <c r="D85" t="n">
         <v>4.52</v>
       </c>
-      <c r="E85" s="102">
-        <f>E82*$B87</f>
-        <v/>
-      </c>
-      <c r="F85" s="102">
-        <f>F82*$B87</f>
-        <v/>
-      </c>
-      <c r="G85" s="102">
-        <f>G82*$B87</f>
-        <v/>
-      </c>
-      <c r="H85" s="102">
-        <f>H82*$B87</f>
-        <v/>
-      </c>
-      <c r="I85" s="102">
-        <f>I82*$B87</f>
-        <v/>
+      <c r="E85" s="102" t="n">
+        <v>3.568876135820183</v>
+      </c>
+      <c r="F85" s="102" t="n">
+        <v>3.397826483253322</v>
+      </c>
+      <c r="G85" s="102" t="n">
+        <v>3.309338739735233</v>
+      </c>
+      <c r="H85" s="102" t="n">
+        <v>3.288623617853839</v>
+      </c>
+      <c r="I85" s="102" t="n">
+        <v>3.32428054847982</v>
       </c>
     </row>
     <row r="86">
@@ -6909,25 +6183,20 @@
       <c r="D86" t="n">
         <v>16.51</v>
       </c>
-      <c r="E86" s="47">
-        <f>E82+E83-E84-E85</f>
-        <v/>
-      </c>
-      <c r="F86" s="47">
-        <f>F82+F83-F84-F85</f>
-        <v/>
-      </c>
-      <c r="G86" s="47">
-        <f>G82+G83-G84-G85</f>
-        <v/>
-      </c>
-      <c r="H86" s="47">
-        <f>H82+H83-H84-H85</f>
-        <v/>
-      </c>
-      <c r="I86" s="47">
-        <f>I82+I83-I84-I85</f>
-        <v/>
+      <c r="E86" s="47" t="n">
+        <v>15.71870614266083</v>
+      </c>
+      <c r="F86" s="47" t="n">
+        <v>15.30935244421764</v>
+      </c>
+      <c r="G86" s="47" t="n">
+        <v>15.21352209055835</v>
+      </c>
+      <c r="H86" s="47" t="n">
+        <v>15.37847483821085</v>
+      </c>
+      <c r="I86" s="47" t="n">
+        <v>15.76381166164559</v>
       </c>
     </row>
     <row r="87">
@@ -6936,9 +6205,8 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B87" s="28">
-        <f>D85/(D82+D83-D84)</f>
-        <v/>
+      <c r="B87" s="28" t="n">
+        <v>0.2161645145863224</v>
       </c>
     </row>
   </sheetData>
@@ -7022,25 +6290,20 @@
       <c r="D4" s="100" t="n">
         <v>7224.46</v>
       </c>
-      <c r="E4" s="104">
-        <f>'Asset schedule'!E6+'Asset schedule'!E14+'Asset schedule'!E22+'Asset schedule'!E30+'Asset schedule'!E38+'Asset schedule'!E46+'Asset schedule'!E54+'Asset schedule'!E62+'Asset schedule'!E70+'Asset schedule'!E78+'Asset schedule'!E86</f>
-        <v/>
-      </c>
-      <c r="F4" s="104">
-        <f>'Asset schedule'!F6+'Asset schedule'!F14+'Asset schedule'!F22+'Asset schedule'!F30+'Asset schedule'!F38+'Asset schedule'!F46+'Asset schedule'!F54+'Asset schedule'!F62+'Asset schedule'!F70+'Asset schedule'!F78+'Asset schedule'!F86</f>
-        <v/>
-      </c>
-      <c r="G4" s="104">
-        <f>'Asset schedule'!G6+'Asset schedule'!G14+'Asset schedule'!G22+'Asset schedule'!G30+'Asset schedule'!G38+'Asset schedule'!G46+'Asset schedule'!G54+'Asset schedule'!G62+'Asset schedule'!G70+'Asset schedule'!G78+'Asset schedule'!G86</f>
-        <v/>
-      </c>
-      <c r="H4" s="104">
-        <f>'Asset schedule'!H6+'Asset schedule'!H14+'Asset schedule'!H22+'Asset schedule'!H30+'Asset schedule'!H38+'Asset schedule'!H46+'Asset schedule'!H54+'Asset schedule'!H62+'Asset schedule'!H70+'Asset schedule'!H78+'Asset schedule'!H86</f>
-        <v/>
-      </c>
-      <c r="I4" s="104">
-        <f>'Asset schedule'!I6+'Asset schedule'!I14+'Asset schedule'!I22+'Asset schedule'!I30+'Asset schedule'!I38+'Asset schedule'!I46+'Asset schedule'!I54+'Asset schedule'!I62+'Asset schedule'!I70+'Asset schedule'!I78+'Asset schedule'!I86</f>
-        <v/>
+      <c r="E4" s="104" t="n">
+        <v>7088.693052020696</v>
+      </c>
+      <c r="F4" s="104" t="n">
+        <v>6960.331255933688</v>
+      </c>
+      <c r="G4" s="104" t="n">
+        <v>6876.924751098072</v>
+      </c>
+      <c r="H4" s="104" t="n">
+        <v>6836.457073271327</v>
+      </c>
+      <c r="I4" s="104" t="n">
+        <v>6837.308117831549</v>
       </c>
     </row>
     <row r="5">
@@ -7055,25 +6318,20 @@
       <c r="D5" s="100" t="n">
         <v>269.25</v>
       </c>
-      <c r="E5" s="98">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="98">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="98">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="98">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="98">
-        <f>H5</f>
-        <v/>
+      <c r="E5" s="98" t="n">
+        <v>269.25</v>
+      </c>
+      <c r="F5" s="98" t="n">
+        <v>269.25</v>
+      </c>
+      <c r="G5" s="98" t="n">
+        <v>269.25</v>
+      </c>
+      <c r="H5" s="98" t="n">
+        <v>269.25</v>
+      </c>
+      <c r="I5" s="98" t="n">
+        <v>269.25</v>
       </c>
     </row>
     <row r="6">
@@ -7088,25 +6346,20 @@
       <c r="D6" s="100" t="n">
         <v>15.57</v>
       </c>
-      <c r="E6" s="98">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="98">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="98">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="98">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="98">
-        <f>H6</f>
-        <v/>
+      <c r="E6" s="98" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="F6" s="98" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="G6" s="98" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="H6" s="98" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="I6" s="98" t="n">
+        <v>15.57</v>
       </c>
     </row>
     <row r="7">
@@ -7358,33 +6611,26 @@
         </is>
       </c>
       <c r="B16" s="36" t="n"/>
-      <c r="C16" s="105">
-        <f>SUM(C4:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="105">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="105">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="105">
-        <f>SUM(F4:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="105">
-        <f>SUM(G4:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="105">
-        <f>SUM(H4:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="105">
-        <f>SUM(I4:I15)</f>
-        <v/>
+      <c r="C16" s="105" t="n">
+        <v>9289.219999999999</v>
+      </c>
+      <c r="D16" s="105" t="n">
+        <v>9190.82</v>
+      </c>
+      <c r="E16" s="105" t="n">
+        <v>9015.023052020695</v>
+      </c>
+      <c r="F16" s="105" t="n">
+        <v>8886.661255933688</v>
+      </c>
+      <c r="G16" s="105" t="n">
+        <v>8803.254751098071</v>
+      </c>
+      <c r="H16" s="105" t="n">
+        <v>8762.787073271327</v>
+      </c>
+      <c r="I16" s="105" t="n">
+        <v>8763.638117831548</v>
       </c>
     </row>
     <row r="17">
@@ -7408,25 +6654,20 @@
       <c r="D18" s="100" t="n">
         <v>1404.78</v>
       </c>
-      <c r="E18" s="104">
-        <f>SUM('Financial Statements'!E4:E7)*'Balance Sheet'!E57</f>
-        <v/>
-      </c>
-      <c r="F18" s="104">
-        <f>SUM('Financial Statements'!F4:F7)*'Balance Sheet'!F57</f>
-        <v/>
-      </c>
-      <c r="G18" s="104">
-        <f>SUM('Financial Statements'!G4:G7)*'Balance Sheet'!G57</f>
-        <v/>
-      </c>
-      <c r="H18" s="104">
-        <f>SUM('Financial Statements'!H4:H7)*'Balance Sheet'!H57</f>
-        <v/>
-      </c>
-      <c r="I18" s="104">
-        <f>SUM('Financial Statements'!I4:I7)*'Balance Sheet'!I57</f>
-        <v/>
+      <c r="E18" s="104" t="n">
+        <v>1614.692303209429</v>
+      </c>
+      <c r="F18" s="104" t="n">
+        <v>1750.038339358</v>
+      </c>
+      <c r="G18" s="104" t="n">
+        <v>1895.527379897816</v>
+      </c>
+      <c r="H18" s="104" t="n">
+        <v>2051.867616754349</v>
+      </c>
+      <c r="I18" s="104" t="n">
+        <v>2219.81431636348</v>
       </c>
     </row>
     <row r="19">
@@ -7492,25 +6733,20 @@
       <c r="D21" s="100" t="n">
         <v>665.97</v>
       </c>
-      <c r="E21" s="104">
-        <f>'Financial Statements'!E2*'Balance Sheet'!E58</f>
-        <v/>
-      </c>
-      <c r="F21" s="104">
-        <f>'Financial Statements'!F2*'Balance Sheet'!F58</f>
-        <v/>
-      </c>
-      <c r="G21" s="104">
-        <f>'Financial Statements'!G2*'Balance Sheet'!G58</f>
-        <v/>
-      </c>
-      <c r="H21" s="104">
-        <f>'Financial Statements'!H2*'Balance Sheet'!H58</f>
-        <v/>
-      </c>
-      <c r="I21" s="104">
-        <f>'Financial Statements'!I2*'Balance Sheet'!I58</f>
-        <v/>
+      <c r="E21" s="104" t="n">
+        <v>704.9318970579036</v>
+      </c>
+      <c r="F21" s="104" t="n">
+        <v>758.4545040567446</v>
+      </c>
+      <c r="G21" s="104" t="n">
+        <v>815.5670420128246</v>
+      </c>
+      <c r="H21" s="104" t="n">
+        <v>876.4946975043709</v>
+      </c>
+      <c r="I21" s="104" t="n">
+        <v>941.4762009400401</v>
       </c>
     </row>
     <row r="22">
@@ -7525,25 +6761,20 @@
       <c r="D22" s="100" t="n">
         <v>2559.66</v>
       </c>
-      <c r="E22" s="104">
-        <f>'Financial Statements'!O34</f>
-        <v/>
-      </c>
-      <c r="F22" s="104">
-        <f>'Financial Statements'!P34</f>
-        <v/>
-      </c>
-      <c r="G22" s="104">
-        <f>'Financial Statements'!Q34</f>
-        <v/>
-      </c>
-      <c r="H22" s="104">
-        <f>'Financial Statements'!R34</f>
-        <v/>
-      </c>
-      <c r="I22" s="104">
-        <f>'Financial Statements'!S34</f>
-        <v/>
+      <c r="E22" s="104" t="n">
+        <v>3143.421708963787</v>
+      </c>
+      <c r="F22" s="104" t="n">
+        <v>3888.890718034904</v>
+      </c>
+      <c r="G22" s="104" t="n">
+        <v>4626.195635123337</v>
+      </c>
+      <c r="H22" s="104" t="n">
+        <v>5354.223003271239</v>
+      </c>
+      <c r="I22" s="104" t="n">
+        <v>6071.295348656084</v>
       </c>
     </row>
     <row r="23">
@@ -7659,33 +6890,26 @@
       </c>
     </row>
     <row r="27" s="74">
-      <c r="C27" s="105">
-        <f>SUM(C18:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="105">
-        <f>SUM(D18:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="105">
-        <f>SUM(E18:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="105">
-        <f>SUM(F18:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="105">
-        <f>SUM(G18:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="105">
-        <f>SUM(H18:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="105">
-        <f>SUM(I18:I26)</f>
-        <v/>
+      <c r="C27" s="105" t="n">
+        <v>4092.650000000001</v>
+      </c>
+      <c r="D27" s="105" t="n">
+        <v>5641.84</v>
+      </c>
+      <c r="E27" s="105" t="n">
+        <v>6474.47590923112</v>
+      </c>
+      <c r="F27" s="105" t="n">
+        <v>7408.81356144965</v>
+      </c>
+      <c r="G27" s="105" t="n">
+        <v>8348.720057033977</v>
+      </c>
+      <c r="H27" s="105" t="n">
+        <v>9294.015317529958</v>
+      </c>
+      <c r="I27" s="105" t="n">
+        <v>10244.0158659596</v>
       </c>
     </row>
     <row r="28">
@@ -7722,33 +6946,26 @@
           <t>Total Current assets</t>
         </is>
       </c>
-      <c r="C29" s="105">
-        <f>C27+C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="105">
-        <f>D27+D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="105">
-        <f>E27+E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="105">
-        <f>F27+F28</f>
-        <v/>
-      </c>
-      <c r="G29" s="105">
-        <f>G27+G28</f>
-        <v/>
-      </c>
-      <c r="H29" s="105">
-        <f>H27+H28</f>
-        <v/>
-      </c>
-      <c r="I29" s="105">
-        <f>I27+I28</f>
-        <v/>
+      <c r="C29" s="105" t="n">
+        <v>4104.72</v>
+      </c>
+      <c r="D29" s="105" t="n">
+        <v>5654.92</v>
+      </c>
+      <c r="E29" s="105" t="n">
+        <v>6487.55590923112</v>
+      </c>
+      <c r="F29" s="105" t="n">
+        <v>7421.893561449649</v>
+      </c>
+      <c r="G29" s="105" t="n">
+        <v>8361.800057033977</v>
+      </c>
+      <c r="H29" s="105" t="n">
+        <v>9307.095317529958</v>
+      </c>
+      <c r="I29" s="105" t="n">
+        <v>10257.0958659596</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="74" thickBot="1">
@@ -7758,33 +6975,26 @@
         </is>
       </c>
       <c r="B30" s="60" t="n"/>
-      <c r="C30" s="106">
-        <f>C29+C16</f>
-        <v/>
-      </c>
-      <c r="D30" s="106">
-        <f>D29+D16</f>
-        <v/>
-      </c>
-      <c r="E30" s="106">
-        <f>E29+E16</f>
-        <v/>
-      </c>
-      <c r="F30" s="106">
-        <f>F29+F16</f>
-        <v/>
-      </c>
-      <c r="G30" s="106">
-        <f>G29+G16</f>
-        <v/>
-      </c>
-      <c r="H30" s="106">
-        <f>H29+H16</f>
-        <v/>
-      </c>
-      <c r="I30" s="106">
-        <f>I29+I16</f>
-        <v/>
+      <c r="C30" s="106" t="n">
+        <v>13393.94</v>
+      </c>
+      <c r="D30" s="106" t="n">
+        <v>14845.74</v>
+      </c>
+      <c r="E30" s="106" t="n">
+        <v>15502.57896125181</v>
+      </c>
+      <c r="F30" s="106" t="n">
+        <v>16308.55481738334</v>
+      </c>
+      <c r="G30" s="106" t="n">
+        <v>17165.05480813205</v>
+      </c>
+      <c r="H30" s="106" t="n">
+        <v>18069.88239080129</v>
+      </c>
+      <c r="I30" s="106" t="n">
+        <v>19020.73398379115</v>
       </c>
     </row>
     <row r="31">
@@ -7817,25 +7027,20 @@
       <c r="D33" s="100" t="n">
         <v>187.99</v>
       </c>
-      <c r="E33" s="107">
-        <f>D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="107">
-        <f>E33</f>
-        <v/>
-      </c>
-      <c r="G33" s="107">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H33" s="107">
-        <f>G33</f>
-        <v/>
-      </c>
-      <c r="I33" s="107">
-        <f>H33</f>
-        <v/>
+      <c r="E33" s="107" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="F33" s="107" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="G33" s="107" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="H33" s="107" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="I33" s="107" t="n">
+        <v>187.99</v>
       </c>
     </row>
     <row r="34">
@@ -7850,25 +7055,20 @@
       <c r="D34" s="100" t="n">
         <v>9167.860000000001</v>
       </c>
-      <c r="E34" s="107">
-        <f>D34+'Financial Statements'!E20</f>
-        <v/>
-      </c>
-      <c r="F34" s="107">
-        <f>E34+'Financial Statements'!F20</f>
-        <v/>
-      </c>
-      <c r="G34" s="107">
-        <f>F34+'Financial Statements'!G20</f>
-        <v/>
-      </c>
-      <c r="H34" s="107">
-        <f>G34+'Financial Statements'!H20</f>
-        <v/>
-      </c>
-      <c r="I34" s="107">
-        <f>H34+'Financial Statements'!I20</f>
-        <v/>
+      <c r="E34" s="107" t="n">
+        <v>9775.935080537865</v>
+      </c>
+      <c r="F34" s="107" t="n">
+        <v>10425.74684436236</v>
+      </c>
+      <c r="G34" s="107" t="n">
+        <v>11114.37960676032</v>
+      </c>
+      <c r="H34" s="107" t="n">
+        <v>11838.81970358575</v>
+      </c>
+      <c r="I34" s="107" t="n">
+        <v>12595.89211658078</v>
       </c>
     </row>
     <row r="35">
@@ -7906,33 +7106,26 @@
         </is>
       </c>
       <c r="B36" s="36" t="n"/>
-      <c r="C36" s="105">
-        <f>C33+C34+C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="105">
-        <f>D33+D34+D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="105">
-        <f>E33+E34+E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="105">
-        <f>F33+F34+F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="105">
-        <f>G33+G34+G35</f>
-        <v/>
-      </c>
-      <c r="H36" s="105">
-        <f>H33+H34+H35</f>
-        <v/>
-      </c>
-      <c r="I36" s="105">
-        <f>I33+I34+I35</f>
-        <v/>
+      <c r="C36" s="105" t="n">
+        <v>8816.210000000001</v>
+      </c>
+      <c r="D36" s="105" t="n">
+        <v>9358.73</v>
+      </c>
+      <c r="E36" s="105" t="n">
+        <v>9966.805080537864</v>
+      </c>
+      <c r="F36" s="105" t="n">
+        <v>10616.61684436236</v>
+      </c>
+      <c r="G36" s="105" t="n">
+        <v>11305.24960676032</v>
+      </c>
+      <c r="H36" s="105" t="n">
+        <v>12029.68970358575</v>
+      </c>
+      <c r="I36" s="105" t="n">
+        <v>12786.76211658078</v>
       </c>
     </row>
     <row r="37">
@@ -8016,33 +7209,26 @@
         </is>
       </c>
       <c r="B41" s="36" t="n"/>
-      <c r="C41" s="105">
-        <f>SUM(C39:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="105">
-        <f>SUM(D39:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="105">
-        <f>SUM(E39:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="105">
-        <f>SUM(F39:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="105">
-        <f>SUM(G39:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="105">
-        <f>SUM(H39:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="105">
-        <f>SUM(I39:I40)</f>
-        <v/>
+      <c r="C41" s="105" t="n">
+        <v>597.6700000000001</v>
+      </c>
+      <c r="D41" s="105" t="n">
+        <v>694.3499999999999</v>
+      </c>
+      <c r="E41" s="105" t="n">
+        <v>694.3499999999999</v>
+      </c>
+      <c r="F41" s="105" t="n">
+        <v>694.3499999999999</v>
+      </c>
+      <c r="G41" s="105" t="n">
+        <v>694.3499999999999</v>
+      </c>
+      <c r="H41" s="105" t="n">
+        <v>694.3499999999999</v>
+      </c>
+      <c r="I41" s="105" t="n">
+        <v>694.3499999999999</v>
       </c>
     </row>
     <row r="42">
@@ -8075,25 +7261,20 @@
       <c r="D44" s="100" t="n">
         <v>1813.74</v>
       </c>
-      <c r="E44" s="104">
-        <f>SUM('Financial Statements'!E4:E7)*'Balance Sheet'!E59</f>
-        <v/>
-      </c>
-      <c r="F44" s="104">
-        <f>SUM('Financial Statements'!F4:F7)*'Balance Sheet'!F59</f>
-        <v/>
-      </c>
-      <c r="G44" s="104">
-        <f>SUM('Financial Statements'!G4:G7)*'Balance Sheet'!G59</f>
-        <v/>
-      </c>
-      <c r="H44" s="104">
-        <f>SUM('Financial Statements'!H4:H7)*'Balance Sheet'!H59</f>
-        <v/>
-      </c>
-      <c r="I44" s="104">
-        <f>SUM('Financial Statements'!I4:I7)*'Balance Sheet'!I59</f>
-        <v/>
+      <c r="E44" s="104" t="n">
+        <v>1863.05388071395</v>
+      </c>
+      <c r="F44" s="104" t="n">
+        <v>2019.217973020979</v>
+      </c>
+      <c r="G44" s="104" t="n">
+        <v>2187.085201371727</v>
+      </c>
+      <c r="H44" s="104" t="n">
+        <v>2367.472687215539</v>
+      </c>
+      <c r="I44" s="104" t="n">
+        <v>2561.251867210372</v>
       </c>
     </row>
     <row r="45">
@@ -8215,33 +7396,26 @@
         </is>
       </c>
       <c r="B49" s="36" t="n"/>
-      <c r="C49" s="105">
-        <f>SUM(C44:C48)</f>
-        <v/>
-      </c>
-      <c r="D49" s="105">
-        <f>SUM(D44:D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="105">
-        <f>SUM(E44:E48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="105">
-        <f>SUM(F44:F48)</f>
-        <v/>
-      </c>
-      <c r="G49" s="105">
-        <f>SUM(G44:G48)</f>
-        <v/>
-      </c>
-      <c r="H49" s="105">
-        <f>SUM(H44:H48)</f>
-        <v/>
-      </c>
-      <c r="I49" s="105">
-        <f>SUM(I44:I48)</f>
-        <v/>
+      <c r="C49" s="105" t="n">
+        <v>3980.06</v>
+      </c>
+      <c r="D49" s="105" t="n">
+        <v>4792.66</v>
+      </c>
+      <c r="E49" s="105" t="n">
+        <v>4841.97388071395</v>
+      </c>
+      <c r="F49" s="105" t="n">
+        <v>4998.137973020979</v>
+      </c>
+      <c r="G49" s="105" t="n">
+        <v>5166.005201371727</v>
+      </c>
+      <c r="H49" s="105" t="n">
+        <v>5346.392687215539</v>
+      </c>
+      <c r="I49" s="105" t="n">
+        <v>5540.171867210372</v>
       </c>
     </row>
     <row r="50">
@@ -8251,33 +7425,26 @@
         </is>
       </c>
       <c r="B50" s="36" t="n"/>
-      <c r="C50" s="105">
-        <f>C49+C41</f>
-        <v/>
-      </c>
-      <c r="D50" s="105">
-        <f>D49+D41</f>
-        <v/>
-      </c>
-      <c r="E50" s="105">
-        <f>E49+E41</f>
-        <v/>
-      </c>
-      <c r="F50" s="105">
-        <f>F49+F41</f>
-        <v/>
-      </c>
-      <c r="G50" s="105">
-        <f>G49+G41</f>
-        <v/>
-      </c>
-      <c r="H50" s="105">
-        <f>H49+H41</f>
-        <v/>
-      </c>
-      <c r="I50" s="105">
-        <f>I49+I41</f>
-        <v/>
+      <c r="C50" s="105" t="n">
+        <v>4577.73</v>
+      </c>
+      <c r="D50" s="105" t="n">
+        <v>5487.01</v>
+      </c>
+      <c r="E50" s="105" t="n">
+        <v>5536.32388071395</v>
+      </c>
+      <c r="F50" s="105" t="n">
+        <v>5692.48797302098</v>
+      </c>
+      <c r="G50" s="105" t="n">
+        <v>5860.355201371727</v>
+      </c>
+      <c r="H50" s="105" t="n">
+        <v>6040.742687215539</v>
+      </c>
+      <c r="I50" s="105" t="n">
+        <v>6234.521867210371</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="74" thickBot="1">
@@ -8287,55 +7454,43 @@
         </is>
       </c>
       <c r="B51" s="60" t="n"/>
-      <c r="C51" s="106">
-        <f>C50+C36</f>
-        <v/>
-      </c>
-      <c r="D51" s="106">
-        <f>D50+D36</f>
-        <v/>
-      </c>
-      <c r="E51" s="106">
-        <f>E50+E36</f>
-        <v/>
-      </c>
-      <c r="F51" s="106">
-        <f>F50+F36</f>
-        <v/>
-      </c>
-      <c r="G51" s="106">
-        <f>G50+G36</f>
-        <v/>
-      </c>
-      <c r="H51" s="106">
-        <f>H50+H36</f>
-        <v/>
-      </c>
-      <c r="I51" s="106">
-        <f>I50+I36</f>
-        <v/>
+      <c r="C51" s="106" t="n">
+        <v>13393.94</v>
+      </c>
+      <c r="D51" s="106" t="n">
+        <v>14845.74</v>
+      </c>
+      <c r="E51" s="106" t="n">
+        <v>15503.12896125181</v>
+      </c>
+      <c r="F51" s="106" t="n">
+        <v>16309.10481738334</v>
+      </c>
+      <c r="G51" s="106" t="n">
+        <v>17165.60480813205</v>
+      </c>
+      <c r="H51" s="106" t="n">
+        <v>18070.43239080129</v>
+      </c>
+      <c r="I51" s="106" t="n">
+        <v>19021.28398379115</v>
       </c>
     </row>
     <row r="53">
-      <c r="E53" s="101">
-        <f>E51-E30</f>
-        <v/>
-      </c>
-      <c r="F53" s="101">
-        <f>F51-F30</f>
-        <v/>
-      </c>
-      <c r="G53" s="101">
-        <f>G51-G30</f>
-        <v/>
-      </c>
-      <c r="H53" s="101">
-        <f>H51-H30</f>
-        <v/>
-      </c>
-      <c r="I53" s="101">
-        <f>I51-I30</f>
-        <v/>
+      <c r="E53" s="101" t="n">
+        <v>0.5499999999992724</v>
+      </c>
+      <c r="F53" s="101" t="n">
+        <v>0.5499999999992724</v>
+      </c>
+      <c r="G53" s="101" t="n">
+        <v>0.5499999999992724</v>
+      </c>
+      <c r="H53" s="101" t="n">
+        <v>0.5500000000029104</v>
+      </c>
+      <c r="I53" s="101" t="n">
+        <v>0.5500000000029104</v>
       </c>
     </row>
     <row r="57">
@@ -8344,33 +7499,26 @@
           <t>Inventory as % of raw material</t>
         </is>
       </c>
-      <c r="C57" s="28">
-        <f>C18/SUM('Financial Statements'!C4:C7)</f>
-        <v/>
-      </c>
-      <c r="D57" s="28">
-        <f>D18/SUM('Financial Statements'!D4:D7)</f>
-        <v/>
-      </c>
-      <c r="E57" s="28">
-        <f>AVERAGE(C57:D57)</f>
-        <v/>
-      </c>
-      <c r="F57" s="28">
-        <f>E57</f>
-        <v/>
-      </c>
-      <c r="G57" s="28">
-        <f>F57</f>
-        <v/>
-      </c>
-      <c r="H57" s="28">
-        <f>G57</f>
-        <v/>
-      </c>
-      <c r="I57" s="28">
-        <f>H57</f>
-        <v/>
+      <c r="C57" s="28" t="n">
+        <v>0.1710494153929529</v>
+      </c>
+      <c r="D57" s="28" t="n">
+        <v>0.1571688615947809</v>
+      </c>
+      <c r="E57" s="28" t="n">
+        <v>0.1641091384938669</v>
+      </c>
+      <c r="F57" s="28" t="n">
+        <v>0.1641091384938669</v>
+      </c>
+      <c r="G57" s="28" t="n">
+        <v>0.1641091384938669</v>
+      </c>
+      <c r="H57" s="28" t="n">
+        <v>0.1641091384938669</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>0.1641091384938669</v>
       </c>
     </row>
     <row r="58">
@@ -8379,33 +7527,26 @@
           <t>Trade receivables as % of Sales</t>
         </is>
       </c>
-      <c r="C58" s="28">
-        <f>C21/'Financial Statements'!C2</f>
-        <v/>
-      </c>
-      <c r="D58" s="28">
-        <f>D21/'Financial Statements'!D2</f>
-        <v/>
-      </c>
-      <c r="E58" s="28">
-        <f>AVERAGE(C58:D58)</f>
-        <v/>
-      </c>
-      <c r="F58" s="28">
-        <f>E58</f>
-        <v/>
-      </c>
-      <c r="G58" s="28">
-        <f>F58</f>
-        <v/>
-      </c>
-      <c r="H58" s="28">
-        <f>G58</f>
-        <v/>
-      </c>
-      <c r="I58" s="28">
-        <f>H58</f>
-        <v/>
+      <c r="C58" s="28" t="n">
+        <v>0.0479814978132143</v>
+      </c>
+      <c r="D58" s="28" t="n">
+        <v>0.04964893786744479</v>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>0.04881521784032954</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>0.04881521784032954</v>
+      </c>
+      <c r="G58" s="28" t="n">
+        <v>0.04881521784032954</v>
+      </c>
+      <c r="H58" s="28" t="n">
+        <v>0.04881521784032954</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>0.04881521784032954</v>
       </c>
     </row>
     <row r="59">
@@ -8414,33 +7555,26 @@
           <t>Trade payables as % of raw material</t>
         </is>
       </c>
-      <c r="C59" s="28">
-        <f>C44/SUM('Financial Statements'!C4:C7)</f>
-        <v/>
-      </c>
-      <c r="D59" s="28">
-        <f>D44/SUM('Financial Statements'!D4:D7)</f>
-        <v/>
-      </c>
-      <c r="E59" s="28">
-        <f>AVERAGE(C59:D59)</f>
-        <v/>
-      </c>
-      <c r="F59" s="28">
-        <f>E59</f>
-        <v/>
-      </c>
-      <c r="G59" s="28">
-        <f>F59</f>
-        <v/>
-      </c>
-      <c r="H59" s="28">
-        <f>G59</f>
-        <v/>
-      </c>
-      <c r="I59" s="28">
-        <f>H59</f>
-        <v/>
+      <c r="C59" s="28" t="n">
+        <v>0.1757787893305547</v>
+      </c>
+      <c r="D59" s="28" t="n">
+        <v>0.202923910526145</v>
+      </c>
+      <c r="E59" s="28" t="n">
+        <v>0.1893513499283499</v>
+      </c>
+      <c r="F59" s="28" t="n">
+        <v>0.1893513499283499</v>
+      </c>
+      <c r="G59" s="28" t="n">
+        <v>0.1893513499283499</v>
+      </c>
+      <c r="H59" s="28" t="n">
+        <v>0.1893513499283499</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>0.1893513499283499</v>
       </c>
     </row>
   </sheetData>
@@ -8496,25 +7630,20 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B2" s="26">
-        <f>'Financial Statements'!E12</f>
-        <v/>
-      </c>
-      <c r="C2" s="26">
-        <f>'Financial Statements'!F12</f>
-        <v/>
-      </c>
-      <c r="D2" s="26">
-        <f>'Financial Statements'!G12</f>
-        <v/>
-      </c>
-      <c r="E2" s="26">
-        <f>'Financial Statements'!H12</f>
-        <v/>
-      </c>
-      <c r="F2" s="26">
-        <f>'Financial Statements'!I12</f>
-        <v/>
+      <c r="B2" s="26" t="n">
+        <v>1391.326062337152</v>
+      </c>
+      <c r="C2" s="26" t="n">
+        <v>1480.060203128183</v>
+      </c>
+      <c r="D2" s="26" t="n">
+        <v>1562.595461845554</v>
+      </c>
+      <c r="E2" s="26" t="n">
+        <v>1638.723529632292</v>
+      </c>
+      <c r="F2" s="26" t="n">
+        <v>1708.101360099694</v>
       </c>
     </row>
     <row r="3">
@@ -8523,25 +7652,20 @@
           <t>Less: Tax on EBIT</t>
         </is>
       </c>
-      <c r="B3" s="66">
-        <f>B2*'Financial Statements'!E16</f>
-        <v/>
-      </c>
-      <c r="C3" s="66">
-        <f>C2*'Financial Statements'!F16</f>
-        <v/>
-      </c>
-      <c r="D3" s="66">
-        <f>D2*'Financial Statements'!G16</f>
-        <v/>
-      </c>
-      <c r="E3" s="66">
-        <f>E2*'Financial Statements'!H16</f>
-        <v/>
-      </c>
-      <c r="F3" s="66">
-        <f>F2*'Financial Statements'!I16</f>
-        <v/>
+      <c r="B3" s="66" t="n">
+        <v>381.4911916079781</v>
+      </c>
+      <c r="C3" s="66" t="n">
+        <v>405.8214287989766</v>
+      </c>
+      <c r="D3" s="66" t="n">
+        <v>428.4519789267241</v>
+      </c>
+      <c r="E3" s="66" t="n">
+        <v>449.3257252619223</v>
+      </c>
+      <c r="F3" s="66" t="n">
+        <v>468.3486070526408</v>
       </c>
     </row>
     <row r="4">
@@ -8550,25 +7674,20 @@
           <t>Debt free earning</t>
         </is>
       </c>
-      <c r="B4" s="26">
-        <f>B2-B3</f>
-        <v/>
-      </c>
-      <c r="C4" s="26">
-        <f>C2-C3</f>
-        <v/>
-      </c>
-      <c r="D4" s="26">
-        <f>D2-D3</f>
-        <v/>
-      </c>
-      <c r="E4" s="26">
-        <f>E2-E3</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>F2-F3</f>
-        <v/>
+      <c r="B4" s="26" t="n">
+        <v>1009.834870729173</v>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>1074.238774329207</v>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>1134.14348291883</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>1189.39780437037</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>1239.752753047054</v>
       </c>
     </row>
     <row r="6">
@@ -8577,25 +7696,20 @@
           <t>Add: Dep &amp; Ammo</t>
         </is>
       </c>
-      <c r="B6" s="41">
-        <f>'Financial Statements'!E11</f>
-        <v/>
-      </c>
-      <c r="C6" s="41">
-        <f>'Financial Statements'!F11</f>
-        <v/>
-      </c>
-      <c r="D6" s="41">
-        <f>'Financial Statements'!G11</f>
-        <v/>
-      </c>
-      <c r="E6" s="41">
-        <f>'Financial Statements'!H11</f>
-        <v/>
-      </c>
-      <c r="F6" s="41">
-        <f>'Financial Statements'!I11</f>
-        <v/>
+      <c r="B6" s="41" t="n">
+        <v>582.6373910172789</v>
+      </c>
+      <c r="C6" s="41" t="n">
+        <v>566.0919764667541</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>554.0982951837184</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>546.3229136890859</v>
+      </c>
+      <c r="F6" s="41" t="n">
+        <v>542.5072518919166</v>
       </c>
     </row>
     <row r="7">
@@ -8604,25 +7718,20 @@
           <t>Less: Capex</t>
         </is>
       </c>
-      <c r="B7" s="41">
-        <f>-'Asset schedule'!P2</f>
-        <v/>
-      </c>
-      <c r="C7" s="41">
-        <f>-'Asset schedule'!Q2</f>
-        <v/>
-      </c>
-      <c r="D7" s="41">
-        <f>-'Asset schedule'!R2</f>
-        <v/>
-      </c>
-      <c r="E7" s="41">
-        <f>-'Asset schedule'!S2</f>
-        <v/>
-      </c>
-      <c r="F7" s="41">
-        <f>-'Asset schedule'!T2</f>
-        <v/>
+      <c r="B7" s="41" t="n">
+        <v>-406.8404430379748</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>-437.730180379747</v>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>-470.6917903481014</v>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>-505.8552358623419</v>
+      </c>
+      <c r="F7" s="41" t="n">
+        <v>-543.3582964521364</v>
       </c>
     </row>
     <row r="8">
@@ -8631,25 +7740,20 @@
           <t>Add/Less: Change in WC</t>
         </is>
       </c>
-      <c r="B8" s="66">
-        <f>'Financial Statements'!O18+'Financial Statements'!O19+'Financial Statements'!O20</f>
-        <v/>
-      </c>
-      <c r="C8" s="66">
-        <f>'Financial Statements'!P18+'Financial Statements'!P19+'Financial Statements'!P20</f>
-        <v/>
-      </c>
-      <c r="D8" s="66">
-        <f>'Financial Statements'!Q18+'Financial Statements'!Q19+'Financial Statements'!Q20</f>
-        <v/>
-      </c>
-      <c r="E8" s="66">
-        <f>'Financial Statements'!R18+'Financial Statements'!R19+'Financial Statements'!R20</f>
-        <v/>
-      </c>
-      <c r="F8" s="66">
-        <f>'Financial Statements'!S18+'Financial Statements'!S19+'Financial Statements'!S20</f>
-        <v/>
+      <c r="B8" s="66" t="n">
+        <v>-199.5603195533827</v>
+      </c>
+      <c r="C8" s="66" t="n">
+        <v>-32.70455084038326</v>
+      </c>
+      <c r="D8" s="66" t="n">
+        <v>-34.73435014514769</v>
+      </c>
+      <c r="E8" s="66" t="n">
+        <v>-36.88040650426797</v>
+      </c>
+      <c r="F8" s="66" t="n">
+        <v>-39.14902304996701</v>
       </c>
     </row>
     <row r="9">
@@ -8658,25 +7762,20 @@
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B9" s="67">
-        <f>SUM(B4:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="67">
-        <f>SUM(C4:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="67">
-        <f>SUM(D4:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="67">
-        <f>SUM(E4:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="67">
-        <f>SUM(F4:F8)</f>
-        <v/>
+      <c r="B9" s="67" t="n">
+        <v>986.0714991550949</v>
+      </c>
+      <c r="C9" s="67" t="n">
+        <v>1169.89601957583</v>
+      </c>
+      <c r="D9" s="67" t="n">
+        <v>1182.815637609299</v>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>1192.985075692846</v>
+      </c>
+      <c r="F9" s="67" t="n">
+        <v>1199.752685436867</v>
       </c>
     </row>
     <row r="10">
@@ -8689,9 +7788,8 @@
       <c r="C10" s="72" t="n"/>
       <c r="D10" s="72" t="n"/>
       <c r="E10" s="72" t="n"/>
-      <c r="F10" s="108">
-        <f>F9*(1+B27)/(H21-B27)</f>
-        <v/>
+      <c r="F10" s="108" t="n">
+        <v>11152.95574540723</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -8705,25 +7803,20 @@
           <t>FCFF after TV</t>
         </is>
       </c>
-      <c r="B11" s="41">
-        <f>SUM(B9:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="41">
-        <f>SUM(C9:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="41">
-        <f>SUM(D9:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="41">
-        <f>SUM(E9:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="41">
-        <f>SUM(F9:F10)</f>
-        <v/>
+      <c r="B11" s="41" t="n">
+        <v>986.0714991550949</v>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>1169.89601957583</v>
+      </c>
+      <c r="D11" s="41" t="n">
+        <v>1182.815637609299</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>1192.985075692846</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>12352.7084308441</v>
       </c>
     </row>
     <row r="14">
@@ -8742,9 +7835,8 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="B15" s="28">
-        <f>B17+B18*(B19-B17)</f>
-        <v/>
+      <c r="B15" s="28" t="n">
+        <v>0.1407998</v>
       </c>
       <c r="C15" s="44" t="inlineStr">
         <is>
@@ -8821,18 +7913,16 @@
           <t>Wd</t>
         </is>
       </c>
-      <c r="E21" s="98">
-        <f>B21/(B21+B22)</f>
-        <v/>
+      <c r="E21" s="98" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="44" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="H21" s="28">
-        <f>B15*E22+B14*E21*(1-'Financial Statements'!D16)</f>
-        <v/>
+      <c r="H21" s="28" t="n">
+        <v>0.1407998</v>
       </c>
     </row>
     <row r="22">
@@ -8841,18 +7931,16 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="B22" s="100">
-        <f>B24*B25</f>
-        <v/>
+      <c r="B22" s="100" t="n">
+        <v>27310.415</v>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="E22" s="28">
-        <f>B22/(B21+B22)</f>
-        <v/>
+      <c r="E22" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8861,9 +7949,8 @@
           <t>EV</t>
         </is>
       </c>
-      <c r="H23" s="109">
-        <f>NPV(H21,B11:F11)</f>
-        <v/>
+      <c r="H23" s="109" t="n">
+        <v>9657.508522725955</v>
       </c>
       <c r="I23" s="44" t="inlineStr">
         <is>
@@ -8885,9 +7972,8 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="H24">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
+      <c r="H24" t="n">
+        <v>2559.66</v>
       </c>
     </row>
     <row r="25">
@@ -8904,9 +7990,8 @@
           <t>Eq</t>
         </is>
       </c>
-      <c r="H25" s="41">
-        <f>H23+H24</f>
-        <v/>
+      <c r="H25" s="41" t="n">
+        <v>12217.16852272595</v>
       </c>
     </row>
     <row r="27">
@@ -8923,9 +8008,8 @@
           <t>Intrinsic value</t>
         </is>
       </c>
-      <c r="H27" s="41">
-        <f>H25/B25</f>
-        <v/>
+      <c r="H27" s="41" t="n">
+        <v>653.3245199318693</v>
       </c>
     </row>
     <row r="29">
@@ -8941,9 +8025,8 @@
       <c r="D32" s="24" t="n"/>
       <c r="E32" s="24" t="n"/>
       <c r="F32" s="24" t="n"/>
-      <c r="I32" s="41">
-        <f>H27</f>
-        <v/>
+      <c r="I32" s="41" t="n">
+        <v>653.3245199318693</v>
       </c>
       <c r="J32" s="28" t="n">
         <v>0.12</v>
@@ -8980,9 +8063,8 @@
       <c r="I33" s="28" t="n">
         <v>0.05</v>
       </c>
-      <c r="J33" s="41">
-        <f t="dataTable" ref="J33:O38" dt2D="1" dtr="1" r1="H21" r2="B33"/>
-        <v/>
+      <c r="J33" s="41" t="n">
+        <v>772.4391085312169</v>
       </c>
       <c r="K33" s="41" t="n">
         <v>708.9961709554921</v>
@@ -9001,9 +8083,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="I34" s="28">
-        <f>I33+1%</f>
-        <v/>
+      <c r="I34" s="28" t="n">
+        <v>0.06</v>
       </c>
       <c r="J34" s="41" t="n">
         <v>793.0856659073795</v>
@@ -9025,9 +8106,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="I35" s="28">
-        <f>I34+1%</f>
-        <v/>
+      <c r="I35" s="28" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="J35" s="41" t="n">
         <v>814.3696041808344</v>
@@ -9049,9 +8129,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="I36" s="28">
-        <f>I35+1%</f>
-        <v/>
+      <c r="I36" s="28" t="n">
+        <v>0.08</v>
       </c>
       <c r="J36" s="41" t="n">
         <v>836.3059419573533</v>
@@ -9073,9 +8152,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="I37" s="28">
-        <f>I36+1%</f>
-        <v/>
+      <c r="I37" s="28" t="n">
+        <v>0.09</v>
       </c>
       <c r="J37" s="41" t="n">
         <v>858.9099303040131</v>
@@ -9097,9 +8175,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="I38" s="28">
-        <f>I37+1%</f>
-        <v/>
+      <c r="I38" s="28" t="n">
+        <v>0.09999999999999999</v>
       </c>
       <c r="J38" s="41" t="n">
         <v>882.1970544892916</v>
@@ -9221,21 +8298,17 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="B3" s="102">
-        <f>'Financial Statements'!D17/Relative!$B$8</f>
-        <v/>
-      </c>
-      <c r="C3" s="102">
-        <f>'Financial Statements'!E17/Relative!$B$8</f>
-        <v/>
-      </c>
-      <c r="D3" s="102">
-        <f>'Financial Statements'!F17/Relative!$B$8</f>
-        <v/>
-      </c>
-      <c r="E3" s="102">
-        <f>'Financial Statements'!G17/Relative!$B$8</f>
-        <v/>
+      <c r="B3" s="102" t="n">
+        <v>48.5053475935828</v>
+      </c>
+      <c r="C3" s="102" t="n">
+        <v>50.17759674807353</v>
+      </c>
+      <c r="D3" s="102" t="n">
+        <v>53.62165576411809</v>
+      </c>
+      <c r="E3" s="102" t="n">
+        <v>56.82511611650435</v>
       </c>
       <c r="F3" t="n">
         <v>80.90000000000001</v>
@@ -9280,21 +8353,17 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="B4" s="100">
-        <f>'Financial Statements'!D2</f>
-        <v/>
-      </c>
-      <c r="C4" s="100">
-        <f>'Financial Statements'!E2</f>
-        <v/>
-      </c>
-      <c r="D4" s="100">
-        <f>'Financial Statements'!F2</f>
-        <v/>
-      </c>
-      <c r="E4" s="100">
-        <f>'Financial Statements'!G2</f>
-        <v/>
+      <c r="B4" s="100" t="n">
+        <v>13413.58</v>
+      </c>
+      <c r="C4" s="100" t="n">
+        <v>14440.82251898734</v>
+      </c>
+      <c r="D4" s="100" t="n">
+        <v>15537.25533987342</v>
+      </c>
+      <c r="E4" s="100" t="n">
+        <v>16707.22938655064</v>
       </c>
       <c r="F4" s="100" t="n">
         <v>32304.6</v>
@@ -9339,21 +8408,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B5" s="26">
-        <f>'Financial Statements'!D10</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
-        <f>'Financial Statements'!E10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
-        <f>'Financial Statements'!F10</f>
-        <v/>
-      </c>
-      <c r="E5" s="26">
-        <f>'Financial Statements'!G10</f>
-        <v/>
+      <c r="B5" s="26" t="n">
+        <v>2034.749999999998</v>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>1973.96345335443</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>2046.152179594937</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>2116.693757029272</v>
       </c>
       <c r="F5" s="100" t="n">
         <v>6145.2</v>
@@ -9401,9 +8466,8 @@
       <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="100">
-        <f>15863+2763</f>
-        <v/>
+      <c r="F6" s="100" t="n">
+        <v>18626</v>
       </c>
       <c r="G6" s="100" t="n"/>
       <c r="H6" s="100" t="n"/>
@@ -9421,9 +8485,8 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B7" s="100">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
+      <c r="B7" s="100" t="n">
+        <v>2559.66</v>
       </c>
       <c r="F7" s="100" t="n">
         <v>218</v>
@@ -9491,29 +8554,23 @@
           <t>EV</t>
         </is>
       </c>
-      <c r="B12" s="98">
-        <f>(B9*B8)+B6-B7</f>
-        <v/>
-      </c>
-      <c r="F12" s="98">
-        <f>(F9*F8)+F6-F7</f>
-        <v/>
-      </c>
-      <c r="J12" s="98">
-        <f>(J9*J8)+J6-J7</f>
-        <v/>
-      </c>
-      <c r="N12" s="98">
-        <f>(N9*N8)+N6-N7</f>
-        <v/>
-      </c>
-      <c r="P12" s="98">
-        <f>AVERAGE(B12,F12,J12,N12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="98">
-        <f>MEDIAN(B12,F12,J12,N12)</f>
-        <v/>
+      <c r="B12" s="98" t="n">
+        <v>30314.94</v>
+      </c>
+      <c r="F12" s="98" t="n">
+        <v>126638</v>
+      </c>
+      <c r="J12" s="98" t="n">
+        <v>40043.5</v>
+      </c>
+      <c r="N12" s="98" t="n">
+        <v>30906</v>
+      </c>
+      <c r="P12" s="98" t="n">
+        <v>56975.61</v>
+      </c>
+      <c r="Q12" s="98" t="n">
+        <v>35474.75</v>
       </c>
     </row>
     <row r="13">
@@ -9522,29 +8579,23 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="B13" s="103">
-        <f>(E4/B4)^(1/3)-1</f>
-        <v/>
-      </c>
-      <c r="F13" s="103">
-        <f>(I4/F4)^(1/3)-1</f>
-        <v/>
-      </c>
-      <c r="J13" s="103">
-        <f>(M4/J4)^(1/3)-1</f>
-        <v/>
-      </c>
-      <c r="N13" s="103">
-        <f>(Q4/N4)^(1/3)-1</f>
-        <v/>
-      </c>
-      <c r="P13" s="98">
-        <f>AVERAGE(B13,F13,J13,N13)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="98">
-        <f>MEDIAN(B13,F13,J13,N13)</f>
-        <v/>
+      <c r="B13" s="103" t="n">
+        <v>0.0759363426072921</v>
+      </c>
+      <c r="F13" s="103" t="n">
+        <v>0.1364431479867485</v>
+      </c>
+      <c r="J13" s="103" t="n">
+        <v>0.09525345934086094</v>
+      </c>
+      <c r="N13" s="103" t="n">
+        <v>0.1434422250383043</v>
+      </c>
+      <c r="P13" s="98" t="n">
+        <v>0.1127687937433015</v>
+      </c>
+      <c r="Q13" s="98" t="n">
+        <v>0.1158483036638047</v>
       </c>
     </row>
     <row r="14">
@@ -9553,29 +8604,23 @@
           <t>Trailing PE</t>
         </is>
       </c>
-      <c r="B14" s="102">
-        <f>B9/B3</f>
-        <v/>
-      </c>
-      <c r="F14" s="102">
-        <f>F9/F3</f>
-        <v/>
-      </c>
-      <c r="J14" s="102">
-        <f>J9/J3</f>
-        <v/>
-      </c>
-      <c r="N14" s="102">
-        <f>N9/N3</f>
-        <v/>
-      </c>
-      <c r="P14" s="98">
-        <f>AVERAGE(B14,F14,J14,N14)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="98">
-        <f>MEDIAN(B14,F14,J14,N14)</f>
-        <v/>
+      <c r="B14" s="102" t="n">
+        <v>36.24342649247567</v>
+      </c>
+      <c r="F14" s="102" t="n">
+        <v>48.8257107540173</v>
+      </c>
+      <c r="J14" s="102" t="n">
+        <v>37.04292527821939</v>
+      </c>
+      <c r="N14" s="102" t="n">
+        <v>47.97996661101836</v>
+      </c>
+      <c r="P14" s="98" t="n">
+        <v>42.52300728393269</v>
+      </c>
+      <c r="Q14" s="98" t="n">
+        <v>42.51144594461888</v>
       </c>
     </row>
     <row r="15">
@@ -9584,29 +8629,23 @@
           <t>Trailing PS</t>
         </is>
       </c>
-      <c r="B15" s="102">
-        <f>B9/(B4/B8)</f>
-        <v/>
-      </c>
-      <c r="F15" s="102">
-        <f>F9/(F4/F8)</f>
-        <v/>
-      </c>
-      <c r="J15" s="102">
-        <f>J9/(J4/J8)</f>
-        <v/>
-      </c>
-      <c r="N15" s="102">
-        <f>N9/(N4/N8)</f>
-        <v/>
-      </c>
-      <c r="P15" s="98">
-        <f>AVERAGE(B15,F15,J15,N15)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="98">
-        <f>MEDIAN(B15,F15,J15,N15)</f>
-        <v/>
+      <c r="B15" s="102" t="n">
+        <v>2.450844591824106</v>
+      </c>
+      <c r="F15" s="102" t="n">
+        <v>3.350296861747244</v>
+      </c>
+      <c r="J15" s="102" t="n">
+        <v>4.427198499076281</v>
+      </c>
+      <c r="N15" s="102" t="n">
+        <v>2.937831056593254</v>
+      </c>
+      <c r="P15" s="98" t="n">
+        <v>3.291542752310221</v>
+      </c>
+      <c r="Q15" s="98" t="n">
+        <v>3.144063959170249</v>
       </c>
     </row>
     <row r="16">
@@ -9615,29 +8654,23 @@
           <t>Trailing PEG</t>
         </is>
       </c>
-      <c r="B16" s="102">
-        <f>B14/B13</f>
-        <v/>
-      </c>
-      <c r="F16" s="102">
-        <f>F14/F13</f>
-        <v/>
-      </c>
-      <c r="J16" s="102">
-        <f>J14/J13</f>
-        <v/>
-      </c>
-      <c r="N16" s="102">
-        <f>N14/N13</f>
-        <v/>
-      </c>
-      <c r="P16" s="98">
-        <f>AVERAGE(B16,F16,J16,N16)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="98">
-        <f>MEDIAN(B16,F16,J16,N16)</f>
-        <v/>
+      <c r="B16" s="102" t="n">
+        <v>477.2869649504985</v>
+      </c>
+      <c r="F16" s="102" t="n">
+        <v>357.8465571518425</v>
+      </c>
+      <c r="J16" s="102" t="n">
+        <v>388.8879788151596</v>
+      </c>
+      <c r="N16" s="102" t="n">
+        <v>334.4898379693007</v>
+      </c>
+      <c r="P16" s="98" t="n">
+        <v>389.6278347217003</v>
+      </c>
+      <c r="Q16" s="98" t="n">
+        <v>373.3672679835011</v>
       </c>
     </row>
     <row r="17"/>
@@ -9647,29 +8680,23 @@
           <t>Leading PE</t>
         </is>
       </c>
-      <c r="B18" s="102">
-        <f>B9/C3</f>
-        <v/>
-      </c>
-      <c r="F18" s="102">
-        <f>F9/G3</f>
-        <v/>
-      </c>
-      <c r="J18" s="102">
-        <f>J9/K3</f>
-        <v/>
-      </c>
-      <c r="N18" s="102">
-        <f>N9/O3</f>
-        <v/>
-      </c>
-      <c r="P18" s="98">
-        <f>AVERAGE(B18,F18,J18,N18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="98">
-        <f>MEDIAN(B18,F18,J18,N18)</f>
-        <v/>
+      <c r="B18" s="102" t="n">
+        <v>35.03555598380655</v>
+      </c>
+      <c r="F18" s="102" t="n">
+        <v>37.98076923076923</v>
+      </c>
+      <c r="J18" s="102" t="n">
+        <v>34.06432748538012</v>
+      </c>
+      <c r="N18" s="102" t="n">
+        <v>89.53271028037383</v>
+      </c>
+      <c r="P18" s="98" t="n">
+        <v>49.15334074508243</v>
+      </c>
+      <c r="Q18" s="98" t="n">
+        <v>36.50816260728789</v>
       </c>
     </row>
     <row r="19">
@@ -9678,29 +8705,23 @@
           <t>Leading PS</t>
         </is>
       </c>
-      <c r="B19" s="47">
-        <f>B9/(C4/B8)</f>
-        <v/>
-      </c>
-      <c r="F19" s="47">
-        <f>F9/(G4/F8)</f>
-        <v/>
-      </c>
-      <c r="J19" s="47">
-        <f>J9/(K4/J8)</f>
-        <v/>
-      </c>
-      <c r="N19" s="47">
-        <f>N9/(O4/N8)</f>
-        <v/>
-      </c>
-      <c r="P19" s="98">
-        <f>AVERAGE(B19,F19,J19,N19)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="98">
-        <f>MEDIAN(B19,F19,J19,N19)</f>
-        <v/>
+      <c r="B19" s="47" t="n">
+        <v>2.276504676709047</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <v>2.964969906500579</v>
+      </c>
+      <c r="J19" s="47" t="n">
+        <v>4.037687586754782</v>
+      </c>
+      <c r="N19" s="47" t="n">
+        <v>2.58047138047138</v>
+      </c>
+      <c r="P19" s="98" t="n">
+        <v>2.964908387608947</v>
+      </c>
+      <c r="Q19" s="98" t="n">
+        <v>2.77272064348598</v>
       </c>
     </row>
     <row r="20">
@@ -9709,29 +8730,23 @@
           <t>Leading PEG</t>
         </is>
       </c>
-      <c r="B20" s="102">
-        <f>B18/B13</f>
-        <v/>
-      </c>
-      <c r="F20" s="102">
-        <f>F18/F13</f>
-        <v/>
-      </c>
-      <c r="J20" s="102">
-        <f>J18/J13</f>
-        <v/>
-      </c>
-      <c r="N20" s="102">
-        <f>N18/N13</f>
-        <v/>
-      </c>
-      <c r="P20" s="98">
-        <f>AVERAGE(B20,F20,J20,N20)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="98">
-        <f>MEDIAN(B20,F20,J20,N20)</f>
-        <v/>
+      <c r="B20" s="102" t="n">
+        <v>461.3806088211855</v>
+      </c>
+      <c r="F20" s="102" t="n">
+        <v>278.3633314767698</v>
+      </c>
+      <c r="J20" s="102" t="n">
+        <v>357.6177466004904</v>
+      </c>
+      <c r="N20" s="102" t="n">
+        <v>624.172625992558</v>
+      </c>
+      <c r="P20" s="98" t="n">
+        <v>430.3835782227509</v>
+      </c>
+      <c r="Q20" s="98" t="n">
+        <v>409.4991777108379</v>
       </c>
     </row>
     <row r="21"/>
@@ -9741,29 +8756,23 @@
           <t>Trailing EV/EBITDA</t>
         </is>
       </c>
-      <c r="B22" s="102">
-        <f>B12/B5</f>
-        <v/>
-      </c>
-      <c r="F22" s="102">
-        <f>F12/F5</f>
-        <v/>
-      </c>
-      <c r="J22" s="102">
-        <f>J12/J5</f>
-        <v/>
-      </c>
-      <c r="N22" s="102">
-        <f>N12/N5</f>
-        <v/>
-      </c>
-      <c r="P22" s="98">
-        <f>AVERAGE(B22,F22,J22,N22)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="98">
-        <f>MEDIAN(B22,F22,J22,N22)</f>
-        <v/>
+      <c r="B22" s="102" t="n">
+        <v>14.89860670844085</v>
+      </c>
+      <c r="F22" s="102" t="n">
+        <v>20.60762871834928</v>
+      </c>
+      <c r="J22" s="102" t="n">
+        <v>20.63991546827483</v>
+      </c>
+      <c r="N22" s="102" t="n">
+        <v>15.25167785234899</v>
+      </c>
+      <c r="P22" s="98" t="n">
+        <v>17.84945718685349</v>
+      </c>
+      <c r="Q22" s="98" t="n">
+        <v>17.92965328534914</v>
       </c>
     </row>
     <row r="23">
@@ -9772,29 +8781,23 @@
           <t>Trailing EV/Sales</t>
         </is>
       </c>
-      <c r="B23" s="102">
-        <f>B12/B4</f>
-        <v/>
-      </c>
-      <c r="F23" s="102">
-        <f>F12/F4</f>
-        <v/>
-      </c>
-      <c r="J23" s="102">
-        <f>J12/J4</f>
-        <v/>
-      </c>
-      <c r="N23" s="102">
-        <f>N12/N4</f>
-        <v/>
-      </c>
-      <c r="P23" s="98">
-        <f>AVERAGE(B23,F23,J23,N23)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="98">
-        <f>MEDIAN(B23,F23,J23,N23)</f>
-        <v/>
+      <c r="B23" s="102" t="n">
+        <v>2.26001857818718</v>
+      </c>
+      <c r="F23" s="102" t="n">
+        <v>3.920122830804282</v>
+      </c>
+      <c r="J23" s="102" t="n">
+        <v>3.833050952914262</v>
+      </c>
+      <c r="N23" s="102" t="n">
+        <v>3.590047393364929</v>
+      </c>
+      <c r="P23" s="98" t="n">
+        <v>3.400809938817663</v>
+      </c>
+      <c r="Q23" s="98" t="n">
+        <v>3.711549173139596</v>
       </c>
     </row>
     <row r="24">
@@ -9803,29 +8806,23 @@
           <t>Leading EV/EBITDA</t>
         </is>
       </c>
-      <c r="B24" s="102">
-        <f>B12/C5</f>
-        <v/>
-      </c>
-      <c r="F24" s="102">
-        <f>F12/G5</f>
-        <v/>
-      </c>
-      <c r="J24" s="102">
-        <f>J12/K5</f>
-        <v/>
-      </c>
-      <c r="N24" s="102">
-        <f>N12/O5</f>
-        <v/>
-      </c>
-      <c r="P24" s="98">
-        <f>AVERAGE(B24,F24,J24,N24)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="98">
-        <f>MEDIAN(B24,F24,J24,N24)</f>
-        <v/>
+      <c r="B24" s="102" t="n">
+        <v>15.35739678892468</v>
+      </c>
+      <c r="F24" s="102" t="n">
+        <v>18.63885904361008</v>
+      </c>
+      <c r="J24" s="102" t="n">
+        <v>19.02755999049656</v>
+      </c>
+      <c r="N24" s="102" t="n">
+        <v>14.55907292255512</v>
+      </c>
+      <c r="P24" s="98" t="n">
+        <v>16.89572218639661</v>
+      </c>
+      <c r="Q24" s="98" t="n">
+        <v>16.99812791626738</v>
       </c>
     </row>
     <row r="25">
@@ -9834,29 +8831,23 @@
           <t xml:space="preserve">Leading EV/Sales </t>
         </is>
       </c>
-      <c r="B25" s="102">
-        <f>B12/C4</f>
-        <v/>
-      </c>
-      <c r="F25" s="102">
-        <f>F12/G4</f>
-        <v/>
-      </c>
-      <c r="J25" s="102">
-        <f>J12/K4</f>
-        <v/>
-      </c>
-      <c r="N25" s="102">
-        <f>N12/O4</f>
-        <v/>
-      </c>
-      <c r="P25" s="98">
-        <f>AVERAGE(B25,F25,J25,N25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="98">
-        <f>MEDIAN(B25,F25,J25,N25)</f>
-        <v/>
+      <c r="B25" s="102" t="n">
+        <v>2.099253000314959</v>
+      </c>
+      <c r="F25" s="102" t="n">
+        <v>3.469258606850414</v>
+      </c>
+      <c r="J25" s="102" t="n">
+        <v>3.495813945367404</v>
+      </c>
+      <c r="N25" s="102" t="n">
+        <v>3.153351698806244</v>
+      </c>
+      <c r="P25" s="98" t="n">
+        <v>3.054419312834755</v>
+      </c>
+      <c r="Q25" s="98" t="n">
+        <v>3.311305152828329</v>
       </c>
     </row>
     <row r="28">
@@ -9882,13 +8873,11 @@
           <t>Trailing PE</t>
         </is>
       </c>
-      <c r="B29" s="98">
-        <f>$Q$14*$B$3*0.8</f>
-        <v/>
-      </c>
-      <c r="C29" s="98">
-        <f>$Q$14*$B$3*1.2</f>
-        <v/>
+      <c r="B29" s="98" t="n">
+        <v>1649.625969799636</v>
+      </c>
+      <c r="C29" s="98" t="n">
+        <v>2474.438954699453</v>
       </c>
       <c r="D29" s="28" t="n">
         <v>0.05</v>
@@ -9900,13 +8889,11 @@
           <t>Trailing PS</t>
         </is>
       </c>
-      <c r="B30" s="98">
-        <f>$Q$15*($B$4/$B$8)*0.8</f>
-        <v/>
-      </c>
-      <c r="C30" s="98">
-        <f>$Q$15*($B$4/$B$8)*1.2</f>
-        <v/>
+      <c r="B30" s="98" t="n">
+        <v>1804.199077708957</v>
+      </c>
+      <c r="C30" s="98" t="n">
+        <v>2706.298616563435</v>
       </c>
       <c r="D30" s="28" t="n">
         <v>0.05</v>
@@ -9924,13 +8911,11 @@
           <t>Trailing PEG</t>
         </is>
       </c>
-      <c r="B31" s="98">
-        <f>$Q$16*$B$3*$B$13*0.8</f>
-        <v/>
-      </c>
-      <c r="C31" s="98">
-        <f>$Q$16*$B$3*$B$13*1.2</f>
-        <v/>
+      <c r="B31" s="98" t="n">
+        <v>1100.184510059806</v>
+      </c>
+      <c r="C31" s="98" t="n">
+        <v>1650.276765089709</v>
       </c>
       <c r="D31" s="28" t="n">
         <v>0.05</v>
@@ -9952,24 +8937,20 @@
           <t>Leading PE</t>
         </is>
       </c>
-      <c r="B32" s="98">
-        <f>$Q$18*$C$3*0.8</f>
-        <v/>
-      </c>
-      <c r="C32" s="98">
-        <f>$Q$18*$C$3*1.2</f>
-        <v/>
+      <c r="B32" s="98" t="n">
+        <v>1465.513489057271</v>
+      </c>
+      <c r="C32" s="98" t="n">
+        <v>2198.270233585906</v>
       </c>
       <c r="D32" s="28" t="n">
         <v>0.05</v>
       </c>
-      <c r="I32" s="114">
-        <f>SUMPRODUCT(B29:B40,D29:D40)</f>
-        <v/>
-      </c>
-      <c r="J32" s="114">
-        <f>SUMPRODUCT(C29:C40,D29:D40)</f>
-        <v/>
+      <c r="I32" s="114" t="n">
+        <v>1090.853753518176</v>
+      </c>
+      <c r="J32" s="114" t="n">
+        <v>1636.280630277264</v>
       </c>
     </row>
     <row r="33">
@@ -9978,13 +8959,11 @@
           <t>Leading PS</t>
         </is>
       </c>
-      <c r="B33" s="98">
-        <f>$Q$19*($C$4/$B$8)*0.8</f>
-        <v/>
-      </c>
-      <c r="C33" s="98">
-        <f>$Q$19*($C$4/$B$8)*1.2</f>
-        <v/>
+      <c r="B33" s="98" t="n">
+        <v>1712.956864483996</v>
+      </c>
+      <c r="C33" s="98" t="n">
+        <v>2569.435296725994</v>
       </c>
       <c r="D33" s="28" t="n">
         <v>0.05</v>
@@ -9996,13 +8975,11 @@
           <t>Leading PEG</t>
         </is>
       </c>
-      <c r="B34" s="98">
-        <f>$Q$20*$C$3*$B$13*0.8</f>
-        <v/>
-      </c>
-      <c r="C34" s="98">
-        <f>$Q$20*$C$3*$B$13*1.2</f>
-        <v/>
+      <c r="B34" s="98" t="n">
+        <v>1248.252814534146</v>
+      </c>
+      <c r="C34" s="98" t="n">
+        <v>1872.379221801218</v>
       </c>
       <c r="D34" s="28" t="n">
         <v>0.05</v>
@@ -10014,13 +8991,11 @@
           <t>Trailing EV/EBITDA</t>
         </is>
       </c>
-      <c r="B35" s="100">
-        <f>D45*0.8</f>
-        <v/>
-      </c>
-      <c r="C35" s="100">
-        <f>D45*1.2</f>
-        <v/>
+      <c r="B35" s="100" t="n">
+        <v>1670.246931438038</v>
+      </c>
+      <c r="C35" s="100" t="n">
+        <v>2505.370397157056</v>
       </c>
       <c r="D35" s="28" t="n">
         <v>0.05</v>
@@ -10032,13 +9007,11 @@
           <t>Trailing EV/Sales</t>
         </is>
       </c>
-      <c r="B36" s="100">
-        <f>D46*0.8</f>
-        <v/>
-      </c>
-      <c r="C36" s="100">
-        <f>D46*1.2</f>
-        <v/>
+      <c r="B36" s="100" t="n">
+        <v>2239.350663437083</v>
+      </c>
+      <c r="C36" s="100" t="n">
+        <v>3359.025995155624</v>
       </c>
       <c r="D36" s="28" t="n">
         <v>0.05</v>
@@ -10050,13 +9023,11 @@
           <t>Leading EV/EBITDA</t>
         </is>
       </c>
-      <c r="B37" s="100">
-        <f>D47*0.8</f>
-        <v/>
-      </c>
-      <c r="C37" s="100">
-        <f>D47*1.2</f>
-        <v/>
+      <c r="B37" s="100" t="n">
+        <v>1544.955862338204</v>
+      </c>
+      <c r="C37" s="100" t="n">
+        <v>2317.433793507305</v>
       </c>
       <c r="D37" s="28" t="n">
         <v>0.05</v>
@@ -10068,13 +9039,11 @@
           <t xml:space="preserve">Leading EV/Sales </t>
         </is>
       </c>
-      <c r="B38" s="100">
-        <f>D48*0.8</f>
-        <v/>
-      </c>
-      <c r="C38" s="100">
-        <f>D48*1.2</f>
-        <v/>
+      <c r="B38" s="100" t="n">
+        <v>2155.19272805143</v>
+      </c>
+      <c r="C38" s="100" t="n">
+        <v>3232.789092077145</v>
       </c>
       <c r="D38" s="28" t="n">
         <v>0.05</v>
@@ -10086,13 +9055,11 @@
           <t>DCF</t>
         </is>
       </c>
-      <c r="B40" s="100">
-        <f>DCF!H27*0.8</f>
-        <v/>
-      </c>
-      <c r="C40" s="100">
-        <f>DCF!H27*1.2</f>
-        <v/>
+      <c r="B40" s="100" t="n">
+        <v>522.6596159454955</v>
+      </c>
+      <c r="C40" s="100" t="n">
+        <v>783.9894239182431</v>
       </c>
       <c r="D40" s="28" t="n">
         <v>0.5</v>
@@ -10121,17 +9088,14 @@
           <t>Trailing EV/EBITDA</t>
         </is>
       </c>
-      <c r="B45" s="100">
-        <f>Q22*B5</f>
-        <v/>
-      </c>
-      <c r="C45" s="98">
-        <f>B45-$B$6+$B$7</f>
-        <v/>
-      </c>
-      <c r="D45" s="41">
-        <f>C45/$B$8</f>
-        <v/>
+      <c r="B45" s="100" t="n">
+        <v>36482.36202236412</v>
+      </c>
+      <c r="C45" s="98" t="n">
+        <v>39042.02202236412</v>
+      </c>
+      <c r="D45" s="41" t="n">
+        <v>2087.808664297547</v>
       </c>
     </row>
     <row r="46">
@@ -10140,17 +9104,14 @@
           <t>Trailing EV/Sales</t>
         </is>
       </c>
-      <c r="B46" s="100">
-        <f>Q23*B4</f>
-        <v/>
-      </c>
-      <c r="C46" s="98">
-        <f>B46-$B$6+$B$7</f>
-        <v/>
-      </c>
-      <c r="D46" s="41">
-        <f>C46/$B$8</f>
-        <v/>
+      <c r="B46" s="100" t="n">
+        <v>49785.16175784182</v>
+      </c>
+      <c r="C46" s="98" t="n">
+        <v>52344.82175784181</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>2799.188329296353</v>
       </c>
     </row>
     <row r="47">
@@ -10159,17 +9120,14 @@
           <t>Leading EV/EBITDA</t>
         </is>
       </c>
-      <c r="B47" s="100">
-        <f>Q24*C5</f>
-        <v/>
-      </c>
-      <c r="C47" s="98">
-        <f>B47-$B$6+$B$7</f>
-        <v/>
-      </c>
-      <c r="D47" s="41">
-        <f>C47/$B$8</f>
-        <v/>
+      <c r="B47" s="100" t="n">
+        <v>33553.6832821555</v>
+      </c>
+      <c r="C47" s="98" t="n">
+        <v>36113.3432821555</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <v>1931.194827922754</v>
       </c>
     </row>
     <row r="48">
@@ -10178,17 +9136,14 @@
           <t xml:space="preserve">Leading EV/Sales </t>
         </is>
       </c>
-      <c r="B48" s="100">
-        <f>Q25*C4</f>
-        <v/>
-      </c>
-      <c r="C48" s="98">
-        <f>B48-$B$6+$B$7</f>
-        <v/>
-      </c>
-      <c r="D48" s="41">
-        <f>C48/$B$8</f>
-        <v/>
+      <c r="B48" s="100" t="n">
+        <v>47817.97001820216</v>
+      </c>
+      <c r="C48" s="98" t="n">
+        <v>50377.63001820217</v>
+      </c>
+      <c r="D48" s="41" t="n">
+        <v>2693.990910064287</v>
       </c>
     </row>
   </sheetData>
@@ -10534,53 +9489,41 @@
           <t>Ultratech</t>
         </is>
       </c>
-      <c r="B14" s="15">
-        <f>B7/E7</f>
-        <v/>
-      </c>
-      <c r="C14" s="15">
-        <f>C7/F7</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>D7/G7</f>
-        <v/>
-      </c>
-      <c r="E14" s="118">
-        <f>E7/H7</f>
-        <v/>
-      </c>
-      <c r="F14" s="118">
-        <f>F7/I7</f>
-        <v/>
-      </c>
-      <c r="G14" s="118">
-        <f>G7/J7</f>
-        <v/>
-      </c>
-      <c r="H14" s="118">
-        <f>H7/K7</f>
-        <v/>
-      </c>
-      <c r="I14" s="118">
-        <f>I7/L7</f>
-        <v/>
-      </c>
-      <c r="J14" s="118">
-        <f>J7/M7</f>
-        <v/>
-      </c>
-      <c r="K14" s="15">
-        <f>B14*E14*H14</f>
-        <v/>
-      </c>
-      <c r="L14" s="15">
-        <f>C14*F14*I14</f>
-        <v/>
-      </c>
-      <c r="M14" s="15">
-        <f>D14*G14*J14</f>
-        <v/>
+      <c r="B14" s="15" t="n">
+        <v>0.08024350687825672</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0.08568787506786069</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>0.07721315537737194</v>
+      </c>
+      <c r="E14" s="118" t="n">
+        <v>1.310765549283686</v>
+      </c>
+      <c r="F14" s="118" t="n">
+        <v>1.272055545071267</v>
+      </c>
+      <c r="G14" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="118" t="n">
+        <v>1.194862127479054</v>
+      </c>
+      <c r="I14" s="118" t="n">
+        <v>1.114559448964497</v>
+      </c>
+      <c r="J14" s="118" t="n">
+        <v>1.206885259596508</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>0.1256761056315622</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>0.1214866863905326</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>0.09318741907188505</v>
       </c>
     </row>
     <row r="15">
@@ -10589,53 +9532,41 @@
           <t xml:space="preserve">Ambuja </t>
         </is>
       </c>
-      <c r="B15" s="15">
-        <f>B8/E8</f>
-        <v/>
-      </c>
-      <c r="C15" s="15">
-        <f>C8/F8</f>
-        <v/>
-      </c>
-      <c r="D15" s="15">
-        <f>D8/G8</f>
-        <v/>
-      </c>
-      <c r="E15" s="118">
-        <f>E8/H8</f>
-        <v/>
-      </c>
-      <c r="F15" s="118">
-        <f>F8/I8</f>
-        <v/>
-      </c>
-      <c r="G15" s="118">
-        <f>G8/J8</f>
-        <v/>
-      </c>
-      <c r="H15" s="118">
-        <f>H8/K8</f>
-        <v/>
-      </c>
-      <c r="I15" s="118">
-        <f>I8/L8</f>
-        <v/>
-      </c>
-      <c r="J15" s="118">
-        <f>J8/M8</f>
-        <v/>
-      </c>
-      <c r="K15" s="15">
-        <f>B15*E15*H15</f>
-        <v/>
-      </c>
-      <c r="L15" s="15">
-        <f>C15*F15*I15</f>
-        <v/>
-      </c>
-      <c r="M15" s="15">
-        <f>D15*G15*J15</f>
-        <v/>
+      <c r="B15" s="15" t="n">
+        <v>0.08625106746370624</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.1022266096303609</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0.1220703125</v>
+      </c>
+      <c r="E15" s="118" t="n">
+        <v>0.4787652680533551</v>
+      </c>
+      <c r="F15" s="118" t="n">
+        <v>0.4763571764460003</v>
+      </c>
+      <c r="G15" s="118" t="n">
+        <v>0.5354528341351181</v>
+      </c>
+      <c r="H15" s="118" t="n">
+        <v>0.7454285499858472</v>
+      </c>
+      <c r="I15" s="118" t="n">
+        <v>0.9887445645912796</v>
+      </c>
+      <c r="J15" s="118" t="n">
+        <v>0.9574825478728758</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0.03078173804817113</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>0.04814828017132937</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>0.06258383104168033</v>
       </c>
     </row>
     <row r="16">
@@ -10644,53 +9575,41 @@
           <t>ACC</t>
         </is>
       </c>
-      <c r="B16" s="15">
-        <f>B9/E9</f>
-        <v/>
-      </c>
-      <c r="C16" s="15">
-        <f>C9/F9</f>
-        <v/>
-      </c>
-      <c r="D16" s="15">
-        <f>D9/G9</f>
-        <v/>
-      </c>
-      <c r="E16" s="118">
-        <f>E9/H9</f>
-        <v/>
-      </c>
-      <c r="F16" s="118">
-        <f>F9/I9</f>
-        <v/>
-      </c>
-      <c r="G16" s="118">
-        <f>G9/J9</f>
-        <v/>
-      </c>
-      <c r="H16" s="118">
-        <f>H9/K9</f>
-        <v/>
-      </c>
-      <c r="I16" s="118">
-        <f>I9/L9</f>
-        <v/>
-      </c>
-      <c r="J16" s="118">
-        <f>J9/M9</f>
-        <v/>
-      </c>
-      <c r="K16" s="15">
-        <f>B16*E16*H16</f>
-        <v/>
-      </c>
-      <c r="L16" s="15">
-        <f>C16*F16*I16</f>
-        <v/>
-      </c>
-      <c r="M16" s="15">
-        <f>D16*G16*J16</f>
-        <v/>
+      <c r="B16" s="15" t="n">
+        <v>0.04396107784431138</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.05206465183217093</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0.06451759228114153</v>
+      </c>
+      <c r="E16" s="118" t="n">
+        <v>1.421833228327686</v>
+      </c>
+      <c r="F16" s="118" t="n">
+        <v>1.361384486533853</v>
+      </c>
+      <c r="G16" s="118" t="n">
+        <v>1.559118772862487</v>
+      </c>
+      <c r="H16" s="118" t="n">
+        <v>1.115801423560231</v>
+      </c>
+      <c r="I16" s="118" t="n">
+        <v>1.053652306376549</v>
+      </c>
+      <c r="J16" s="118" t="n">
+        <v>0.9820584630606931</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>0.0697435264109135</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>0.07468288527609936</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>0.09878583953164585</v>
       </c>
     </row>
   </sheetData>
